--- a/rlt_leave_report.xlsx
+++ b/rlt_leave_report.xlsx
@@ -1871,13 +1871,13 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-02-09T12:32:00.064+0500</t>
+          <t>2026-03-02T14:17:45.818+0500</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
         <v>8</v>
@@ -1946,13 +1946,13 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-01-29T16:13:17.413+0500</t>
+          <t>2026-03-02T12:44:58.393+0500</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M20" t="n">
         <v>8</v>
@@ -2025,13 +2025,13 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-01-29T16:17:44.255+0500</t>
+          <t>2026-03-02T12:45:03.019+0500</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
         <v>8</v>
@@ -2104,13 +2104,13 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-01-29T16:18:29.071+0500</t>
+          <t>2026-03-02T12:45:09.193+0500</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
         <v>8</v>
@@ -2183,13 +2183,13 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-01-29T16:21:57.948+0500</t>
+          <t>2026-03-02T12:45:13.551+0500</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
         <v>8</v>
@@ -2262,13 +2262,13 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-01-29T16:23:12.972+0500</t>
+          <t>2026-03-02T12:45:28.982+0500</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
         <v>8</v>
@@ -2341,13 +2341,13 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-01-29T16:24:51.116+0500</t>
+          <t>2026-03-02T12:45:31.965+0500</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M25" t="n">
         <v>8</v>
@@ -2420,13 +2420,13 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-01-29T16:25:35.949+0500</t>
+          <t>2026-03-02T12:45:34.794+0500</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
         <v>8</v>
@@ -2499,13 +2499,13 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-01-29T16:25:58.817+0500</t>
+          <t>2026-03-02T12:45:39.947+0500</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
         <v>8</v>
@@ -2578,13 +2578,13 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-01-29T16:26:25.077+0500</t>
+          <t>2026-03-02T12:45:43.917+0500</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
         <v>8</v>
@@ -2657,13 +2657,13 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-01-29T16:26:43.424+0500</t>
+          <t>2026-03-02T12:45:47.698+0500</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
         <v>8</v>
@@ -2736,13 +2736,13 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-01-29T16:27:02.302+0500</t>
+          <t>2026-03-02T12:45:51.097+0500</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
         <v>8</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2815,13 +2815,13 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-02-02T09:47:41.356+0500</t>
+          <t>2026-03-02T14:48:16.498+0500</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
         <v>8</v>
@@ -2969,13 +2969,13 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-01-30T16:56:01.700+0500</t>
+          <t>2026-03-02T14:16:20.211+0500</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3281,13 +3281,13 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-02-02T09:47:44.398+0500</t>
+          <t>2026-03-02T13:51:49.750+0500</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M37" t="n">
         <v>8</v>
@@ -3360,13 +3360,13 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-02-02T10:38:26.241+0500</t>
+          <t>2026-03-02T13:42:10.695+0500</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M38" t="n">
         <v>8</v>
@@ -3439,13 +3439,13 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-02-02T09:38:30.583+0500</t>
+          <t>2026-03-02T13:51:58.269+0500</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M39" t="n">
         <v>8</v>
@@ -3518,13 +3518,13 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-02-02T09:43:30.522+0500</t>
+          <t>2026-03-02T13:52:05.234+0500</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
         <v>8</v>
@@ -3597,13 +3597,13 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-02-02T09:45:57.436+0500</t>
+          <t>2026-03-02T13:52:11.634+0500</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M41" t="n">
         <v>8</v>
@@ -3755,13 +3755,13 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-02-02T12:11:51.912+0500</t>
+          <t>2026-03-02T14:10:46.759+0500</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M43" t="n">
         <v>8</v>
@@ -3834,13 +3834,13 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-02-02T12:12:52.484+0500</t>
+          <t>2026-03-02T13:47:09.761+0500</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M44" t="n">
         <v>8</v>
@@ -3913,13 +3913,13 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-02-02T12:13:07.099+0500</t>
+          <t>2026-03-02T13:47:12.053+0500</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M45" t="n">
         <v>8</v>
@@ -3992,13 +3992,13 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-02-02T12:13:30.328+0500</t>
+          <t>2026-03-02T13:47:14.632+0500</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M46" t="n">
         <v>8</v>
@@ -4071,13 +4071,13 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-02-02T12:13:44.762+0500</t>
+          <t>2026-03-02T13:47:17.059+0500</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M47" t="n">
         <v>8</v>
@@ -4150,13 +4150,13 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-02-02T12:13:58.512+0500</t>
+          <t>2026-03-02T13:47:19.049+0500</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M48" t="n">
         <v>8</v>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4229,13 +4229,13 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-02-03T12:10:06.577+0500</t>
+          <t>2026-03-02T13:40:02.680+0500</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M49" t="n">
         <v>8</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4308,13 +4308,13 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-02-03T12:10:25.451+0500</t>
+          <t>2026-03-02T13:40:17.949+0500</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M50" t="n">
         <v>8</v>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4387,13 +4387,13 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-02-03T12:10:38.913+0500</t>
+          <t>2026-03-02T13:40:31.852+0500</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M51" t="n">
         <v>8</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4466,13 +4466,13 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-02-03T12:11:49.287+0500</t>
+          <t>2026-03-02T13:40:48.160+0500</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M52" t="n">
         <v>8</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4545,13 +4545,13 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-02-03T12:11:15.157+0500</t>
+          <t>2026-03-02T13:41:07.864+0500</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M53" t="n">
         <v>8</v>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6062,13 +6062,13 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-02-09T19:02:04.073+0500</t>
+          <t>2026-03-02T13:41:27.375+0500</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M72" t="n">
         <v>8</v>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-02-10T11:39:49.172+0500</t>
+          <t>2026-03-02T14:15:28.564+0500</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -7049,13 +7049,13 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-02-18T11:05:49.638+0500</t>
+          <t>2026-03-02T13:49:52.860+0500</t>
         </is>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M85" t="n">
         <v>8</v>
@@ -7349,13 +7349,13 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-02-26T09:21:17.700+0500</t>
+          <t>2026-03-02T13:42:46.034+0500</t>
         </is>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M89" t="n">
         <v>6.5</v>
@@ -12367,13 +12367,13 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-02-09T12:32:00.064+0500</t>
+          <t>2026-03-02T14:17:45.818+0500</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
         <v>8</v>
@@ -12442,13 +12442,13 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-01-29T16:13:17.413+0500</t>
+          <t>2026-03-02T12:44:58.393+0500</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M20" t="n">
         <v>8</v>
@@ -12521,13 +12521,13 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-01-29T16:17:44.255+0500</t>
+          <t>2026-03-02T12:45:03.019+0500</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
         <v>8</v>
@@ -12600,13 +12600,13 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-01-29T16:18:29.071+0500</t>
+          <t>2026-03-02T12:45:09.193+0500</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
         <v>8</v>
@@ -12679,13 +12679,13 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-01-29T16:21:57.948+0500</t>
+          <t>2026-03-02T12:45:13.551+0500</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
         <v>8</v>
@@ -12758,13 +12758,13 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-01-29T16:23:12.972+0500</t>
+          <t>2026-03-02T12:45:28.982+0500</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
         <v>8</v>
@@ -12837,13 +12837,13 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-01-29T16:24:51.116+0500</t>
+          <t>2026-03-02T12:45:31.965+0500</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M25" t="n">
         <v>8</v>
@@ -12916,13 +12916,13 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-01-29T16:25:35.949+0500</t>
+          <t>2026-03-02T12:45:34.794+0500</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
         <v>8</v>
@@ -12995,13 +12995,13 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-01-29T16:25:58.817+0500</t>
+          <t>2026-03-02T12:45:39.947+0500</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
         <v>8</v>
@@ -13074,13 +13074,13 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-01-29T16:26:25.077+0500</t>
+          <t>2026-03-02T12:45:43.917+0500</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M28" t="n">
         <v>8</v>
@@ -13153,13 +13153,13 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-01-29T16:26:43.424+0500</t>
+          <t>2026-03-02T12:45:47.698+0500</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
         <v>8</v>
@@ -13232,13 +13232,13 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-01-29T16:27:02.302+0500</t>
+          <t>2026-03-02T12:45:51.097+0500</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
         <v>8</v>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13311,13 +13311,13 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-02-02T09:47:41.356+0500</t>
+          <t>2026-03-02T14:48:16.498+0500</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
         <v>8</v>
@@ -13465,13 +13465,13 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-01-30T16:56:01.700+0500</t>
+          <t>2026-03-02T14:16:20.211+0500</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -13777,13 +13777,13 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-02-02T09:47:44.398+0500</t>
+          <t>2026-03-02T13:51:49.750+0500</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M37" t="n">
         <v>8</v>
@@ -13856,13 +13856,13 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-02-02T10:38:26.241+0500</t>
+          <t>2026-03-02T13:42:10.695+0500</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M38" t="n">
         <v>8</v>
@@ -13935,13 +13935,13 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-02-02T09:38:30.583+0500</t>
+          <t>2026-03-02T13:51:58.269+0500</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M39" t="n">
         <v>8</v>
@@ -14014,13 +14014,13 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-02-02T09:43:30.522+0500</t>
+          <t>2026-03-02T13:52:05.234+0500</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
         <v>8</v>
@@ -14093,13 +14093,13 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-02-02T09:45:57.436+0500</t>
+          <t>2026-03-02T13:52:11.634+0500</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M41" t="n">
         <v>8</v>
@@ -14251,13 +14251,13 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-02-02T12:11:51.912+0500</t>
+          <t>2026-03-02T14:10:46.759+0500</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M43" t="n">
         <v>8</v>
@@ -14330,13 +14330,13 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-02-02T12:12:52.484+0500</t>
+          <t>2026-03-02T13:47:09.761+0500</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M44" t="n">
         <v>8</v>
@@ -14409,13 +14409,13 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-02-02T12:13:07.099+0500</t>
+          <t>2026-03-02T13:47:12.053+0500</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M45" t="n">
         <v>8</v>
@@ -14488,13 +14488,13 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-02-02T12:13:30.328+0500</t>
+          <t>2026-03-02T13:47:14.632+0500</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M46" t="n">
         <v>8</v>
@@ -14567,13 +14567,13 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-02-02T12:13:44.762+0500</t>
+          <t>2026-03-02T13:47:17.059+0500</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M47" t="n">
         <v>8</v>
@@ -14646,13 +14646,13 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-02-02T12:13:58.512+0500</t>
+          <t>2026-03-02T13:47:19.049+0500</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M48" t="n">
         <v>8</v>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14725,13 +14725,13 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-02-03T12:10:06.577+0500</t>
+          <t>2026-03-02T13:40:02.680+0500</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M49" t="n">
         <v>8</v>
@@ -14779,7 +14779,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -14804,13 +14804,13 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-02-03T12:10:25.451+0500</t>
+          <t>2026-03-02T13:40:17.949+0500</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M50" t="n">
         <v>8</v>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -14883,13 +14883,13 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-02-03T12:10:38.913+0500</t>
+          <t>2026-03-02T13:40:31.852+0500</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M51" t="n">
         <v>8</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -14962,13 +14962,13 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-02-03T12:11:49.287+0500</t>
+          <t>2026-03-02T13:40:48.160+0500</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M52" t="n">
         <v>8</v>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -15041,13 +15041,13 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-02-03T12:11:15.157+0500</t>
+          <t>2026-03-02T13:41:07.864+0500</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M53" t="n">
         <v>8</v>
@@ -27271,7 +27271,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Annual Leave</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -27296,13 +27296,13 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2026-02-09T19:02:04.073+0500</t>
+          <t>2026-03-02T13:41:27.375+0500</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M190" t="n">
         <v>8</v>
@@ -27434,7 +27434,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-02-10T11:39:49.172+0500</t>
+          <t>2026-03-02T14:15:28.564+0500</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -28283,13 +28283,13 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2026-02-18T11:05:49.638+0500</t>
+          <t>2026-03-02T13:49:52.860+0500</t>
         </is>
       </c>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M203" t="n">
         <v>8</v>
@@ -28583,13 +28583,13 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2026-02-26T09:21:17.700+0500</t>
+          <t>2026-03-02T13:42:46.034+0500</t>
         </is>
       </c>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M207" t="n">
         <v>6.5</v>
@@ -38292,7 +38292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38376,14 +38376,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>awais akhter</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -38392,13 +38392,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -38407,29 +38407,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -38438,11 +38438,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
@@ -38457,7 +38457,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -38469,29 +38469,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -38500,11 +38500,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -38519,7 +38519,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -38531,11 +38531,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -38544,13 +38544,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -38562,29 +38562,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -38593,14 +38593,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -38615,7 +38615,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81</v>
+        <v>2.62</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -38624,20 +38624,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -38646,7 +38646,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -38655,14 +38655,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -38677,7 +38677,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -38686,11 +38686,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -38705,7 +38705,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -38717,7 +38717,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -38730,10 +38730,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -38742,99 +38742,6 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Waqar Rasheed</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>48</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Zain Munir</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>88</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>11</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Zeeshan Sarwar</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>11</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38849,7 +38756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38887,19 +38794,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -38911,12 +38818,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -38940,7 +38847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -38959,12 +38866,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -38983,12 +38890,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -39007,12 +38914,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -39036,7 +38943,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -39055,19 +38962,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -39079,12 +38986,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -39108,7 +39015,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -39127,12 +39034,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -39151,12 +39058,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -39175,12 +39082,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -39204,7 +39111,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -39223,12 +39130,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -39247,12 +39154,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -39271,12 +39178,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -39295,12 +39202,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -39319,12 +39226,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -39343,19 +39250,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -39367,12 +39274,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -39396,7 +39303,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -39415,19 +39322,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -39439,12 +39346,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -39463,12 +39370,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -39492,7 +39399,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -39511,60 +39418,60 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -39583,19 +39490,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -39607,25 +39514,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33">
@@ -39636,7 +39543,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -39655,12 +39562,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -39679,12 +39586,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -39703,19 +39610,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -39727,12 +39634,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -39756,7 +39663,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -39775,12 +39682,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -39799,12 +39706,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -39823,19 +39730,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -39852,7 +39759,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -39871,12 +39778,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -39895,19 +39802,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -39924,7 +39831,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -39943,12 +39850,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -39967,19 +39874,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -39991,12 +39898,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -40020,7 +39927,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -40039,19 +39946,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -40063,12 +39970,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -40092,7 +39999,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -40111,19 +40018,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -40135,12 +40042,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -40159,19 +40066,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -40188,7 +40095,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -40207,19 +40114,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -40236,7 +40143,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -40255,19 +40162,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -40284,7 +40191,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -40303,19 +40210,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -40332,7 +40239,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -40351,19 +40258,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -40380,7 +40287,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -40404,7 +40311,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -40428,7 +40335,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -40447,19 +40354,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -40476,7 +40383,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -40500,7 +40407,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -40519,19 +40426,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -40543,19 +40450,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -40567,12 +40474,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -40596,7 +40503,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -40620,7 +40527,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -40644,7 +40551,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -40668,7 +40575,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -40692,7 +40599,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -40711,12 +40618,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Waqar Rasheed</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -40729,1182 +40636,6 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Muhammad Ahmad Saleem</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
-        <v>8</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Waqar Rasheed</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>8</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>8</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Waqar Rasheed</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>8</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>8</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Waqar Rasheed</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>8</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>8</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Waqar Rasheed</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>8</v>
-      </c>
-      <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>8</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Waqar Rasheed</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>8</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Hassan Malik</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>8</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>8</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Faiza Nasir</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="n">
-        <v>8</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>8</v>
-      </c>
-      <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>8</v>
-      </c>
-      <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Hassan Malik</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" t="n">
-        <v>8</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>8</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>8</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>8</v>
-      </c>
-      <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Muhammad Abdullah</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Muhammad Ahmad Saleem</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>8</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>8</v>
-      </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Muhammad Ahmad Saleem</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>8</v>
-      </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>8</v>
-      </c>
-      <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>8</v>
-      </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>8</v>
-      </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>8</v>
-      </c>
-      <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>8</v>
-      </c>
-      <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>8</v>
-      </c>
-      <c r="D110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>8</v>
-      </c>
-      <c r="D111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>8</v>
-      </c>
-      <c r="D112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>8</v>
-      </c>
-      <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>8</v>
-      </c>
-      <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>8</v>
-      </c>
-      <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>8</v>
-      </c>
-      <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>8</v>
-      </c>
-      <c r="D117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>8</v>
-      </c>
-      <c r="D118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>8</v>
-      </c>
-      <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2026-03-20</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>8</v>
-      </c>
-      <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>8</v>
-      </c>
-      <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>8</v>
-      </c>
-      <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>8</v>
-      </c>
-      <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>8</v>
-      </c>
-      <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>8</v>
-      </c>
-      <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>8</v>
-      </c>
-      <c r="D126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>8</v>
-      </c>
-      <c r="D127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" t="n">
         <v>8</v>
       </c>
     </row>
@@ -41919,7 +40650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41957,40 +40688,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-W01</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-W01</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -41999,7 +40730,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -42010,11 +40741,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-W01</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -42023,46 +40754,46 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-W01</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-W01</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -42071,66 +40802,66 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-W02</t>
+          <t>2026-W08</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-W02</t>
+          <t>2026-W08</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-W02</t>
+          <t>2026-W08</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -42149,12 +40880,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-W02</t>
+          <t>2026-W09</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -42173,64 +40904,64 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-W03</t>
+          <t>2026-W09</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>6.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-W03</t>
+          <t>2026-W09</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-W03</t>
+          <t>2026-W10</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -42239,7 +40970,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -42250,7 +40981,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-W03</t>
+          <t>2026-W11</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -42269,16 +41000,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-W03</t>
+          <t>2026-W12</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -42287,42 +41018,42 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-W03</t>
+          <t>2026-W13</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-W03</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -42341,25 +41072,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-W04</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -42370,7 +41101,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-W04</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -42389,40 +41120,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-W04</t>
+          <t>2026-W17</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zain Munir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-W04</t>
+          <t>2026-W18</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -42431,487 +41162,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>awais akhter</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-W05</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" t="n">
-        <v>16</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-W05</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>40</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Muhammad Abdullah</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-W05</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Muhammad Imran Aslam</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-W05</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-W06</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>40</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Waqar Rasheed</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-W06</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-W07</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>40</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Muhammad Ahmad Saleem</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-W07</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Waqar Rasheed</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-W07</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>40</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Faiza Nasir</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-W08</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>8</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Hassan Malik</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-W08</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>8</v>
-      </c>
-      <c r="D32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-W08</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>40</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-W09</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>40</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Muhammad Abdullah</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-W09</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Muhammad Ahmad Saleem</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-W09</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>13</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-W10</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>40</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-W11</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>40</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-W12</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>40</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-W13</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>40</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-W14</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>16</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -42925,7 +41176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42963,408 +41214,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>16</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>176</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Muhammad Usman Javed</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>56</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Zain Munir</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>88</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Faiza Nasir</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Hassan Malik</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Muhammad Abdullah</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Muhammad Ahmad Saleem</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>21</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Waqar Rasheed</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>48</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>176</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
         <v>176</v>
       </c>
     </row>
@@ -43469,7 +41504,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RLT-179</t>
+          <t>RLT-182</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -43479,22 +41514,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Leave - Febuary 9, 2026</t>
+          <t>Leave for one day 07-01-26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No Entry for planned date and/or original estimate</t>
+          <t>Unknown leave classification</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -43511,7 +41546,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RLT-182</t>
+          <t>RLT-190</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -43521,7 +41556,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Leave for one day 07-01-26</t>
+          <t>Leave for one day 13-02-26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -43553,32 +41588,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RLT-190</t>
+          <t>RLT-59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leave for one day 13-02-26</t>
+          <t>Planned Leave 8th Nov 2024</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unknown leave classification</t>
+          <t>No Entry for planned date and/or original estimate</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -43595,22 +41630,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RLT-59</t>
+          <t>RLT-161</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Planned Leave 8th Nov 2024</t>
+          <t>16 Dec 2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -43637,17 +41672,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RLT-161</t>
+          <t>RLT-102</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16 Dec 2025</t>
+          <t>Annual leave 23 December</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -43679,7 +41714,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RLT-102</t>
+          <t>RLT-103</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -43689,7 +41724,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annual leave 23 December</t>
+          <t>Annual leave 24 December</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -43721,7 +41756,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RLT-103</t>
+          <t>RLT-104</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -43731,7 +41766,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annual leave 24 December</t>
+          <t>Annual leave 26 December</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -43763,7 +41798,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RLT-104</t>
+          <t>RLT-105</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -43773,7 +41808,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annual leave 26 December</t>
+          <t>Annual leave 29 December</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -43805,7 +41840,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RLT-105</t>
+          <t>RLT-106</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -43815,7 +41850,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Annual leave 29 December</t>
+          <t>Annual leave 30 December</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -43847,7 +41882,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RLT-106</t>
+          <t>RLT-107</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -43857,7 +41892,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annual leave 30 December</t>
+          <t>Annual leave 31 December</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -43889,7 +41924,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RLT-107</t>
+          <t>RLT-84</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -43899,12 +41934,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Annual leave 31 December</t>
+          <t>Casual leave</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -43931,22 +41966,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RLT-84</t>
+          <t>RLT-175</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Casual leave</t>
+          <t>Planned Leave 2nd March 2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -43964,16 +41999,14 @@
           <t>No Entry</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>No Entry</t>
-        </is>
+      <c r="H14" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RLT-175</t>
+          <t>RLT-176</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -43983,7 +42016,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Planned Leave 2nd March 2026</t>
+          <t>Planned Leave 1st April 2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -44007,28 +42040,28 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RLT-176</t>
+          <t>RLT-135</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Planned Leave 1st April 2026</t>
+          <t>Leave - December 26, 2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -44046,14 +42079,16 @@
           <t>No Entry</t>
         </is>
       </c>
-      <c r="H16" t="n">
-        <v>8</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>No Entry</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RLT-135</t>
+          <t>RLT-179</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -44063,12 +42098,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Leave - December 26, 2025</t>
+          <t>Leave - Febuary 9, 2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">

--- a/rlt_leave_report.xlsx
+++ b/rlt_leave_report.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S141"/>
+  <dimension ref="A1:S142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-02-12T11:45:41.736+0500</t>
+          <t>2026-03-05T11:18:36.551+0500</t>
         </is>
       </c>
       <c r="J83" t="inlineStr"/>
@@ -6908,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
@@ -7838,53 +7838,53 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RLT-43</t>
+          <t>RLT-202</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>39198</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Planned Leave 15th May 2024</t>
+          <t>Sick Leave- 4th March 2026</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-40</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Syed Yousaf Qadri</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2024-05-15T13:17:36.997+0500</t>
+          <t>2026-03-05T12:40:13.046+0500</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:48.485+0500</t>
+          <t>2026-03-05T12:42:07.496+0500</t>
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M96" t="n">
         <v>8</v>
@@ -7892,7 +7892,7 @@
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7913,47 +7913,47 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RLT-44</t>
+          <t>RLT-43</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Leaves Faiza</t>
+          <t>Planned Leave 15th May 2024</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2024-05-27T17:19:47.991+0500</t>
+          <t>2024-05-15T13:17:36.997+0500</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2025-12-30T10:15:12.915+0500</t>
+          <t>2024-08-16T16:28:48.485+0500</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
@@ -7962,21 +7962,21 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -7988,47 +7988,47 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RLT-45</t>
+          <t>RLT-44</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Leave for one day 05-06-24</t>
+          <t>Leaves Faiza</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2024-06-06T09:10:07.974+0500</t>
+          <t>2024-05-27T17:19:47.991+0500</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2024-06-06T09:11:39.142+0500</t>
+          <t>2025-12-30T10:15:12.915+0500</t>
         </is>
       </c>
       <c r="J98" t="inlineStr"/>
@@ -8037,21 +8037,21 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -8063,47 +8063,47 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RLT-46</t>
+          <t>RLT-45</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Planned Leave 20th June 2024</t>
+          <t>Leave for one day 05-06-24</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2024-06-21T09:20:21.600+0500</t>
+          <t>2024-06-06T09:10:07.974+0500</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:56.168+0500</t>
+          <t>2024-06-06T09:11:39.142+0500</t>
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
@@ -8117,7 +8117,7 @@
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -8138,47 +8138,47 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RLT-47</t>
+          <t>RLT-46</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Leave for two days 20 and 21-06-24</t>
+          <t>Planned Leave 20th June 2024</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2024-06-24T09:18:18.735+0500</t>
+          <t>2024-06-21T09:20:21.600+0500</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2024-06-24T09:19:43.343+0500</t>
+          <t>2024-08-16T16:28:56.168+0500</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
@@ -8187,21 +8187,21 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -8213,47 +8213,47 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RLT-48</t>
+          <t>RLT-47</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half day leave</t>
+          <t>Leave for two days 20 and 21-06-24</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Half Day Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2024-06-27T19:06:21.094+0500</t>
+          <t>2024-06-24T09:18:18.735+0500</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2024-06-27T19:06:47.198+0500</t>
+          <t>2024-06-24T09:19:43.343+0500</t>
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
@@ -8262,7 +8262,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
@@ -8271,12 +8271,12 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -8288,47 +8288,47 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RLT-49</t>
+          <t>RLT-48</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Emergency leave</t>
+          <t>Half day leave</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Half Day Leave</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2024-07-18T11:05:11.868+0500</t>
+          <t>2024-06-27T19:06:21.094+0500</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-01-29T16:48:09.549+0500</t>
+          <t>2024-06-27T19:06:47.198+0500</t>
         </is>
       </c>
       <c r="J102" t="inlineStr"/>
@@ -8337,21 +8337,21 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -8363,47 +8363,47 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RLT-50</t>
+          <t>RLT-49</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sick leave for one day 22-07-24</t>
+          <t>Emergency leave</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2024-07-23T09:08:09.289+0500</t>
+          <t>2024-07-18T11:05:11.868+0500</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2024-07-23T09:09:17.479+0500</t>
+          <t>2026-01-29T16:48:09.549+0500</t>
         </is>
       </c>
       <c r="J103" t="inlineStr"/>
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
@@ -8421,12 +8421,12 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -8438,47 +8438,47 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RLT-51</t>
+          <t>RLT-50</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Full Day Sick Leave</t>
+          <t>Sick leave for one day 22-07-24</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2024-07-23T12:27:33.881+0500</t>
+          <t>2024-07-23T09:08:09.289+0500</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2024-10-03T16:40:27.519+0500</t>
+          <t>2024-07-23T09:09:17.479+0500</t>
         </is>
       </c>
       <c r="J104" t="inlineStr"/>
@@ -8487,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
@@ -8496,12 +8496,12 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -8513,47 +8513,47 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RLT-52</t>
+          <t>RLT-51</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Urgent work leave 05-08-24</t>
+          <t>Full Day Sick Leave</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2024-08-06T09:08:48.315+0500</t>
+          <t>2024-07-23T12:27:33.881+0500</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2024-08-06T09:11:15.823+0500</t>
+          <t>2024-10-03T16:40:27.519+0500</t>
         </is>
       </c>
       <c r="J105" t="inlineStr"/>
@@ -8562,21 +8562,21 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -8588,47 +8588,47 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RLT-53</t>
+          <t>RLT-52</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2024</t>
+          <t>Urgent work leave 05-08-24</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:43.991+0500</t>
+          <t>2024-08-06T09:08:48.315+0500</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2024-08-16T16:29:17.981+0500</t>
+          <t>2024-08-06T09:11:15.823+0500</t>
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
@@ -8642,7 +8642,7 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8663,47 +8663,47 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RLT-54</t>
+          <t>RLT-53</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Leave for one day 30-08-24</t>
+          <t>Planned Leave 15th Aug 2024</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:09.454+0500</t>
+          <t>2024-08-16T16:28:43.991+0500</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2024-09-03T09:15:53.284+0500</t>
+          <t>2024-08-16T16:29:17.981+0500</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -8717,7 +8717,7 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8738,17 +8738,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RLT-55</t>
+          <t>RLT-54</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Leave for one day 02-09-24</t>
+          <t>Leave for one day 30-08-24</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:29.824+0500</t>
+          <t>2024-08-28T16:51:09.454+0500</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2024-09-03T09:16:12.471+0500</t>
+          <t>2024-09-03T09:15:53.284+0500</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -8813,47 +8813,47 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RLT-56</t>
+          <t>RLT-55</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sick leave 28th Aug 2024</t>
+          <t>Leave for one day 02-09-24</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2024-09-03T10:03:57.925+0500</t>
+          <t>2024-08-28T16:51:29.824+0500</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2024-09-03T10:04:14.562+0500</t>
+          <t>2024-09-03T09:16:12.471+0500</t>
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
@@ -8867,7 +8867,7 @@
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8888,17 +8888,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RLT-57</t>
+          <t>RLT-56</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sick Leave 13th Sept 2024</t>
+          <t>Sick leave 28th Aug 2024</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2024-09-23T11:07:49.200+0500</t>
+          <t>2024-09-03T10:03:57.925+0500</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2024-09-23T11:08:09.638+0500</t>
+          <t>2024-09-03T10:04:14.562+0500</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -8963,47 +8963,47 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RLT-58</t>
+          <t>RLT-57</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Leave for one day 14-11-24</t>
+          <t>Sick Leave 13th Sept 2024</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2024-11-15T09:25:05.670+0500</t>
+          <t>2024-09-23T11:07:49.200+0500</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2024-11-15T09:38:06.205+0500</t>
+          <t>2024-09-23T11:08:09.638+0500</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -9017,7 +9017,7 @@
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -9038,47 +9038,47 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RLT-59</t>
+          <t>RLT-58</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Planned Leave 8th Nov 2024</t>
+          <t>Leave for one day 14-11-24</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-11-21T12:24:36.990+0500</t>
+          <t>2024-11-15T09:25:05.670+0500</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:57.134+0500</t>
+          <t>2024-11-15T09:38:06.205+0500</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -9087,16 +9087,16 @@
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
@@ -9106,24 +9106,24 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RLT-60</t>
+          <t>RLT-59</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Planned Leave 19th Nov 2024</t>
+          <t>Planned Leave 8th Nov 2024</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2024-11-21T12:25:03.206+0500</t>
+          <t>2024-11-21T12:24:36.990+0500</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:07.591+0500</t>
+          <t>2024-12-31T11:38:57.134+0500</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -9162,7 +9162,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
@@ -9181,54 +9181,54 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RLT-62</t>
+          <t>RLT-60</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sick leave for one day 30-12-24</t>
+          <t>Planned Leave 19th Nov 2024</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:13.907+0500</t>
+          <t>2024-11-21T12:25:03.206+0500</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:33.151+0500</t>
+          <t>2024-12-31T11:39:07.591+0500</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -9242,7 +9242,7 @@
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -9263,47 +9263,47 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RLT-63</t>
+          <t>RLT-62</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Planned Leave 29th Nov 2024</t>
+          <t>Sick leave for one day 30-12-24</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:18.228+0500</t>
+          <t>2024-12-31T09:30:13.907+0500</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:11.165+0500</t>
+          <t>2024-12-31T09:30:33.151+0500</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -9317,7 +9317,7 @@
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9338,17 +9338,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RLT-64</t>
+          <t>RLT-63</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Planned Leave 16th Dec 2024</t>
+          <t>Planned Leave 29th Nov 2024</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:25.533+0500</t>
+          <t>2024-12-31T11:38:18.228+0500</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:27.662+0500</t>
+          <t>2024-12-31T11:39:11.165+0500</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -9413,17 +9413,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RLT-65</t>
+          <t>RLT-64</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
+          <t>Planned Leave 16th Dec 2024</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-12-31T11:40:34.525+0500</t>
+          <t>2024-12-31T11:39:25.533+0500</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:36.616+0500</t>
+          <t>2025-03-25T09:09:27.662+0500</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -9462,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
@@ -9471,12 +9471,12 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -9488,47 +9488,47 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RLT-67</t>
+          <t>RLT-65</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Casual Leave for half day 02-01-25</t>
+          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2025-01-06T09:19:42.013+0500</t>
+          <t>2024-12-31T11:40:34.525+0500</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:11.598+0500</t>
+          <t>2025-03-25T09:09:36.616+0500</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
@@ -9546,12 +9546,12 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -9563,17 +9563,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RLT-68</t>
+          <t>RLT-67</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Leave for one day 03-01-25</t>
+          <t>Casual Leave for half day 02-01-25</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9598,12 +9598,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2025-01-06T09:20:06.483+0500</t>
+          <t>2025-01-06T09:19:42.013+0500</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:08.280+0500</t>
+          <t>2025-01-06T09:21:11.598+0500</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -9612,16 +9612,16 @@
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
@@ -9638,47 +9638,47 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RLT-70</t>
+          <t>RLT-68</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Medical Leaves</t>
+          <t>Leave for one day 03-01-25</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2025-02-27T12:06:39.343+0500</t>
+          <t>2025-01-06T09:20:06.483+0500</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2025-02-27T12:07:35.090+0500</t>
+          <t>2025-01-06T09:21:08.280+0500</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -9687,21 +9687,21 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -9713,47 +9713,47 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RLT-71</t>
+          <t>RLT-70</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Leave for one day 27-02-25</t>
+          <t>Medical Leaves</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:26.122+0500</t>
+          <t>2025-02-27T12:06:39.343+0500</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:46.578+0500</t>
+          <t>2025-02-27T12:07:35.090+0500</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -9762,21 +9762,21 @@
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P121" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -9788,17 +9788,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RLT-72</t>
+          <t>RLT-71</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Annual leave 31 Jan</t>
+          <t>Leave for one day 27-02-25</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9808,27 +9808,27 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:16.894+0500</t>
+          <t>2025-02-28T09:31:26.122+0500</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:47.087+0500</t>
+          <t>2025-02-28T09:31:46.578+0500</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -9842,7 +9842,7 @@
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9863,47 +9863,47 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RLT-74</t>
+          <t>RLT-72</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Planned Leave 21st Feb 2025</t>
+          <t>Annual leave 31 Jan</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:51.777+0500</t>
+          <t>2025-03-04T11:51:16.894+0500</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:06.523+0500</t>
+          <t>2025-03-04T11:51:47.087+0500</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -9938,17 +9938,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RLT-77</t>
+          <t>RLT-74</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Planned Leave 3rd April 2025</t>
+          <t>Planned Leave 21st Feb 2025</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2025-04-29T14:35:54.729+0500</t>
+          <t>2025-03-25T09:09:51.777+0500</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:21.782+0500</t>
+          <t>2025-04-29T14:36:06.523+0500</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -10013,17 +10013,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RLT-78</t>
+          <t>RLT-77</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Planned Leave 4th April 2025</t>
+          <t>Planned Leave 3rd April 2025</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:42.933+0500</t>
+          <t>2025-04-29T14:35:54.729+0500</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2025-04-29T14:37:01.596+0500</t>
+          <t>2025-04-29T14:36:21.782+0500</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -10088,47 +10088,47 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RLT-79</t>
+          <t>RLT-78</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sick leave</t>
+          <t>Planned Leave 4th April 2025</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2025-05-15T10:52:44.037+0500</t>
+          <t>2025-04-29T14:36:42.933+0500</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:11.410+0500</t>
+          <t>2025-04-29T14:37:01.596+0500</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -10142,7 +10142,7 @@
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -10163,47 +10163,47 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RLT-80</t>
+          <t>RLT-79</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>16 may 2025</t>
+          <t>Sick leave</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>RLT-5</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:34.680+0500</t>
+          <t>2025-05-15T10:52:44.037+0500</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:58.959+0500</t>
+          <t>2025-09-11T09:15:11.410+0500</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -10238,47 +10238,47 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RLT-81</t>
+          <t>RLT-80</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Annual leave 22 May</t>
+          <t>16 may 2025</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-5</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2025-05-21T17:45:49.062+0500</t>
+          <t>2025-05-20T15:48:34.680+0500</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:14.892+0500</t>
+          <t>2025-05-20T15:48:58.959+0500</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -10292,7 +10292,7 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -10313,47 +10313,47 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RLT-82</t>
+          <t>RLT-81</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Planned Leave 5th June 2025</t>
+          <t>Annual leave 22 May</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2025-06-10T11:05:56.983+0500</t>
+          <t>2025-05-21T17:45:49.062+0500</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:20.879+0500</t>
+          <t>2025-09-11T09:15:14.892+0500</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -10388,47 +10388,47 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RLT-83</t>
+          <t>RLT-82</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Annual leave 07 July</t>
+          <t>Planned Leave 5th June 2025</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2025-07-07T12:00:55.557+0500</t>
+          <t>2025-06-10T11:05:56.983+0500</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:19.601+0500</t>
+          <t>2025-09-26T09:55:20.879+0500</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -10463,17 +10463,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RLT-84</t>
+          <t>RLT-83</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Casual leave</t>
+          <t>Annual leave 07 July</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10498,12 +10498,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2025-09-11T09:14:17.734+0500</t>
+          <t>2025-07-07T12:00:55.557+0500</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:22.445+0500</t>
+          <t>2025-09-11T09:15:19.601+0500</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -10512,7 +10512,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
@@ -10521,7 +10521,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
@@ -10531,24 +10531,24 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RLT-85</t>
+          <t>RLT-84</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Casual leave 10 sept 25</t>
+          <t>Casual leave</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:09.033+0500</t>
+          <t>2025-09-11T09:14:17.734+0500</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:45.168+0500</t>
+          <t>2025-09-11T09:15:22.445+0500</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -10587,7 +10587,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
@@ -10606,54 +10606,54 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RLT-86</t>
+          <t>RLT-85</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Planned Leave 15th July 2025</t>
+          <t>Casual leave 10 sept 25</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:06.810+0500</t>
+          <t>2025-09-11T09:16:09.033+0500</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:30.527+0500</t>
+          <t>2025-09-11T09:16:45.168+0500</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -10667,7 +10667,7 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10688,17 +10688,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RLT-87</t>
+          <t>RLT-86</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Planned 1st Sept 2025</t>
+          <t>Planned Leave 15th July 2025</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10723,12 +10723,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2025-09-26T09:56:28.622+0500</t>
+          <t>2025-09-26T09:55:06.810+0500</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:11.707+0500</t>
+          <t>2025-09-26T09:55:30.527+0500</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -10763,17 +10763,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RLT-88</t>
+          <t>RLT-87</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2025</t>
+          <t>Planned 1st Sept 2025</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:27.334+0500</t>
+          <t>2025-09-26T09:56:28.622+0500</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:46.408+0500</t>
+          <t>2025-09-26T10:05:11.707+0500</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -10838,22 +10838,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RLT-89</t>
+          <t>RLT-88</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
+          <t>Planned Leave 15th Aug 2025</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-10-08T10:16:40.435+0500</t>
+          <t>2025-09-26T10:05:27.334+0500</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2025-11-06T09:37:59.818+0500</t>
+          <t>2025-09-26T10:05:46.408+0500</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
@@ -10887,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
@@ -10896,12 +10896,12 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -10913,22 +10913,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RLT-90</t>
+          <t>RLT-89</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Planned Leave 5th Nov 2025</t>
+          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-11-06T09:38:11.154+0500</t>
+          <t>2025-10-08T10:16:40.435+0500</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:11.084+0500</t>
+          <t>2025-11-06T09:37:59.818+0500</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -10962,21 +10962,21 @@
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -10988,22 +10988,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RLT-95</t>
+          <t>RLT-90</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>31542</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sick Leave 18th Nov 2025</t>
+          <t>Planned Leave 5th Nov 2025</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:01.035+0500</t>
+          <t>2025-11-06T09:38:11.154+0500</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:30.413+0500</t>
+          <t>2025-12-08T11:30:11.084+0500</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -11042,7 +11042,7 @@
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -11063,22 +11063,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RLT-96</t>
+          <t>RLT-95</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
+          <t>Sick Leave 18th Nov 2025</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:53.468+0500</t>
+          <t>2025-12-08T11:30:01.035+0500</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:21.845+0500</t>
+          <t>2025-12-08T11:30:30.413+0500</t>
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
@@ -11112,7 +11112,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
@@ -11121,12 +11121,12 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -11138,22 +11138,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RLT-97</t>
+          <t>RLT-96</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>3rd Dec 2025</t>
+          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.693+0500</t>
+          <t>2025-12-08T11:30:53.468+0500</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2025-12-08T11:32:24.681+0500</t>
+          <t>2025-12-08T11:31:21.845+0500</t>
         </is>
       </c>
       <c r="J140" t="inlineStr"/>
@@ -11187,21 +11187,21 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -11213,47 +11213,47 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RLT-99</t>
+          <t>RLT-97</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Leave for one day 05-12-25</t>
+          <t>3rd Dec 2025</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2025-12-29T12:28:16.268+0500</t>
+          <t>2025-12-08T11:31:59.693+0500</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2025-12-29T12:29:46.783+0500</t>
+          <t>2025-12-08T11:32:24.681+0500</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
@@ -11267,7 +11267,7 @@
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -11280,6 +11280,81 @@
         </is>
       </c>
       <c r="S141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>RLT-99</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>32431</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Leave for one day 05-12-25</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Resolved!</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>RLT-35</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:28:16.268+0500</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:29:46.783+0500</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>8</v>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11296,7 +11371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S259"/>
+  <dimension ref="A1:S260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28512,7 +28587,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>2026-02-12T11:45:41.736+0500</t>
+          <t>2026-03-05T11:18:36.551+0500</t>
         </is>
       </c>
       <c r="J201" t="inlineStr"/>
@@ -28521,7 +28596,7 @@
         <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
@@ -28530,7 +28605,7 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr">
@@ -29451,53 +29526,53 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>RLT-43</t>
+          <t>RLT-202</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>39198</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Planned Leave 15th May 2024</t>
+          <t>Sick Leave- 4th March 2026</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-40</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Syed Yousaf Qadri</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2024-05-15T13:17:36.997+0500</t>
+          <t>2026-03-05T12:40:13.046+0500</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:48.485+0500</t>
+          <t>2026-03-05T12:42:07.496+0500</t>
         </is>
       </c>
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M214" t="n">
         <v>8</v>
@@ -29505,7 +29580,7 @@
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -29526,47 +29601,47 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>RLT-44</t>
+          <t>RLT-43</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Leaves Faiza</t>
+          <t>Planned Leave 15th May 2024</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2024-05-27T17:19:47.991+0500</t>
+          <t>2024-05-15T13:17:36.997+0500</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2025-12-30T10:15:12.915+0500</t>
+          <t>2024-08-16T16:28:48.485+0500</t>
         </is>
       </c>
       <c r="J215" t="inlineStr"/>
@@ -29575,21 +29650,21 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P215" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
@@ -29601,47 +29676,47 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>RLT-45</t>
+          <t>RLT-44</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Leave for one day 05-06-24</t>
+          <t>Leaves Faiza</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2024-06-06T09:10:07.974+0500</t>
+          <t>2024-05-27T17:19:47.991+0500</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2024-06-06T09:11:39.142+0500</t>
+          <t>2025-12-30T10:15:12.915+0500</t>
         </is>
       </c>
       <c r="J216" t="inlineStr"/>
@@ -29650,21 +29725,21 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P216" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -29676,47 +29751,47 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>RLT-46</t>
+          <t>RLT-45</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Planned Leave 20th June 2024</t>
+          <t>Leave for one day 05-06-24</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2024-06-21T09:20:21.600+0500</t>
+          <t>2024-06-06T09:10:07.974+0500</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:56.168+0500</t>
+          <t>2024-06-06T09:11:39.142+0500</t>
         </is>
       </c>
       <c r="J217" t="inlineStr"/>
@@ -29730,7 +29805,7 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -29751,47 +29826,47 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>RLT-47</t>
+          <t>RLT-46</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Leave for two days 20 and 21-06-24</t>
+          <t>Planned Leave 20th June 2024</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2024-06-24T09:18:18.735+0500</t>
+          <t>2024-06-21T09:20:21.600+0500</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2024-06-24T09:19:43.343+0500</t>
+          <t>2024-08-16T16:28:56.168+0500</t>
         </is>
       </c>
       <c r="J218" t="inlineStr"/>
@@ -29800,21 +29875,21 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P218" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
@@ -29826,47 +29901,47 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>RLT-48</t>
+          <t>RLT-47</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Half day leave</t>
+          <t>Leave for two days 20 and 21-06-24</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Half Day Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2024-06-27T19:06:21.094+0500</t>
+          <t>2024-06-24T09:18:18.735+0500</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2024-06-27T19:06:47.198+0500</t>
+          <t>2024-06-24T09:19:43.343+0500</t>
         </is>
       </c>
       <c r="J219" t="inlineStr"/>
@@ -29875,7 +29950,7 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
@@ -29884,12 +29959,12 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
@@ -29901,47 +29976,47 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>RLT-49</t>
+          <t>RLT-48</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Emergency leave</t>
+          <t>Half day leave</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Half Day Leave</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2024-07-18T11:05:11.868+0500</t>
+          <t>2024-06-27T19:06:21.094+0500</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2026-01-29T16:48:09.549+0500</t>
+          <t>2024-06-27T19:06:47.198+0500</t>
         </is>
       </c>
       <c r="J220" t="inlineStr"/>
@@ -29950,21 +30025,21 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P220" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S220" t="inlineStr">
@@ -29976,47 +30051,47 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>RLT-50</t>
+          <t>RLT-49</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Sick leave for one day 22-07-24</t>
+          <t>Emergency leave</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2024-07-23T09:08:09.289+0500</t>
+          <t>2024-07-18T11:05:11.868+0500</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2024-07-23T09:09:17.479+0500</t>
+          <t>2026-01-29T16:48:09.549+0500</t>
         </is>
       </c>
       <c r="J221" t="inlineStr"/>
@@ -30025,7 +30100,7 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr">
@@ -30034,12 +30109,12 @@
         </is>
       </c>
       <c r="P221" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S221" t="inlineStr">
@@ -30051,47 +30126,47 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>RLT-51</t>
+          <t>RLT-50</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Full Day Sick Leave</t>
+          <t>Sick leave for one day 22-07-24</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2024-07-23T12:27:33.881+0500</t>
+          <t>2024-07-23T09:08:09.289+0500</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2024-10-03T16:40:27.519+0500</t>
+          <t>2024-07-23T09:09:17.479+0500</t>
         </is>
       </c>
       <c r="J222" t="inlineStr"/>
@@ -30100,7 +30175,7 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
@@ -30109,12 +30184,12 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S222" t="inlineStr">
@@ -30126,47 +30201,47 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>RLT-52</t>
+          <t>RLT-51</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Urgent work leave 05-08-24</t>
+          <t>Full Day Sick Leave</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2024-08-06T09:08:48.315+0500</t>
+          <t>2024-07-23T12:27:33.881+0500</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2024-08-06T09:11:15.823+0500</t>
+          <t>2024-10-03T16:40:27.519+0500</t>
         </is>
       </c>
       <c r="J223" t="inlineStr"/>
@@ -30175,21 +30250,21 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P223" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S223" t="inlineStr">
@@ -30201,47 +30276,47 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>RLT-53</t>
+          <t>RLT-52</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2024</t>
+          <t>Urgent work leave 05-08-24</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:43.991+0500</t>
+          <t>2024-08-06T09:08:48.315+0500</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2024-08-16T16:29:17.981+0500</t>
+          <t>2024-08-06T09:11:15.823+0500</t>
         </is>
       </c>
       <c r="J224" t="inlineStr"/>
@@ -30255,7 +30330,7 @@
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -30276,47 +30351,47 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>RLT-54</t>
+          <t>RLT-53</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Leave for one day 30-08-24</t>
+          <t>Planned Leave 15th Aug 2024</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:09.454+0500</t>
+          <t>2024-08-16T16:28:43.991+0500</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2024-09-03T09:15:53.284+0500</t>
+          <t>2024-08-16T16:29:17.981+0500</t>
         </is>
       </c>
       <c r="J225" t="inlineStr"/>
@@ -30330,7 +30405,7 @@
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -30351,17 +30426,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>RLT-55</t>
+          <t>RLT-54</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Leave for one day 02-09-24</t>
+          <t>Leave for one day 30-08-24</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30386,12 +30461,12 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:29.824+0500</t>
+          <t>2024-08-28T16:51:09.454+0500</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2024-09-03T09:16:12.471+0500</t>
+          <t>2024-09-03T09:15:53.284+0500</t>
         </is>
       </c>
       <c r="J226" t="inlineStr"/>
@@ -30426,47 +30501,47 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>RLT-56</t>
+          <t>RLT-55</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Sick leave 28th Aug 2024</t>
+          <t>Leave for one day 02-09-24</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2024-09-03T10:03:57.925+0500</t>
+          <t>2024-08-28T16:51:29.824+0500</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2024-09-03T10:04:14.562+0500</t>
+          <t>2024-09-03T09:16:12.471+0500</t>
         </is>
       </c>
       <c r="J227" t="inlineStr"/>
@@ -30480,7 +30555,7 @@
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -30501,17 +30576,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RLT-57</t>
+          <t>RLT-56</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Sick Leave 13th Sept 2024</t>
+          <t>Sick leave 28th Aug 2024</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -30536,12 +30611,12 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2024-09-23T11:07:49.200+0500</t>
+          <t>2024-09-03T10:03:57.925+0500</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2024-09-23T11:08:09.638+0500</t>
+          <t>2024-09-03T10:04:14.562+0500</t>
         </is>
       </c>
       <c r="J228" t="inlineStr"/>
@@ -30576,47 +30651,47 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RLT-58</t>
+          <t>RLT-57</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Leave for one day 14-11-24</t>
+          <t>Sick Leave 13th Sept 2024</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2024-11-15T09:25:05.670+0500</t>
+          <t>2024-09-23T11:07:49.200+0500</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2024-11-15T09:38:06.205+0500</t>
+          <t>2024-09-23T11:08:09.638+0500</t>
         </is>
       </c>
       <c r="J229" t="inlineStr"/>
@@ -30630,7 +30705,7 @@
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -30651,47 +30726,47 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RLT-59</t>
+          <t>RLT-58</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Planned Leave 8th Nov 2024</t>
+          <t>Leave for one day 14-11-24</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2024-11-21T12:24:36.990+0500</t>
+          <t>2024-11-15T09:25:05.670+0500</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:57.134+0500</t>
+          <t>2024-11-15T09:38:06.205+0500</t>
         </is>
       </c>
       <c r="J230" t="inlineStr"/>
@@ -30700,16 +30775,16 @@
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P230" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr">
@@ -30719,24 +30794,24 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RLT-60</t>
+          <t>RLT-59</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Planned Leave 19th Nov 2024</t>
+          <t>Planned Leave 8th Nov 2024</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30761,12 +30836,12 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2024-11-21T12:25:03.206+0500</t>
+          <t>2024-11-21T12:24:36.990+0500</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:07.591+0500</t>
+          <t>2024-12-31T11:38:57.134+0500</t>
         </is>
       </c>
       <c r="J231" t="inlineStr"/>
@@ -30775,7 +30850,7 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
@@ -30784,7 +30859,7 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr">
@@ -30794,54 +30869,54 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RLT-62</t>
+          <t>RLT-60</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Sick leave for one day 30-12-24</t>
+          <t>Planned Leave 19th Nov 2024</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:13.907+0500</t>
+          <t>2024-11-21T12:25:03.206+0500</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:33.151+0500</t>
+          <t>2024-12-31T11:39:07.591+0500</t>
         </is>
       </c>
       <c r="J232" t="inlineStr"/>
@@ -30855,7 +30930,7 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -30876,47 +30951,47 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>RLT-63</t>
+          <t>RLT-62</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Planned Leave 29th Nov 2024</t>
+          <t>Sick leave for one day 30-12-24</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:18.228+0500</t>
+          <t>2024-12-31T09:30:13.907+0500</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:11.165+0500</t>
+          <t>2024-12-31T09:30:33.151+0500</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
@@ -30930,7 +31005,7 @@
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -30951,17 +31026,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RLT-64</t>
+          <t>RLT-63</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Planned Leave 16th Dec 2024</t>
+          <t>Planned Leave 29th Nov 2024</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30986,12 +31061,12 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:25.533+0500</t>
+          <t>2024-12-31T11:38:18.228+0500</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:27.662+0500</t>
+          <t>2024-12-31T11:39:11.165+0500</t>
         </is>
       </c>
       <c r="J234" t="inlineStr"/>
@@ -31026,17 +31101,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>RLT-65</t>
+          <t>RLT-64</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
+          <t>Planned Leave 16th Dec 2024</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -31061,12 +31136,12 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2024-12-31T11:40:34.525+0500</t>
+          <t>2024-12-31T11:39:25.533+0500</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:36.616+0500</t>
+          <t>2025-03-25T09:09:27.662+0500</t>
         </is>
       </c>
       <c r="J235" t="inlineStr"/>
@@ -31075,7 +31150,7 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
@@ -31084,12 +31159,12 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
@@ -31101,47 +31176,47 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RLT-67</t>
+          <t>RLT-65</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Casual Leave for half day 02-01-25</t>
+          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2025-01-06T09:19:42.013+0500</t>
+          <t>2024-12-31T11:40:34.525+0500</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:11.598+0500</t>
+          <t>2025-03-25T09:09:36.616+0500</t>
         </is>
       </c>
       <c r="J236" t="inlineStr"/>
@@ -31150,7 +31225,7 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr">
@@ -31159,12 +31234,12 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -31176,17 +31251,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RLT-68</t>
+          <t>RLT-67</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Leave for one day 03-01-25</t>
+          <t>Casual Leave for half day 02-01-25</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -31211,12 +31286,12 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2025-01-06T09:20:06.483+0500</t>
+          <t>2025-01-06T09:19:42.013+0500</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:08.280+0500</t>
+          <t>2025-01-06T09:21:11.598+0500</t>
         </is>
       </c>
       <c r="J237" t="inlineStr"/>
@@ -31225,16 +31300,16 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr">
@@ -31251,47 +31326,47 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>RLT-70</t>
+          <t>RLT-68</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Medical Leaves</t>
+          <t>Leave for one day 03-01-25</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2025-02-27T12:06:39.343+0500</t>
+          <t>2025-01-06T09:20:06.483+0500</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2025-02-27T12:07:35.090+0500</t>
+          <t>2025-01-06T09:21:08.280+0500</t>
         </is>
       </c>
       <c r="J238" t="inlineStr"/>
@@ -31300,21 +31375,21 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
@@ -31326,47 +31401,47 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>RLT-71</t>
+          <t>RLT-70</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Leave for one day 27-02-25</t>
+          <t>Medical Leaves</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:26.122+0500</t>
+          <t>2025-02-27T12:06:39.343+0500</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:46.578+0500</t>
+          <t>2025-02-27T12:07:35.090+0500</t>
         </is>
       </c>
       <c r="J239" t="inlineStr"/>
@@ -31375,21 +31450,21 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P239" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
@@ -31401,17 +31476,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>RLT-72</t>
+          <t>RLT-71</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annual leave 31 Jan</t>
+          <t>Leave for one day 27-02-25</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31421,27 +31496,27 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:16.894+0500</t>
+          <t>2025-02-28T09:31:26.122+0500</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:47.087+0500</t>
+          <t>2025-02-28T09:31:46.578+0500</t>
         </is>
       </c>
       <c r="J240" t="inlineStr"/>
@@ -31455,7 +31530,7 @@
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -31476,47 +31551,47 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>RLT-74</t>
+          <t>RLT-72</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Planned Leave 21st Feb 2025</t>
+          <t>Annual leave 31 Jan</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:51.777+0500</t>
+          <t>2025-03-04T11:51:16.894+0500</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:06.523+0500</t>
+          <t>2025-03-04T11:51:47.087+0500</t>
         </is>
       </c>
       <c r="J241" t="inlineStr"/>
@@ -31551,17 +31626,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>RLT-77</t>
+          <t>RLT-74</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Planned Leave 3rd April 2025</t>
+          <t>Planned Leave 21st Feb 2025</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31586,12 +31661,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2025-04-29T14:35:54.729+0500</t>
+          <t>2025-03-25T09:09:51.777+0500</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:21.782+0500</t>
+          <t>2025-04-29T14:36:06.523+0500</t>
         </is>
       </c>
       <c r="J242" t="inlineStr"/>
@@ -31626,17 +31701,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>RLT-78</t>
+          <t>RLT-77</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Planned Leave 4th April 2025</t>
+          <t>Planned Leave 3rd April 2025</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31661,12 +31736,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:42.933+0500</t>
+          <t>2025-04-29T14:35:54.729+0500</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2025-04-29T14:37:01.596+0500</t>
+          <t>2025-04-29T14:36:21.782+0500</t>
         </is>
       </c>
       <c r="J243" t="inlineStr"/>
@@ -31701,47 +31776,47 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>RLT-79</t>
+          <t>RLT-78</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Sick leave</t>
+          <t>Planned Leave 4th April 2025</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2025-05-15T10:52:44.037+0500</t>
+          <t>2025-04-29T14:36:42.933+0500</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:11.410+0500</t>
+          <t>2025-04-29T14:37:01.596+0500</t>
         </is>
       </c>
       <c r="J244" t="inlineStr"/>
@@ -31755,7 +31830,7 @@
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -31776,47 +31851,47 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>RLT-80</t>
+          <t>RLT-79</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>16 may 2025</t>
+          <t>Sick leave</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>RLT-5</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:34.680+0500</t>
+          <t>2025-05-15T10:52:44.037+0500</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:58.959+0500</t>
+          <t>2025-09-11T09:15:11.410+0500</t>
         </is>
       </c>
       <c r="J245" t="inlineStr"/>
@@ -31851,47 +31926,47 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RLT-81</t>
+          <t>RLT-80</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual leave 22 May</t>
+          <t>16 may 2025</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-5</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2025-05-21T17:45:49.062+0500</t>
+          <t>2025-05-20T15:48:34.680+0500</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:14.892+0500</t>
+          <t>2025-05-20T15:48:58.959+0500</t>
         </is>
       </c>
       <c r="J246" t="inlineStr"/>
@@ -31905,7 +31980,7 @@
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -31926,47 +32001,47 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>RLT-82</t>
+          <t>RLT-81</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Planned Leave 5th June 2025</t>
+          <t>Annual leave 22 May</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2025-06-10T11:05:56.983+0500</t>
+          <t>2025-05-21T17:45:49.062+0500</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:20.879+0500</t>
+          <t>2025-09-11T09:15:14.892+0500</t>
         </is>
       </c>
       <c r="J247" t="inlineStr"/>
@@ -32001,47 +32076,47 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>RLT-83</t>
+          <t>RLT-82</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Annual leave 07 July</t>
+          <t>Planned Leave 5th June 2025</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2025-07-07T12:00:55.557+0500</t>
+          <t>2025-06-10T11:05:56.983+0500</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:19.601+0500</t>
+          <t>2025-09-26T09:55:20.879+0500</t>
         </is>
       </c>
       <c r="J248" t="inlineStr"/>
@@ -32076,17 +32151,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>RLT-84</t>
+          <t>RLT-83</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Casual leave</t>
+          <t>Annual leave 07 July</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32111,12 +32186,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2025-09-11T09:14:17.734+0500</t>
+          <t>2025-07-07T12:00:55.557+0500</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:22.445+0500</t>
+          <t>2025-09-11T09:15:19.601+0500</t>
         </is>
       </c>
       <c r="J249" t="inlineStr"/>
@@ -32125,7 +32200,7 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr">
@@ -32134,7 +32209,7 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr">
@@ -32144,24 +32219,24 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RLT-85</t>
+          <t>RLT-84</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Casual leave 10 sept 25</t>
+          <t>Casual leave</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32186,12 +32261,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:09.033+0500</t>
+          <t>2025-09-11T09:14:17.734+0500</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:45.168+0500</t>
+          <t>2025-09-11T09:15:22.445+0500</t>
         </is>
       </c>
       <c r="J250" t="inlineStr"/>
@@ -32200,7 +32275,7 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr">
@@ -32209,7 +32284,7 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr">
@@ -32219,54 +32294,54 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>RLT-86</t>
+          <t>RLT-85</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Planned Leave 15th July 2025</t>
+          <t>Casual leave 10 sept 25</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:06.810+0500</t>
+          <t>2025-09-11T09:16:09.033+0500</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:30.527+0500</t>
+          <t>2025-09-11T09:16:45.168+0500</t>
         </is>
       </c>
       <c r="J251" t="inlineStr"/>
@@ -32280,7 +32355,7 @@
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -32301,17 +32376,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RLT-87</t>
+          <t>RLT-86</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Planned 1st Sept 2025</t>
+          <t>Planned Leave 15th July 2025</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32336,12 +32411,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2025-09-26T09:56:28.622+0500</t>
+          <t>2025-09-26T09:55:06.810+0500</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:11.707+0500</t>
+          <t>2025-09-26T09:55:30.527+0500</t>
         </is>
       </c>
       <c r="J252" t="inlineStr"/>
@@ -32376,17 +32451,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>RLT-88</t>
+          <t>RLT-87</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2025</t>
+          <t>Planned 1st Sept 2025</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -32411,12 +32486,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:27.334+0500</t>
+          <t>2025-09-26T09:56:28.622+0500</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:46.408+0500</t>
+          <t>2025-09-26T10:05:11.707+0500</t>
         </is>
       </c>
       <c r="J253" t="inlineStr"/>
@@ -32451,22 +32526,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>RLT-89</t>
+          <t>RLT-88</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
+          <t>Planned Leave 15th Aug 2025</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -32486,12 +32561,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2025-10-08T10:16:40.435+0500</t>
+          <t>2025-09-26T10:05:27.334+0500</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2025-11-06T09:37:59.818+0500</t>
+          <t>2025-09-26T10:05:46.408+0500</t>
         </is>
       </c>
       <c r="J254" t="inlineStr"/>
@@ -32500,7 +32575,7 @@
         <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr">
@@ -32509,12 +32584,12 @@
         </is>
       </c>
       <c r="P254" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S254" t="inlineStr">
@@ -32526,22 +32601,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>RLT-90</t>
+          <t>RLT-89</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Planned Leave 5th Nov 2025</t>
+          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -32561,12 +32636,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2025-11-06T09:38:11.154+0500</t>
+          <t>2025-10-08T10:16:40.435+0500</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:11.084+0500</t>
+          <t>2025-11-06T09:37:59.818+0500</t>
         </is>
       </c>
       <c r="J255" t="inlineStr"/>
@@ -32575,21 +32650,21 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P255" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -32601,22 +32676,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RLT-95</t>
+          <t>RLT-90</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>31542</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Sick Leave 18th Nov 2025</t>
+          <t>Planned Leave 5th Nov 2025</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -32636,12 +32711,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:01.035+0500</t>
+          <t>2025-11-06T09:38:11.154+0500</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:30.413+0500</t>
+          <t>2025-12-08T11:30:11.084+0500</t>
         </is>
       </c>
       <c r="J256" t="inlineStr"/>
@@ -32655,7 +32730,7 @@
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -32676,22 +32751,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>RLT-96</t>
+          <t>RLT-95</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
+          <t>Sick Leave 18th Nov 2025</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -32711,12 +32786,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:53.468+0500</t>
+          <t>2025-12-08T11:30:01.035+0500</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:21.845+0500</t>
+          <t>2025-12-08T11:30:30.413+0500</t>
         </is>
       </c>
       <c r="J257" t="inlineStr"/>
@@ -32725,7 +32800,7 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr">
@@ -32734,12 +32809,12 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
@@ -32751,22 +32826,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>RLT-97</t>
+          <t>RLT-96</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>3rd Dec 2025</t>
+          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -32786,12 +32861,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.693+0500</t>
+          <t>2025-12-08T11:30:53.468+0500</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2025-12-08T11:32:24.681+0500</t>
+          <t>2025-12-08T11:31:21.845+0500</t>
         </is>
       </c>
       <c r="J258" t="inlineStr"/>
@@ -32800,21 +32875,21 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P258" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
@@ -32826,47 +32901,47 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>RLT-99</t>
+          <t>RLT-97</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Leave for one day 05-12-25</t>
+          <t>3rd Dec 2025</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2025-12-29T12:28:16.268+0500</t>
+          <t>2025-12-08T11:31:59.693+0500</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2025-12-29T12:29:46.783+0500</t>
+          <t>2025-12-08T11:32:24.681+0500</t>
         </is>
       </c>
       <c r="J259" t="inlineStr"/>
@@ -32880,7 +32955,7 @@
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -32893,6 +32968,81 @@
         </is>
       </c>
       <c r="S259" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>RLT-99</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>32431</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Leave for one day 05-12-25</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Resolved!</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>RLT-35</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:28:16.268+0500</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:29:46.783+0500</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="n">
+        <v>0</v>
+      </c>
+      <c r="M260" t="n">
+        <v>8</v>
+      </c>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -32909,7 +33059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E252"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38167,22 +38317,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-189</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-03T11:17:00.000+0500</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -38202,7 +38352,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -38217,22 +38367,22 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-202</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-04T04:41:00.000+0500</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Syed Yousaf Qadri</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -38252,7 +38402,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -38277,7 +38427,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -38302,7 +38452,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -38327,7 +38477,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -38352,7 +38502,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -38377,7 +38527,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -38402,7 +38552,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -38427,7 +38577,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -38452,7 +38602,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -38477,7 +38627,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -38502,7 +38652,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -38527,7 +38677,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -38552,7 +38702,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -38577,7 +38727,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -38602,7 +38752,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -38627,7 +38777,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -38652,7 +38802,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -38667,17 +38817,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -38692,17 +38842,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38727,7 +38877,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38752,7 +38902,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38777,7 +38927,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38802,7 +38952,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38827,7 +38977,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38852,7 +39002,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -38877,7 +39027,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -38902,7 +39052,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -38927,7 +39077,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -38952,7 +39102,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -38977,7 +39127,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39002,7 +39152,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -39027,7 +39177,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -39052,7 +39202,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -39077,7 +39227,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -39102,7 +39252,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -39127,7 +39277,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -39152,7 +39302,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -39177,7 +39327,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -39202,15 +39352,65 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="E252" t="n">
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
         <v>8</v>
       </c>
     </row>
@@ -39225,7 +39425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39378,7 +39578,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -39393,7 +39593,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -39588,14 +39788,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sarmad Sabir</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -39610,7 +39810,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -39619,29 +39819,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Sarmad Sabir</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>1.81</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -39650,29 +39850,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Waqar Rasheed</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -39681,31 +39881,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Waqar Rasheed</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>48</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Zeeshan Sarwar</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>11</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39720,7 +39951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41128,19 +41359,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -41150,31 +41381,31 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-189</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-189</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -41184,12 +41415,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-202</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-202</t>
         </is>
       </c>
     </row>
@@ -41201,7 +41432,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -41235,7 +41466,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -41269,7 +41500,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -41303,7 +41534,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -41337,7 +41568,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -41371,7 +41602,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -41405,7 +41636,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -41439,7 +41670,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -41473,7 +41704,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -41507,7 +41738,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -41541,7 +41772,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -41575,7 +41806,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -41609,7 +41840,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -41643,7 +41874,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -41677,7 +41908,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -41711,7 +41942,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -41745,7 +41976,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -41779,7 +42010,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -41813,7 +42044,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -41830,12 +42061,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
@@ -41847,7 +42078,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -41864,12 +42095,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
@@ -41881,7 +42112,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -41915,7 +42146,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -41949,7 +42180,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -41983,7 +42214,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -42017,7 +42248,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -42051,7 +42282,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -42085,7 +42316,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -42119,7 +42350,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -42153,7 +42384,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -42187,7 +42418,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -42221,7 +42452,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -42255,7 +42486,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -42289,7 +42520,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -42323,7 +42554,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -42357,7 +42588,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -42391,7 +42622,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -42425,7 +42656,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -42459,7 +42690,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -42493,7 +42724,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -42527,27 +42758,95 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>8</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>8</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C83" t="n">
-        <v>8</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>8</v>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="C85" t="n">
+        <v>8</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>8</v>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>RLT-173</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
         </is>
@@ -42564,7 +42863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42938,7 +43237,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -42947,22 +43246,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -42971,7 +43270,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.5</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -42980,13 +43279,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -42995,64 +43294,64 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-W11</t>
+          <t>2026-W10</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-W12</t>
+          <t>2026-W10</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -43063,7 +43362,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-W13</t>
+          <t>2026-W11</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -43087,7 +43386,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W12</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -43111,7 +43410,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W13</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -43135,7 +43434,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -43159,7 +43458,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -43183,19 +43482,67 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>40</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>40</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>2026-W18</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C28" t="n">
         <v>32</v>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>32</v>
       </c>
     </row>
@@ -43210,7 +43557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43440,7 +43787,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -43449,22 +43796,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>176</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -43473,7 +43820,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.5</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -43482,13 +43829,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6.5</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -43497,39 +43844,87 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Taimur Zahid</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C15" t="n">
         <v>176</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>176</v>
       </c>
     </row>

--- a/rlt_leave_report.xlsx
+++ b/rlt_leave_report.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S142"/>
+  <dimension ref="A1:S144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-02-20T16:57:24.769+0500</t>
+          <t>2026-03-07T13:23:13.421+0500</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
@@ -7913,47 +7913,47 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RLT-43</t>
+          <t>RLT-203</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>39391</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Planned Leave 15th May 2024</t>
+          <t>Casual Leave 6 march 2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2024-05-15T13:17:36.997+0500</t>
+          <t>2026-03-07T13:23:02.827+0500</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:48.485+0500</t>
+          <t>2026-03-07T13:24:08.437+0500</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
@@ -7964,10 +7964,14 @@
       <c r="M97" t="n">
         <v>8</v>
       </c>
-      <c r="N97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Unplanned Leave</t>
+        </is>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7988,47 +7992,47 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RLT-44</t>
+          <t>RLT-204</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>39425</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Leaves Faiza</t>
+          <t>Sick leave for one day 06-03-26</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2024-05-27T17:19:47.991+0500</t>
+          <t>2026-03-09T09:46:03.515+0500</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2025-12-30T10:15:12.915+0500</t>
+          <t>2026-03-09T09:46:46.946+0500</t>
         </is>
       </c>
       <c r="J98" t="inlineStr"/>
@@ -8037,7 +8041,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>136</v>
+        <v>6.5</v>
       </c>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
@@ -8046,12 +8050,12 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>136</v>
+        <v>6.5</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -8063,47 +8067,47 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RLT-45</t>
+          <t>RLT-43</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Leave for one day 05-06-24</t>
+          <t>Planned Leave 15th May 2024</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2024-06-06T09:10:07.974+0500</t>
+          <t>2024-05-15T13:17:36.997+0500</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2024-06-06T09:11:39.142+0500</t>
+          <t>2024-08-16T16:28:48.485+0500</t>
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
@@ -8117,7 +8121,7 @@
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -8138,47 +8142,47 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RLT-46</t>
+          <t>RLT-44</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Planned Leave 20th June 2024</t>
+          <t>Leaves Faiza</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2024-06-21T09:20:21.600+0500</t>
+          <t>2024-05-27T17:19:47.991+0500</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:56.168+0500</t>
+          <t>2025-12-30T10:15:12.915+0500</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
@@ -8187,21 +8191,21 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -8213,17 +8217,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RLT-47</t>
+          <t>RLT-45</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Leave for two days 20 and 21-06-24</t>
+          <t>Leave for one day 05-06-24</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8248,12 +8252,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2024-06-24T09:18:18.735+0500</t>
+          <t>2024-06-06T09:10:07.974+0500</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2024-06-24T09:19:43.343+0500</t>
+          <t>2024-06-06T09:11:39.142+0500</t>
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
@@ -8262,7 +8266,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
@@ -8271,12 +8275,12 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -8288,47 +8292,47 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RLT-48</t>
+          <t>RLT-46</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Half day leave</t>
+          <t>Planned Leave 20th June 2024</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Half Day Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2024-06-27T19:06:21.094+0500</t>
+          <t>2024-06-21T09:20:21.600+0500</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2024-06-27T19:06:47.198+0500</t>
+          <t>2024-08-16T16:28:56.168+0500</t>
         </is>
       </c>
       <c r="J102" t="inlineStr"/>
@@ -8337,16 +8341,16 @@
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
@@ -8363,47 +8367,47 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RLT-49</t>
+          <t>RLT-47</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Emergency leave</t>
+          <t>Leave for two days 20 and 21-06-24</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2024-07-18T11:05:11.868+0500</t>
+          <t>2024-06-24T09:18:18.735+0500</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-01-29T16:48:09.549+0500</t>
+          <t>2024-06-24T09:19:43.343+0500</t>
         </is>
       </c>
       <c r="J103" t="inlineStr"/>
@@ -8412,16 +8416,16 @@
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
@@ -8438,47 +8442,47 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RLT-50</t>
+          <t>RLT-48</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sick leave for one day 22-07-24</t>
+          <t>Half day leave</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Half Day Leave</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2024-07-23T09:08:09.289+0500</t>
+          <t>2024-06-27T19:06:21.094+0500</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2024-07-23T09:09:17.479+0500</t>
+          <t>2024-06-27T19:06:47.198+0500</t>
         </is>
       </c>
       <c r="J104" t="inlineStr"/>
@@ -8487,16 +8491,16 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
@@ -8513,47 +8517,47 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RLT-51</t>
+          <t>RLT-49</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Full Day Sick Leave</t>
+          <t>Emergency leave</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2024-07-23T12:27:33.881+0500</t>
+          <t>2024-07-18T11:05:11.868+0500</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2024-10-03T16:40:27.519+0500</t>
+          <t>2026-01-29T16:48:09.549+0500</t>
         </is>
       </c>
       <c r="J105" t="inlineStr"/>
@@ -8562,7 +8566,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
@@ -8571,7 +8575,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
@@ -8588,17 +8592,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RLT-52</t>
+          <t>RLT-50</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Urgent work leave 05-08-24</t>
+          <t>Sick leave for one day 22-07-24</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8623,12 +8627,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2024-08-06T09:08:48.315+0500</t>
+          <t>2024-07-23T09:08:09.289+0500</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2024-08-06T09:11:15.823+0500</t>
+          <t>2024-07-23T09:09:17.479+0500</t>
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
@@ -8642,7 +8646,7 @@
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8663,47 +8667,47 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RLT-53</t>
+          <t>RLT-51</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2024</t>
+          <t>Full Day Sick Leave</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:43.991+0500</t>
+          <t>2024-07-23T12:27:33.881+0500</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2024-08-16T16:29:17.981+0500</t>
+          <t>2024-10-03T16:40:27.519+0500</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -8712,21 +8716,21 @@
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -8738,17 +8742,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RLT-54</t>
+          <t>RLT-52</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Leave for one day 30-08-24</t>
+          <t>Urgent work leave 05-08-24</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -8773,12 +8777,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:09.454+0500</t>
+          <t>2024-08-06T09:08:48.315+0500</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2024-09-03T09:15:53.284+0500</t>
+          <t>2024-08-06T09:11:15.823+0500</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -8813,47 +8817,47 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RLT-55</t>
+          <t>RLT-53</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Leave for one day 02-09-24</t>
+          <t>Planned Leave 15th Aug 2024</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:29.824+0500</t>
+          <t>2024-08-16T16:28:43.991+0500</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2024-09-03T09:16:12.471+0500</t>
+          <t>2024-08-16T16:29:17.981+0500</t>
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
@@ -8867,7 +8871,7 @@
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8888,47 +8892,47 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RLT-56</t>
+          <t>RLT-54</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sick leave 28th Aug 2024</t>
+          <t>Leave for one day 30-08-24</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2024-09-03T10:03:57.925+0500</t>
+          <t>2024-08-28T16:51:09.454+0500</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2024-09-03T10:04:14.562+0500</t>
+          <t>2024-09-03T09:15:53.284+0500</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -8942,7 +8946,7 @@
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8963,47 +8967,47 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RLT-57</t>
+          <t>RLT-55</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sick Leave 13th Sept 2024</t>
+          <t>Leave for one day 02-09-24</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2024-09-23T11:07:49.200+0500</t>
+          <t>2024-08-28T16:51:29.824+0500</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2024-09-23T11:08:09.638+0500</t>
+          <t>2024-09-03T09:16:12.471+0500</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -9017,7 +9021,7 @@
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -9038,47 +9042,47 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RLT-58</t>
+          <t>RLT-56</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Leave for one day 14-11-24</t>
+          <t>Sick leave 28th Aug 2024</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-11-15T09:25:05.670+0500</t>
+          <t>2024-09-03T10:03:57.925+0500</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2024-11-15T09:38:06.205+0500</t>
+          <t>2024-09-03T10:04:14.562+0500</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -9092,7 +9096,7 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -9113,22 +9117,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RLT-59</t>
+          <t>RLT-57</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Planned Leave 8th Nov 2024</t>
+          <t>Sick Leave 13th Sept 2024</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9148,12 +9152,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2024-11-21T12:24:36.990+0500</t>
+          <t>2024-09-23T11:07:49.200+0500</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:57.134+0500</t>
+          <t>2024-09-23T11:08:09.638+0500</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -9162,16 +9166,16 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
@@ -9181,54 +9185,54 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RLT-60</t>
+          <t>RLT-58</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Planned Leave 19th Nov 2024</t>
+          <t>Leave for one day 14-11-24</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-11-21T12:25:03.206+0500</t>
+          <t>2024-11-15T09:25:05.670+0500</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:07.591+0500</t>
+          <t>2024-11-15T09:38:06.205+0500</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -9242,7 +9246,7 @@
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -9263,47 +9267,47 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RLT-62</t>
+          <t>RLT-59</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sick leave for one day 30-12-24</t>
+          <t>Planned Leave 8th Nov 2024</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:13.907+0500</t>
+          <t>2024-11-21T12:24:36.990+0500</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:33.151+0500</t>
+          <t>2024-12-31T11:38:57.134+0500</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -9312,16 +9316,16 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
@@ -9331,24 +9335,24 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RLT-63</t>
+          <t>RLT-60</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Planned Leave 29th Nov 2024</t>
+          <t>Planned Leave 19th Nov 2024</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9373,12 +9377,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:18.228+0500</t>
+          <t>2024-11-21T12:25:03.206+0500</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:11.165+0500</t>
+          <t>2024-12-31T11:39:07.591+0500</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -9413,47 +9417,47 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RLT-64</t>
+          <t>RLT-62</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Planned Leave 16th Dec 2024</t>
+          <t>Sick leave for one day 30-12-24</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:25.533+0500</t>
+          <t>2024-12-31T09:30:13.907+0500</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:27.662+0500</t>
+          <t>2024-12-31T09:30:33.151+0500</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -9467,7 +9471,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9488,17 +9492,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RLT-65</t>
+          <t>RLT-63</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
+          <t>Planned Leave 29th Nov 2024</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9523,12 +9527,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-12-31T11:40:34.525+0500</t>
+          <t>2024-12-31T11:38:18.228+0500</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:36.616+0500</t>
+          <t>2024-12-31T11:39:11.165+0500</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -9537,7 +9541,7 @@
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
@@ -9546,12 +9550,12 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -9563,47 +9567,47 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RLT-67</t>
+          <t>RLT-64</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Casual Leave for half day 02-01-25</t>
+          <t>Planned Leave 16th Dec 2024</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2025-01-06T09:19:42.013+0500</t>
+          <t>2024-12-31T11:39:25.533+0500</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:11.598+0500</t>
+          <t>2025-03-25T09:09:27.662+0500</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -9612,7 +9616,7 @@
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
@@ -9621,7 +9625,7 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
@@ -9638,47 +9642,47 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RLT-68</t>
+          <t>RLT-65</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Leave for one day 03-01-25</t>
+          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2025-01-06T09:20:06.483+0500</t>
+          <t>2024-12-31T11:40:34.525+0500</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:08.280+0500</t>
+          <t>2025-03-25T09:09:36.616+0500</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -9687,21 +9691,21 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -9713,47 +9717,47 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RLT-70</t>
+          <t>RLT-67</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Medical Leaves</t>
+          <t>Casual Leave for half day 02-01-25</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2025-02-27T12:06:39.343+0500</t>
+          <t>2025-01-06T09:19:42.013+0500</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2025-02-27T12:07:35.090+0500</t>
+          <t>2025-01-06T09:21:11.598+0500</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -9762,7 +9766,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
@@ -9771,12 +9775,12 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -9788,17 +9792,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RLT-71</t>
+          <t>RLT-68</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Leave for one day 27-02-25</t>
+          <t>Leave for one day 03-01-25</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9823,12 +9827,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:26.122+0500</t>
+          <t>2025-01-06T09:20:06.483+0500</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:46.578+0500</t>
+          <t>2025-01-06T09:21:08.280+0500</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -9863,47 +9867,47 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RLT-72</t>
+          <t>RLT-70</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Annual leave 31 Jan</t>
+          <t>Medical Leaves</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:16.894+0500</t>
+          <t>2025-02-27T12:06:39.343+0500</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:47.087+0500</t>
+          <t>2025-02-27T12:07:35.090+0500</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -9912,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
@@ -9921,12 +9925,12 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -9938,47 +9942,47 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RLT-74</t>
+          <t>RLT-71</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Planned Leave 21st Feb 2025</t>
+          <t>Leave for one day 27-02-25</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:51.777+0500</t>
+          <t>2025-02-28T09:31:26.122+0500</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:06.523+0500</t>
+          <t>2025-02-28T09:31:46.578+0500</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -9992,7 +9996,7 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -10013,47 +10017,47 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RLT-77</t>
+          <t>RLT-72</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Planned Leave 3rd April 2025</t>
+          <t>Annual leave 31 Jan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2025-04-29T14:35:54.729+0500</t>
+          <t>2025-03-04T11:51:16.894+0500</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:21.782+0500</t>
+          <t>2025-03-04T11:51:47.087+0500</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -10088,17 +10092,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RLT-78</t>
+          <t>RLT-74</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Planned Leave 4th April 2025</t>
+          <t>Planned Leave 21st Feb 2025</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10123,12 +10127,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:42.933+0500</t>
+          <t>2025-03-25T09:09:51.777+0500</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2025-04-29T14:37:01.596+0500</t>
+          <t>2025-04-29T14:36:06.523+0500</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -10163,47 +10167,47 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RLT-79</t>
+          <t>RLT-77</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sick leave</t>
+          <t>Planned Leave 3rd April 2025</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2025-05-15T10:52:44.037+0500</t>
+          <t>2025-04-29T14:35:54.729+0500</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:11.410+0500</t>
+          <t>2025-04-29T14:36:21.782+0500</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -10217,7 +10221,7 @@
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -10238,47 +10242,47 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RLT-80</t>
+          <t>RLT-78</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>16 may 2025</t>
+          <t>Planned Leave 4th April 2025</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>RLT-5</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:34.680+0500</t>
+          <t>2025-04-29T14:36:42.933+0500</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:58.959+0500</t>
+          <t>2025-04-29T14:37:01.596+0500</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -10292,7 +10296,7 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -10313,17 +10317,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RLT-81</t>
+          <t>RLT-79</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Annual leave 22 May</t>
+          <t>Sick leave</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10348,12 +10352,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2025-05-21T17:45:49.062+0500</t>
+          <t>2025-05-15T10:52:44.037+0500</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:14.892+0500</t>
+          <t>2025-09-11T09:15:11.410+0500</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -10367,7 +10371,7 @@
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10388,47 +10392,47 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RLT-82</t>
+          <t>RLT-80</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Planned Leave 5th June 2025</t>
+          <t>16 may 2025</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-5</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2025-06-10T11:05:56.983+0500</t>
+          <t>2025-05-20T15:48:34.680+0500</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:20.879+0500</t>
+          <t>2025-05-20T15:48:58.959+0500</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -10442,7 +10446,7 @@
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10463,17 +10467,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RLT-83</t>
+          <t>RLT-81</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Annual leave 07 July</t>
+          <t>Annual leave 22 May</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10498,12 +10502,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2025-07-07T12:00:55.557+0500</t>
+          <t>2025-05-21T17:45:49.062+0500</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:19.601+0500</t>
+          <t>2025-09-11T09:15:14.892+0500</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -10538,47 +10542,47 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RLT-84</t>
+          <t>RLT-82</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Casual leave</t>
+          <t>Planned Leave 5th June 2025</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2025-09-11T09:14:17.734+0500</t>
+          <t>2025-06-10T11:05:56.983+0500</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:22.445+0500</t>
+          <t>2025-09-26T09:55:20.879+0500</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -10587,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
@@ -10596,7 +10600,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
@@ -10606,24 +10610,24 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RLT-85</t>
+          <t>RLT-83</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Casual leave 10 sept 25</t>
+          <t>Annual leave 07 July</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -10648,12 +10652,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:09.033+0500</t>
+          <t>2025-07-07T12:00:55.557+0500</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:45.168+0500</t>
+          <t>2025-09-11T09:15:19.601+0500</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -10688,47 +10692,47 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RLT-86</t>
+          <t>RLT-84</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Planned Leave 15th July 2025</t>
+          <t>Casual leave</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:06.810+0500</t>
+          <t>2025-09-11T09:14:17.734+0500</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:30.527+0500</t>
+          <t>2025-09-11T09:15:22.445+0500</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -10737,16 +10741,16 @@
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr">
@@ -10756,54 +10760,54 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RLT-87</t>
+          <t>RLT-85</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Planned 1st Sept 2025</t>
+          <t>Casual leave 10 sept 25</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2025-09-26T09:56:28.622+0500</t>
+          <t>2025-09-11T09:16:09.033+0500</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:11.707+0500</t>
+          <t>2025-09-11T09:16:45.168+0500</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -10817,7 +10821,7 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10838,17 +10842,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RLT-88</t>
+          <t>RLT-86</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2025</t>
+          <t>Planned Leave 15th July 2025</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10873,12 +10877,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:27.334+0500</t>
+          <t>2025-09-26T09:55:06.810+0500</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:46.408+0500</t>
+          <t>2025-09-26T09:55:30.527+0500</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
@@ -10913,22 +10917,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RLT-89</t>
+          <t>RLT-87</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
+          <t>Planned 1st Sept 2025</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -10948,12 +10952,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-10-08T10:16:40.435+0500</t>
+          <t>2025-09-26T09:56:28.622+0500</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2025-11-06T09:37:59.818+0500</t>
+          <t>2025-09-26T10:05:11.707+0500</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -10962,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
@@ -10971,12 +10975,12 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -10988,22 +10992,22 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RLT-90</t>
+          <t>RLT-88</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Planned Leave 5th Nov 2025</t>
+          <t>Planned Leave 15th Aug 2025</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -11023,12 +11027,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2025-11-06T09:38:11.154+0500</t>
+          <t>2025-09-26T10:05:27.334+0500</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:11.084+0500</t>
+          <t>2025-09-26T10:05:46.408+0500</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -11042,7 +11046,7 @@
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -11063,22 +11067,22 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RLT-95</t>
+          <t>RLT-89</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>31542</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sick Leave 18th Nov 2025</t>
+          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -11098,12 +11102,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:01.035+0500</t>
+          <t>2025-10-08T10:16:40.435+0500</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:30.413+0500</t>
+          <t>2025-11-06T09:37:59.818+0500</t>
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
@@ -11112,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
@@ -11121,12 +11125,12 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
@@ -11138,22 +11142,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RLT-96</t>
+          <t>RLT-90</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
+          <t>Planned Leave 5th Nov 2025</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -11173,12 +11177,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:53.468+0500</t>
+          <t>2025-11-06T09:38:11.154+0500</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:21.845+0500</t>
+          <t>2025-12-08T11:30:11.084+0500</t>
         </is>
       </c>
       <c r="J140" t="inlineStr"/>
@@ -11187,21 +11191,21 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
@@ -11213,22 +11217,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RLT-97</t>
+          <t>RLT-95</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>3rd Dec 2025</t>
+          <t>Sick Leave 18th Nov 2025</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -11248,12 +11252,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.693+0500</t>
+          <t>2025-12-08T11:30:01.035+0500</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2025-12-08T11:32:24.681+0500</t>
+          <t>2025-12-08T11:30:30.413+0500</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
@@ -11267,7 +11271,7 @@
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -11288,47 +11292,47 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RLT-99</t>
+          <t>RLT-96</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Leave for one day 05-12-25</t>
+          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2025-12-29T12:28:16.268+0500</t>
+          <t>2025-12-08T11:30:53.468+0500</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2025-12-29T12:29:46.783+0500</t>
+          <t>2025-12-08T11:31:21.845+0500</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
@@ -11337,24 +11341,174 @@
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>RLT-97</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>31546</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>3rd Dec 2025</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Planned Leave</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Hassan Saeed Wattoo</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>RLT-39</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Hassan Saeed Wattoo</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2025-12-08T11:31:59.693+0500</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2025-12-08T11:32:24.681+0500</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>8</v>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>RLT-99</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>32431</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Leave for one day 05-12-25</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Resolved!</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>RLT-35</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:28:16.268+0500</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:29:46.783+0500</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>8</v>
+      </c>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -11371,7 +11525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S260"/>
+  <dimension ref="A1:S262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28792,7 +28946,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -28812,7 +28966,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-02-20T16:57:24.769+0500</t>
+          <t>2026-03-07T13:23:13.421+0500</t>
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
@@ -29601,47 +29755,47 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>RLT-43</t>
+          <t>RLT-203</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>39391</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Planned Leave 15th May 2024</t>
+          <t>Casual Leave 6 march 2026</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2024-05-15T13:17:36.997+0500</t>
+          <t>2026-03-07T13:23:02.827+0500</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:48.485+0500</t>
+          <t>2026-03-07T13:24:08.437+0500</t>
         </is>
       </c>
       <c r="J215" t="inlineStr"/>
@@ -29652,10 +29806,14 @@
       <c r="M215" t="n">
         <v>8</v>
       </c>
-      <c r="N215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Unplanned Leave</t>
+        </is>
+      </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -29676,47 +29834,47 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>RLT-44</t>
+          <t>RLT-204</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>39425</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Leaves Faiza</t>
+          <t>Sick leave for one day 06-03-26</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2024-05-27T17:19:47.991+0500</t>
+          <t>2026-03-09T09:46:03.515+0500</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2025-12-30T10:15:12.915+0500</t>
+          <t>2026-03-09T09:46:46.946+0500</t>
         </is>
       </c>
       <c r="J216" t="inlineStr"/>
@@ -29725,7 +29883,7 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>136</v>
+        <v>6.5</v>
       </c>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
@@ -29734,12 +29892,12 @@
         </is>
       </c>
       <c r="P216" t="n">
-        <v>136</v>
+        <v>6.5</v>
       </c>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
@@ -29751,47 +29909,47 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>RLT-45</t>
+          <t>RLT-43</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Leave for one day 05-06-24</t>
+          <t>Planned Leave 15th May 2024</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2024-06-06T09:10:07.974+0500</t>
+          <t>2024-05-15T13:17:36.997+0500</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2024-06-06T09:11:39.142+0500</t>
+          <t>2024-08-16T16:28:48.485+0500</t>
         </is>
       </c>
       <c r="J217" t="inlineStr"/>
@@ -29805,7 +29963,7 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -29826,47 +29984,47 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>RLT-46</t>
+          <t>RLT-44</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Planned Leave 20th June 2024</t>
+          <t>Leaves Faiza</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2024-06-21T09:20:21.600+0500</t>
+          <t>2024-05-27T17:19:47.991+0500</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:56.168+0500</t>
+          <t>2025-12-30T10:15:12.915+0500</t>
         </is>
       </c>
       <c r="J218" t="inlineStr"/>
@@ -29875,21 +30033,21 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P218" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
@@ -29901,17 +30059,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>RLT-47</t>
+          <t>RLT-45</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Leave for two days 20 and 21-06-24</t>
+          <t>Leave for one day 05-06-24</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -29936,12 +30094,12 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2024-06-24T09:18:18.735+0500</t>
+          <t>2024-06-06T09:10:07.974+0500</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>2024-06-24T09:19:43.343+0500</t>
+          <t>2024-06-06T09:11:39.142+0500</t>
         </is>
       </c>
       <c r="J219" t="inlineStr"/>
@@ -29950,7 +30108,7 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
@@ -29959,12 +30117,12 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
@@ -29976,47 +30134,47 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>RLT-48</t>
+          <t>RLT-46</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>17899</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Half day leave</t>
+          <t>Planned Leave 20th June 2024</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Half Day Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2024-06-27T19:06:21.094+0500</t>
+          <t>2024-06-21T09:20:21.600+0500</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>2024-06-27T19:06:47.198+0500</t>
+          <t>2024-08-16T16:28:56.168+0500</t>
         </is>
       </c>
       <c r="J220" t="inlineStr"/>
@@ -30025,16 +30183,16 @@
         <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P220" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr">
@@ -30051,47 +30209,47 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>RLT-49</t>
+          <t>RLT-47</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Emergency leave</t>
+          <t>Leave for two days 20 and 21-06-24</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2024-07-18T11:05:11.868+0500</t>
+          <t>2024-06-24T09:18:18.735+0500</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2026-01-29T16:48:09.549+0500</t>
+          <t>2024-06-24T09:19:43.343+0500</t>
         </is>
       </c>
       <c r="J221" t="inlineStr"/>
@@ -30100,16 +30258,16 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P221" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr">
@@ -30126,47 +30284,47 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>RLT-50</t>
+          <t>RLT-48</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Sick leave for one day 22-07-24</t>
+          <t>Half day leave</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Half Day Leave</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2024-07-23T09:08:09.289+0500</t>
+          <t>2024-06-27T19:06:21.094+0500</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>2024-07-23T09:09:17.479+0500</t>
+          <t>2024-06-27T19:06:47.198+0500</t>
         </is>
       </c>
       <c r="J222" t="inlineStr"/>
@@ -30175,16 +30333,16 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P222" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr">
@@ -30201,47 +30359,47 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>RLT-51</t>
+          <t>RLT-49</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Full Day Sick Leave</t>
+          <t>Emergency leave</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2024-07-23T12:27:33.881+0500</t>
+          <t>2024-07-18T11:05:11.868+0500</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2024-10-03T16:40:27.519+0500</t>
+          <t>2026-01-29T16:48:09.549+0500</t>
         </is>
       </c>
       <c r="J223" t="inlineStr"/>
@@ -30250,7 +30408,7 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr">
@@ -30259,7 +30417,7 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr">
@@ -30276,17 +30434,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>RLT-52</t>
+          <t>RLT-50</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Urgent work leave 05-08-24</t>
+          <t>Sick leave for one day 22-07-24</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -30311,12 +30469,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2024-08-06T09:08:48.315+0500</t>
+          <t>2024-07-23T09:08:09.289+0500</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2024-08-06T09:11:15.823+0500</t>
+          <t>2024-07-23T09:09:17.479+0500</t>
         </is>
       </c>
       <c r="J224" t="inlineStr"/>
@@ -30330,7 +30488,7 @@
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -30351,47 +30509,47 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>RLT-53</t>
+          <t>RLT-51</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2024</t>
+          <t>Full Day Sick Leave</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:43.991+0500</t>
+          <t>2024-07-23T12:27:33.881+0500</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2024-08-16T16:29:17.981+0500</t>
+          <t>2024-10-03T16:40:27.519+0500</t>
         </is>
       </c>
       <c r="J225" t="inlineStr"/>
@@ -30400,21 +30558,21 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S225" t="inlineStr">
@@ -30426,17 +30584,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>RLT-54</t>
+          <t>RLT-52</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Leave for one day 30-08-24</t>
+          <t>Urgent work leave 05-08-24</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -30461,12 +30619,12 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:09.454+0500</t>
+          <t>2024-08-06T09:08:48.315+0500</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2024-09-03T09:15:53.284+0500</t>
+          <t>2024-08-06T09:11:15.823+0500</t>
         </is>
       </c>
       <c r="J226" t="inlineStr"/>
@@ -30501,47 +30659,47 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>RLT-55</t>
+          <t>RLT-53</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Leave for one day 02-09-24</t>
+          <t>Planned Leave 15th Aug 2024</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:29.824+0500</t>
+          <t>2024-08-16T16:28:43.991+0500</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2024-09-03T09:16:12.471+0500</t>
+          <t>2024-08-16T16:29:17.981+0500</t>
         </is>
       </c>
       <c r="J227" t="inlineStr"/>
@@ -30555,7 +30713,7 @@
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -30576,47 +30734,47 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>RLT-56</t>
+          <t>RLT-54</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Sick leave 28th Aug 2024</t>
+          <t>Leave for one day 30-08-24</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>2024-09-03T10:03:57.925+0500</t>
+          <t>2024-08-28T16:51:09.454+0500</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2024-09-03T10:04:14.562+0500</t>
+          <t>2024-09-03T09:15:53.284+0500</t>
         </is>
       </c>
       <c r="J228" t="inlineStr"/>
@@ -30630,7 +30788,7 @@
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -30651,47 +30809,47 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RLT-57</t>
+          <t>RLT-55</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Sick Leave 13th Sept 2024</t>
+          <t>Leave for one day 02-09-24</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2024-09-23T11:07:49.200+0500</t>
+          <t>2024-08-28T16:51:29.824+0500</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2024-09-23T11:08:09.638+0500</t>
+          <t>2024-09-03T09:16:12.471+0500</t>
         </is>
       </c>
       <c r="J229" t="inlineStr"/>
@@ -30705,7 +30863,7 @@
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -30726,47 +30884,47 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RLT-58</t>
+          <t>RLT-56</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Leave for one day 14-11-24</t>
+          <t>Sick leave 28th Aug 2024</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2024-11-15T09:25:05.670+0500</t>
+          <t>2024-09-03T10:03:57.925+0500</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2024-11-15T09:38:06.205+0500</t>
+          <t>2024-09-03T10:04:14.562+0500</t>
         </is>
       </c>
       <c r="J230" t="inlineStr"/>
@@ -30780,7 +30938,7 @@
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -30801,22 +30959,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RLT-59</t>
+          <t>RLT-57</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Planned Leave 8th Nov 2024</t>
+          <t>Sick Leave 13th Sept 2024</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -30836,12 +30994,12 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2024-11-21T12:24:36.990+0500</t>
+          <t>2024-09-23T11:07:49.200+0500</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:57.134+0500</t>
+          <t>2024-09-23T11:08:09.638+0500</t>
         </is>
       </c>
       <c r="J231" t="inlineStr"/>
@@ -30850,16 +31008,16 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr">
@@ -30869,54 +31027,54 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RLT-60</t>
+          <t>RLT-58</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Planned Leave 19th Nov 2024</t>
+          <t>Leave for one day 14-11-24</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2024-11-21T12:25:03.206+0500</t>
+          <t>2024-11-15T09:25:05.670+0500</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:07.591+0500</t>
+          <t>2024-11-15T09:38:06.205+0500</t>
         </is>
       </c>
       <c r="J232" t="inlineStr"/>
@@ -30930,7 +31088,7 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -30951,47 +31109,47 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>RLT-62</t>
+          <t>RLT-59</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Sick leave for one day 30-12-24</t>
+          <t>Planned Leave 8th Nov 2024</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:13.907+0500</t>
+          <t>2024-11-21T12:24:36.990+0500</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:33.151+0500</t>
+          <t>2024-12-31T11:38:57.134+0500</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
@@ -31000,16 +31158,16 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P233" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr">
@@ -31019,24 +31177,24 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RLT-63</t>
+          <t>RLT-60</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Planned Leave 29th Nov 2024</t>
+          <t>Planned Leave 19th Nov 2024</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -31061,12 +31219,12 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:18.228+0500</t>
+          <t>2024-11-21T12:25:03.206+0500</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:11.165+0500</t>
+          <t>2024-12-31T11:39:07.591+0500</t>
         </is>
       </c>
       <c r="J234" t="inlineStr"/>
@@ -31101,47 +31259,47 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>RLT-64</t>
+          <t>RLT-62</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Planned Leave 16th Dec 2024</t>
+          <t>Sick leave for one day 30-12-24</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:25.533+0500</t>
+          <t>2024-12-31T09:30:13.907+0500</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:27.662+0500</t>
+          <t>2024-12-31T09:30:33.151+0500</t>
         </is>
       </c>
       <c r="J235" t="inlineStr"/>
@@ -31155,7 +31313,7 @@
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -31176,17 +31334,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RLT-65</t>
+          <t>RLT-63</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
+          <t>Planned Leave 29th Nov 2024</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -31211,12 +31369,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2024-12-31T11:40:34.525+0500</t>
+          <t>2024-12-31T11:38:18.228+0500</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:36.616+0500</t>
+          <t>2024-12-31T11:39:11.165+0500</t>
         </is>
       </c>
       <c r="J236" t="inlineStr"/>
@@ -31225,7 +31383,7 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr">
@@ -31234,12 +31392,12 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -31251,47 +31409,47 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RLT-67</t>
+          <t>RLT-64</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Casual Leave for half day 02-01-25</t>
+          <t>Planned Leave 16th Dec 2024</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2025-01-06T09:19:42.013+0500</t>
+          <t>2024-12-31T11:39:25.533+0500</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:11.598+0500</t>
+          <t>2025-03-25T09:09:27.662+0500</t>
         </is>
       </c>
       <c r="J237" t="inlineStr"/>
@@ -31300,7 +31458,7 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr">
@@ -31309,7 +31467,7 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr">
@@ -31326,47 +31484,47 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>RLT-68</t>
+          <t>RLT-65</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Leave for one day 03-01-25</t>
+          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2025-01-06T09:20:06.483+0500</t>
+          <t>2024-12-31T11:40:34.525+0500</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:08.280+0500</t>
+          <t>2025-03-25T09:09:36.616+0500</t>
         </is>
       </c>
       <c r="J238" t="inlineStr"/>
@@ -31375,21 +31533,21 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S238" t="inlineStr">
@@ -31401,47 +31559,47 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>RLT-70</t>
+          <t>RLT-67</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Medical Leaves</t>
+          <t>Casual Leave for half day 02-01-25</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>RLT-25</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Ali Qumail</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2025-02-27T12:06:39.343+0500</t>
+          <t>2025-01-06T09:19:42.013+0500</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2025-02-27T12:07:35.090+0500</t>
+          <t>2025-01-06T09:21:11.598+0500</t>
         </is>
       </c>
       <c r="J239" t="inlineStr"/>
@@ -31450,7 +31608,7 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
@@ -31459,12 +31617,12 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S239" t="inlineStr">
@@ -31476,17 +31634,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>RLT-71</t>
+          <t>RLT-68</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Leave for one day 27-02-25</t>
+          <t>Leave for one day 03-01-25</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31511,12 +31669,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:26.122+0500</t>
+          <t>2025-01-06T09:20:06.483+0500</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:46.578+0500</t>
+          <t>2025-01-06T09:21:08.280+0500</t>
         </is>
       </c>
       <c r="J240" t="inlineStr"/>
@@ -31551,47 +31709,47 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>RLT-72</t>
+          <t>RLT-70</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Annual leave 31 Jan</t>
+          <t>Medical Leaves</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-25</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Ali Qumail</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:16.894+0500</t>
+          <t>2025-02-27T12:06:39.343+0500</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:47.087+0500</t>
+          <t>2025-02-27T12:07:35.090+0500</t>
         </is>
       </c>
       <c r="J241" t="inlineStr"/>
@@ -31600,7 +31758,7 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr">
@@ -31609,12 +31767,12 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S241" t="inlineStr">
@@ -31626,47 +31784,47 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>RLT-74</t>
+          <t>RLT-71</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Planned Leave 21st Feb 2025</t>
+          <t>Leave for one day 27-02-25</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:51.777+0500</t>
+          <t>2025-02-28T09:31:26.122+0500</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:06.523+0500</t>
+          <t>2025-02-28T09:31:46.578+0500</t>
         </is>
       </c>
       <c r="J242" t="inlineStr"/>
@@ -31680,7 +31838,7 @@
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -31701,47 +31859,47 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>RLT-77</t>
+          <t>RLT-72</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Planned Leave 3rd April 2025</t>
+          <t>Annual leave 31 Jan</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2025-04-29T14:35:54.729+0500</t>
+          <t>2025-03-04T11:51:16.894+0500</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:21.782+0500</t>
+          <t>2025-03-04T11:51:47.087+0500</t>
         </is>
       </c>
       <c r="J243" t="inlineStr"/>
@@ -31776,17 +31934,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>RLT-78</t>
+          <t>RLT-74</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Planned Leave 4th April 2025</t>
+          <t>Planned Leave 21st Feb 2025</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31811,12 +31969,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:42.933+0500</t>
+          <t>2025-03-25T09:09:51.777+0500</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2025-04-29T14:37:01.596+0500</t>
+          <t>2025-04-29T14:36:06.523+0500</t>
         </is>
       </c>
       <c r="J244" t="inlineStr"/>
@@ -31851,47 +32009,47 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>RLT-79</t>
+          <t>RLT-77</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Sick leave</t>
+          <t>Planned Leave 3rd April 2025</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2025-05-15T10:52:44.037+0500</t>
+          <t>2025-04-29T14:35:54.729+0500</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:11.410+0500</t>
+          <t>2025-04-29T14:36:21.782+0500</t>
         </is>
       </c>
       <c r="J245" t="inlineStr"/>
@@ -31905,7 +32063,7 @@
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -31926,47 +32084,47 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RLT-80</t>
+          <t>RLT-78</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>16 may 2025</t>
+          <t>Planned Leave 4th April 2025</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>RLT-5</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:34.680+0500</t>
+          <t>2025-04-29T14:36:42.933+0500</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:58.959+0500</t>
+          <t>2025-04-29T14:37:01.596+0500</t>
         </is>
       </c>
       <c r="J246" t="inlineStr"/>
@@ -31980,7 +32138,7 @@
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -32001,17 +32159,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>RLT-81</t>
+          <t>RLT-79</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Annual leave 22 May</t>
+          <t>Sick leave</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32036,12 +32194,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2025-05-21T17:45:49.062+0500</t>
+          <t>2025-05-15T10:52:44.037+0500</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:14.892+0500</t>
+          <t>2025-09-11T09:15:11.410+0500</t>
         </is>
       </c>
       <c r="J247" t="inlineStr"/>
@@ -32055,7 +32213,7 @@
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -32076,47 +32234,47 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>RLT-82</t>
+          <t>RLT-80</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Planned Leave 5th June 2025</t>
+          <t>16 may 2025</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-5</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2025-06-10T11:05:56.983+0500</t>
+          <t>2025-05-20T15:48:34.680+0500</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:20.879+0500</t>
+          <t>2025-05-20T15:48:58.959+0500</t>
         </is>
       </c>
       <c r="J248" t="inlineStr"/>
@@ -32130,7 +32288,7 @@
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -32151,17 +32309,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>RLT-83</t>
+          <t>RLT-81</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Annual leave 07 July</t>
+          <t>Annual leave 22 May</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32186,12 +32344,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2025-07-07T12:00:55.557+0500</t>
+          <t>2025-05-21T17:45:49.062+0500</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:19.601+0500</t>
+          <t>2025-09-11T09:15:14.892+0500</t>
         </is>
       </c>
       <c r="J249" t="inlineStr"/>
@@ -32226,47 +32384,47 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RLT-84</t>
+          <t>RLT-82</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Casual leave</t>
+          <t>Planned Leave 5th June 2025</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2025-09-11T09:14:17.734+0500</t>
+          <t>2025-06-10T11:05:56.983+0500</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:22.445+0500</t>
+          <t>2025-09-26T09:55:20.879+0500</t>
         </is>
       </c>
       <c r="J250" t="inlineStr"/>
@@ -32275,7 +32433,7 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr">
@@ -32284,7 +32442,7 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr">
@@ -32294,24 +32452,24 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>RLT-85</t>
+          <t>RLT-83</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Casual leave 10 sept 25</t>
+          <t>Annual leave 07 July</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32336,12 +32494,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:09.033+0500</t>
+          <t>2025-07-07T12:00:55.557+0500</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:45.168+0500</t>
+          <t>2025-09-11T09:15:19.601+0500</t>
         </is>
       </c>
       <c r="J251" t="inlineStr"/>
@@ -32376,47 +32534,47 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RLT-86</t>
+          <t>RLT-84</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Planned Leave 15th July 2025</t>
+          <t>Casual leave</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:06.810+0500</t>
+          <t>2025-09-11T09:14:17.734+0500</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:30.527+0500</t>
+          <t>2025-09-11T09:15:22.445+0500</t>
         </is>
       </c>
       <c r="J252" t="inlineStr"/>
@@ -32425,16 +32583,16 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P252" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr">
@@ -32444,54 +32602,54 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>RLT-87</t>
+          <t>RLT-85</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Planned 1st Sept 2025</t>
+          <t>Casual leave 10 sept 25</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2025-09-26T09:56:28.622+0500</t>
+          <t>2025-09-11T09:16:09.033+0500</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:11.707+0500</t>
+          <t>2025-09-11T09:16:45.168+0500</t>
         </is>
       </c>
       <c r="J253" t="inlineStr"/>
@@ -32505,7 +32663,7 @@
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -32526,17 +32684,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>RLT-88</t>
+          <t>RLT-86</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2025</t>
+          <t>Planned Leave 15th July 2025</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -32561,12 +32719,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:27.334+0500</t>
+          <t>2025-09-26T09:55:06.810+0500</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:46.408+0500</t>
+          <t>2025-09-26T09:55:30.527+0500</t>
         </is>
       </c>
       <c r="J254" t="inlineStr"/>
@@ -32601,22 +32759,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>RLT-89</t>
+          <t>RLT-87</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
+          <t>Planned 1st Sept 2025</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -32636,12 +32794,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2025-10-08T10:16:40.435+0500</t>
+          <t>2025-09-26T09:56:28.622+0500</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2025-11-06T09:37:59.818+0500</t>
+          <t>2025-09-26T10:05:11.707+0500</t>
         </is>
       </c>
       <c r="J255" t="inlineStr"/>
@@ -32650,7 +32808,7 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr">
@@ -32659,12 +32817,12 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S255" t="inlineStr">
@@ -32676,22 +32834,22 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RLT-90</t>
+          <t>RLT-88</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Planned Leave 5th Nov 2025</t>
+          <t>Planned Leave 15th Aug 2025</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -32711,12 +32869,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2025-11-06T09:38:11.154+0500</t>
+          <t>2025-09-26T10:05:27.334+0500</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:11.084+0500</t>
+          <t>2025-09-26T10:05:46.408+0500</t>
         </is>
       </c>
       <c r="J256" t="inlineStr"/>
@@ -32730,7 +32888,7 @@
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -32751,22 +32909,22 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>RLT-95</t>
+          <t>RLT-89</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>31542</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Sick Leave 18th Nov 2025</t>
+          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -32786,12 +32944,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:01.035+0500</t>
+          <t>2025-10-08T10:16:40.435+0500</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:30.413+0500</t>
+          <t>2025-11-06T09:37:59.818+0500</t>
         </is>
       </c>
       <c r="J257" t="inlineStr"/>
@@ -32800,7 +32958,7 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr">
@@ -32809,12 +32967,12 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S257" t="inlineStr">
@@ -32826,22 +32984,22 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>RLT-96</t>
+          <t>RLT-90</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
+          <t>Planned Leave 5th Nov 2025</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -32861,12 +33019,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:53.468+0500</t>
+          <t>2025-11-06T09:38:11.154+0500</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:21.845+0500</t>
+          <t>2025-12-08T11:30:11.084+0500</t>
         </is>
       </c>
       <c r="J258" t="inlineStr"/>
@@ -32875,21 +33033,21 @@
         <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P258" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S258" t="inlineStr">
@@ -32901,22 +33059,22 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>RLT-97</t>
+          <t>RLT-95</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>3rd Dec 2025</t>
+          <t>Sick Leave 18th Nov 2025</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -32936,12 +33094,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.693+0500</t>
+          <t>2025-12-08T11:30:01.035+0500</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2025-12-08T11:32:24.681+0500</t>
+          <t>2025-12-08T11:30:30.413+0500</t>
         </is>
       </c>
       <c r="J259" t="inlineStr"/>
@@ -32955,7 +33113,7 @@
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -32976,47 +33134,47 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>RLT-99</t>
+          <t>RLT-96</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Leave for one day 05-12-25</t>
+          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2025-12-29T12:28:16.268+0500</t>
+          <t>2025-12-08T11:30:53.468+0500</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>2025-12-29T12:29:46.783+0500</t>
+          <t>2025-12-08T11:31:21.845+0500</t>
         </is>
       </c>
       <c r="J260" t="inlineStr"/>
@@ -33025,24 +33183,174 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P260" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q260" t="inlineStr"/>
       <c r="R260" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S260" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>RLT-97</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>31546</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>3rd Dec 2025</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Planned Leave</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Hassan Saeed Wattoo</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>RLT-39</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Hassan Saeed Wattoo</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>2025-12-08T11:31:59.693+0500</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>2025-12-08T11:32:24.681+0500</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="n">
+        <v>0</v>
+      </c>
+      <c r="M261" t="n">
+        <v>8</v>
+      </c>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>RLT-99</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>32431</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Leave for one day 05-12-25</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Resolved!</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>RLT-35</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:28:16.268+0500</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:29:46.783+0500</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="n">
+        <v>0</v>
+      </c>
+      <c r="M262" t="n">
+        <v>8</v>
+      </c>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33059,7 +33367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38442,22 +38750,22 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-203</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-06T09:00:00.000+0500</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -38467,26 +38775,26 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-204</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-06T09:00:00.000+0500</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="218">
@@ -38502,7 +38810,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -38527,7 +38835,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -38552,7 +38860,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -38577,7 +38885,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -38602,7 +38910,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -38627,7 +38935,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -38652,7 +38960,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -38677,7 +38985,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -38702,7 +39010,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -38727,7 +39035,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -38752,7 +39060,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -38777,7 +39085,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -38802,7 +39110,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -38827,7 +39135,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -38852,7 +39160,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38867,17 +39175,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38892,17 +39200,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38927,7 +39235,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38952,7 +39260,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38977,7 +39285,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -39002,7 +39310,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39027,7 +39335,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39052,7 +39360,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39077,7 +39385,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39102,7 +39410,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39127,7 +39435,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39152,7 +39460,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -39177,7 +39485,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -39202,7 +39510,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -39227,7 +39535,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -39252,7 +39560,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -39277,7 +39585,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -39302,7 +39610,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -39327,7 +39635,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -39352,7 +39660,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -39377,7 +39685,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -39402,15 +39710,65 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Maria Sharafat</t>
-        </is>
-      </c>
-      <c r="E254" t="n">
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
         <v>8</v>
       </c>
     </row>
@@ -39575,10 +39933,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>22.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -39590,10 +39948,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>2.81</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -39668,10 +40026,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -39683,10 +40041,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -39951,7 +40309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40645,7 +41003,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -40667,19 +41025,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>RLT-192</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-192</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -40701,12 +41059,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-192</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-192</t>
         </is>
       </c>
     </row>
@@ -41495,7 +41853,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -41504,25 +41862,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-204</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-204</t>
         </is>
       </c>
     </row>
@@ -41534,7 +41892,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -41563,19 +41921,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -41585,12 +41943,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-203</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-203</t>
         </is>
       </c>
     </row>
@@ -41602,7 +41960,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -41636,7 +41994,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -41670,7 +42028,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -41704,7 +42062,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -41738,7 +42096,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -41772,7 +42130,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -41806,7 +42164,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -41840,7 +42198,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -41874,7 +42232,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -41908,7 +42266,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -41942,7 +42300,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -41976,7 +42334,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -42010,7 +42368,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -42044,7 +42402,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -42078,7 +42436,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -42112,7 +42470,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -42129,12 +42487,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
@@ -42146,7 +42504,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -42163,12 +42521,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
@@ -42180,7 +42538,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -42214,7 +42572,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -42248,7 +42606,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -42282,7 +42640,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -42316,7 +42674,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -42350,7 +42708,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -42384,7 +42742,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -42418,7 +42776,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -42452,7 +42810,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -42486,7 +42844,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -42520,7 +42878,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -42554,7 +42912,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -42588,7 +42946,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -42622,7 +42980,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -42656,7 +43014,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -42690,7 +43048,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -42724,7 +43082,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -42758,7 +43116,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -42792,7 +43150,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -42826,27 +43184,95 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>8</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>8</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>8</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C85" t="n">
-        <v>8</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>8</v>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="C87" t="n">
+        <v>8</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>8</v>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>RLT-173</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
         </is>
@@ -42863,7 +43289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43102,7 +43528,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -43111,7 +43537,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -43141,16 +43567,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-W09</t>
+          <t>2026-W08</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -43159,13 +43585,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -43174,22 +43600,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -43201,19 +43627,19 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sarmad Sabir</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -43225,43 +43651,43 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Sarmad Sabir</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-W10</t>
+          <t>2026-W09</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -43270,22 +43696,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -43294,7 +43720,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.5</v>
+        <v>40</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -43303,13 +43729,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>6.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -43333,7 +43759,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -43342,64 +43768,64 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-W11</t>
+          <t>2026-W10</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-W12</t>
+          <t>2026-W10</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -43410,7 +43836,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-W13</t>
+          <t>2026-W11</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -43434,7 +43860,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W12</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -43458,7 +43884,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W13</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -43482,7 +43908,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -43506,7 +43932,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -43530,19 +43956,67 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>40</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>40</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>2026-W18</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C30" t="n">
         <v>32</v>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
         <v>32</v>
       </c>
     </row>
@@ -43557,7 +44031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43628,7 +44102,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -43637,7 +44111,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -43667,7 +44141,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -43676,22 +44150,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -43703,19 +44177,19 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>6.5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sarmad Sabir</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -43727,19 +44201,19 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Sarmad Sabir</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -43748,22 +44222,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Waqar Rasheed</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -43772,7 +44246,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -43781,37 +44255,37 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Waqar Rasheed</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -43820,22 +44294,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>176</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -43844,7 +44318,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.5</v>
+        <v>176</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -43853,13 +44327,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>6.5</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -43883,7 +44357,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -43892,39 +44366,87 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Taimur Zahid</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C17" t="n">
         <v>176</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>176</v>
       </c>
     </row>

--- a/rlt_leave_report.xlsx
+++ b/rlt_leave_report.xlsx
@@ -7099,7 +7099,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7124,13 +7124,13 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-03-07T13:23:13.421+0500</t>
+          <t>2026-03-09T13:34:46.951+0500</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M86" t="n">
         <v>8</v>
@@ -28941,7 +28941,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -28966,13 +28966,13 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>2026-03-07T13:23:13.421+0500</t>
+          <t>2026-03-09T13:34:46.951+0500</t>
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M204" t="n">
         <v>8</v>

--- a/rlt_leave_report.xlsx
+++ b/rlt_leave_report.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S153"/>
+  <dimension ref="A1:S154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9599,77 +9599,77 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>RLT-43</t>
+          <t>RLT-218</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>40546</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Planned Leave 15th May 2024</t>
+          <t>Sick Leave March 16, 2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-11</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2024-05-15T13:17:36.997+0500</t>
+          <t>2026-03-18T09:24:00.476+0500</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:48.485+0500</t>
+          <t>2026-03-18T09:28:18.821+0500</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M111" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -9686,82 +9686,82 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RLT-44</t>
+          <t>RLT-43</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Leaves Faiza</t>
+          <t>Planned Leave 15th May 2024</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-05-27T17:19:47.991+0500</t>
+          <t>2024-05-15T13:17:36.997+0500</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2025-12-30T10:15:12.915+0500</t>
+          <t>2024-08-16T16:28:48.485+0500</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -9773,70 +9773,82 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RLT-45</t>
+          <t>RLT-44</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Leave for one day 05-06-24</t>
+          <t>Leaves Faiza</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2024-06-06T09:10:07.974+0500</t>
+          <t>2024-05-27T17:19:47.991+0500</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2024-06-06T09:11:39.142+0500</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+          <t>2025-12-30T10:15:12.915+0500</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q113" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -9848,47 +9860,47 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RLT-46</t>
+          <t>RLT-45</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Planned Leave 20th June 2024</t>
+          <t>Leave for one day 05-06-24</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-06-21T09:20:21.600+0500</t>
+          <t>2024-06-06T09:10:07.974+0500</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:56.168+0500</t>
+          <t>2024-06-06T09:11:39.142+0500</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -9902,7 +9914,7 @@
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -9923,47 +9935,47 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RLT-47</t>
+          <t>RLT-46</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Leave for two days 20 and 21-06-24</t>
+          <t>Planned Leave 20th June 2024</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2024-06-24T09:18:18.735+0500</t>
+          <t>2024-06-21T09:20:21.600+0500</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2024-06-24T09:19:43.343+0500</t>
+          <t>2024-08-16T16:28:56.168+0500</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -9972,21 +9984,21 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -9998,75 +10010,67 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RLT-49</t>
+          <t>RLT-47</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Emergency leave</t>
+          <t>Leave for two days 20 and 21-06-24</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2024-07-18T11:05:11.868+0500</t>
+          <t>2024-06-24T09:18:18.735+0500</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-01-29T16:48:09.549+0500</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
+          <t>2024-06-24T09:19:43.343+0500</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10081,56 +10085,60 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RLT-50</t>
+          <t>RLT-49</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sick leave for one day 22-07-24</t>
+          <t>Emergency leave</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-07-23T09:08:09.289+0500</t>
+          <t>2024-07-18T11:05:11.868+0500</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2024-07-23T09:09:17.479+0500</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr"/>
+          <t>2026-01-29T16:48:09.549+0500</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
@@ -10139,12 +10147,16 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q117" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -10156,17 +10168,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RLT-52</t>
+          <t>RLT-50</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Urgent work leave 05-08-24</t>
+          <t>Sick leave for one day 22-07-24</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10191,12 +10203,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-08-06T09:08:48.315+0500</t>
+          <t>2024-07-23T09:08:09.289+0500</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2024-08-06T09:11:15.823+0500</t>
+          <t>2024-07-23T09:09:17.479+0500</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -10210,7 +10222,7 @@
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -10231,47 +10243,47 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RLT-53</t>
+          <t>RLT-52</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2024</t>
+          <t>Urgent work leave 05-08-24</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:43.991+0500</t>
+          <t>2024-08-06T09:08:48.315+0500</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2024-08-16T16:29:17.981+0500</t>
+          <t>2024-08-06T09:11:15.823+0500</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -10285,7 +10297,7 @@
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -10306,47 +10318,47 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RLT-54</t>
+          <t>RLT-53</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Leave for one day 30-08-24</t>
+          <t>Planned Leave 15th Aug 2024</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:09.454+0500</t>
+          <t>2024-08-16T16:28:43.991+0500</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2024-09-03T09:15:53.284+0500</t>
+          <t>2024-08-16T16:29:17.981+0500</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -10360,7 +10372,7 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -10381,17 +10393,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RLT-55</t>
+          <t>RLT-54</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Leave for one day 02-09-24</t>
+          <t>Leave for one day 30-08-24</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10416,12 +10428,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:29.824+0500</t>
+          <t>2024-08-28T16:51:09.454+0500</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2024-09-03T09:16:12.471+0500</t>
+          <t>2024-09-03T09:15:53.284+0500</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -10456,47 +10468,47 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RLT-56</t>
+          <t>RLT-55</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sick leave 28th Aug 2024</t>
+          <t>Leave for one day 02-09-24</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2024-09-03T10:03:57.925+0500</t>
+          <t>2024-08-28T16:51:29.824+0500</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2024-09-03T10:04:14.562+0500</t>
+          <t>2024-09-03T09:16:12.471+0500</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -10510,7 +10522,7 @@
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -10531,17 +10543,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RLT-57</t>
+          <t>RLT-56</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sick Leave 13th Sept 2024</t>
+          <t>Sick leave 28th Aug 2024</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10566,12 +10578,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2024-09-23T11:07:49.200+0500</t>
+          <t>2024-09-03T10:03:57.925+0500</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2024-09-23T11:08:09.638+0500</t>
+          <t>2024-09-03T10:04:14.562+0500</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -10606,47 +10618,47 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RLT-58</t>
+          <t>RLT-57</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Leave for one day 14-11-24</t>
+          <t>Sick Leave 13th Sept 2024</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2024-11-15T09:25:05.670+0500</t>
+          <t>2024-09-23T11:07:49.200+0500</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2024-11-15T09:38:06.205+0500</t>
+          <t>2024-09-23T11:08:09.638+0500</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -10660,7 +10672,7 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -10681,47 +10693,47 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RLT-59</t>
+          <t>RLT-58</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Planned Leave 8th Nov 2024</t>
+          <t>Leave for one day 14-11-24</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2024-11-21T12:24:36.990+0500</t>
+          <t>2024-11-15T09:25:05.670+0500</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:57.134+0500</t>
+          <t>2024-11-15T09:38:06.205+0500</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -10730,16 +10742,16 @@
         <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr">
@@ -10749,24 +10761,24 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RLT-60</t>
+          <t>RLT-59</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Planned Leave 19th Nov 2024</t>
+          <t>Planned Leave 8th Nov 2024</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10791,12 +10803,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2024-11-21T12:25:03.206+0500</t>
+          <t>2024-11-21T12:24:36.990+0500</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:07.591+0500</t>
+          <t>2024-12-31T11:38:57.134+0500</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -10805,7 +10817,7 @@
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
@@ -10814,7 +10826,7 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
@@ -10824,54 +10836,54 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RLT-62</t>
+          <t>RLT-60</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sick leave for one day 30-12-24</t>
+          <t>Planned Leave 19th Nov 2024</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:13.907+0500</t>
+          <t>2024-11-21T12:25:03.206+0500</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:33.151+0500</t>
+          <t>2024-12-31T11:39:07.591+0500</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -10885,7 +10897,7 @@
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -10906,47 +10918,47 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RLT-63</t>
+          <t>RLT-62</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Planned Leave 29th Nov 2024</t>
+          <t>Sick leave for one day 30-12-24</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:18.228+0500</t>
+          <t>2024-12-31T09:30:13.907+0500</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:11.165+0500</t>
+          <t>2024-12-31T09:30:33.151+0500</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -10960,7 +10972,7 @@
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -10981,17 +10993,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RLT-64</t>
+          <t>RLT-63</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Planned Leave 16th Dec 2024</t>
+          <t>Planned Leave 29th Nov 2024</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11016,12 +11028,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:25.533+0500</t>
+          <t>2024-12-31T11:38:18.228+0500</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:27.662+0500</t>
+          <t>2024-12-31T11:39:11.165+0500</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -11056,17 +11068,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RLT-65</t>
+          <t>RLT-64</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
+          <t>Planned Leave 16th Dec 2024</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11091,12 +11103,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2024-12-31T11:40:34.525+0500</t>
+          <t>2024-12-31T11:39:25.533+0500</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:36.616+0500</t>
+          <t>2025-03-25T09:09:27.662+0500</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -11105,7 +11117,7 @@
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
@@ -11114,12 +11126,12 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -11131,47 +11143,47 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RLT-67</t>
+          <t>RLT-65</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Casual Leave for half day 02-01-25</t>
+          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2025-01-06T09:19:42.013+0500</t>
+          <t>2024-12-31T11:40:34.525+0500</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:11.598+0500</t>
+          <t>2025-03-25T09:09:36.616+0500</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -11180,7 +11192,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
@@ -11189,12 +11201,12 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -11206,17 +11218,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RLT-68</t>
+          <t>RLT-67</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Leave for one day 03-01-25</t>
+          <t>Casual Leave for half day 02-01-25</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11241,12 +11253,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2025-01-06T09:20:06.483+0500</t>
+          <t>2025-01-06T09:19:42.013+0500</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:08.280+0500</t>
+          <t>2025-01-06T09:21:11.598+0500</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -11255,16 +11267,16 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P132" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
@@ -11281,17 +11293,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RLT-71</t>
+          <t>RLT-68</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Leave for one day 27-02-25</t>
+          <t>Leave for one day 03-01-25</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11316,12 +11328,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:26.122+0500</t>
+          <t>2025-01-06T09:20:06.483+0500</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:46.578+0500</t>
+          <t>2025-01-06T09:21:08.280+0500</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -11356,17 +11368,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RLT-72</t>
+          <t>RLT-71</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Annual leave 31 Jan</t>
+          <t>Leave for one day 27-02-25</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11376,27 +11388,27 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:16.894+0500</t>
+          <t>2025-02-28T09:31:26.122+0500</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:47.087+0500</t>
+          <t>2025-02-28T09:31:46.578+0500</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -11410,7 +11422,7 @@
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -11431,47 +11443,47 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RLT-74</t>
+          <t>RLT-72</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Planned Leave 21st Feb 2025</t>
+          <t>Annual leave 31 Jan</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:51.777+0500</t>
+          <t>2025-03-04T11:51:16.894+0500</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:06.523+0500</t>
+          <t>2025-03-04T11:51:47.087+0500</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -11506,17 +11518,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RLT-77</t>
+          <t>RLT-74</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Planned Leave 3rd April 2025</t>
+          <t>Planned Leave 21st Feb 2025</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11541,12 +11553,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-04-29T14:35:54.729+0500</t>
+          <t>2025-03-25T09:09:51.777+0500</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:21.782+0500</t>
+          <t>2025-04-29T14:36:06.523+0500</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
@@ -11581,17 +11593,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RLT-78</t>
+          <t>RLT-77</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Planned Leave 4th April 2025</t>
+          <t>Planned Leave 3rd April 2025</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -11616,12 +11628,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:42.933+0500</t>
+          <t>2025-04-29T14:35:54.729+0500</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2025-04-29T14:37:01.596+0500</t>
+          <t>2025-04-29T14:36:21.782+0500</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -11656,47 +11668,47 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RLT-79</t>
+          <t>RLT-78</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Sick leave</t>
+          <t>Planned Leave 4th April 2025</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2025-05-15T10:52:44.037+0500</t>
+          <t>2025-04-29T14:36:42.933+0500</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:11.410+0500</t>
+          <t>2025-04-29T14:37:01.596+0500</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -11710,7 +11722,7 @@
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -11731,59 +11743,51 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RLT-80</t>
+          <t>RLT-79</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>16 may 2025</t>
+          <t>Sick leave</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>RLT-5</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:34.680+0500</t>
+          <t>2025-05-15T10:52:44.037+0500</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:58.959+0500</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
+          <t>2025-09-11T09:15:11.410+0500</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="n">
         <v>0</v>
       </c>
@@ -11799,11 +11803,7 @@
       <c r="P139" t="n">
         <v>8</v>
       </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
+      <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr">
         <is>
           <t>No</t>
@@ -11818,51 +11818,59 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RLT-81</t>
+          <t>RLT-80</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Annual leave 22 May</t>
+          <t>16 may 2025</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2025-05-21T17:45:49.062+0500</t>
+          <t>2025-05-20T15:48:34.680+0500</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:14.892+0500</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>2025-05-20T15:48:58.959+0500</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
       <c r="L140" t="n">
         <v>0</v>
       </c>
@@ -11872,13 +11880,17 @@
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P140" t="n">
         <v>8</v>
       </c>
-      <c r="Q140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
       <c r="R140" t="inlineStr">
         <is>
           <t>No</t>
@@ -11893,47 +11905,47 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RLT-82</t>
+          <t>RLT-81</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Planned Leave 5th June 2025</t>
+          <t>Annual leave 22 May</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2025-06-10T11:05:56.983+0500</t>
+          <t>2025-05-21T17:45:49.062+0500</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:20.879+0500</t>
+          <t>2025-09-11T09:15:14.892+0500</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
@@ -11968,47 +11980,47 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RLT-83</t>
+          <t>RLT-82</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual leave 07 July</t>
+          <t>Planned Leave 5th June 2025</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2025-07-07T12:00:55.557+0500</t>
+          <t>2025-06-10T11:05:56.983+0500</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:19.601+0500</t>
+          <t>2025-09-26T09:55:20.879+0500</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
@@ -12043,17 +12055,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RLT-84</t>
+          <t>RLT-83</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Casual leave</t>
+          <t>Annual leave 07 July</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12078,12 +12090,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2025-09-11T09:14:17.734+0500</t>
+          <t>2025-07-07T12:00:55.557+0500</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:22.445+0500</t>
+          <t>2025-09-11T09:15:19.601+0500</t>
         </is>
       </c>
       <c r="J143" t="inlineStr"/>
@@ -12092,7 +12104,7 @@
         <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
@@ -12101,7 +12113,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr">
@@ -12111,24 +12123,24 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RLT-85</t>
+          <t>RLT-84</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Casual leave 10 sept 25</t>
+          <t>Casual leave</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12153,12 +12165,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:09.033+0500</t>
+          <t>2025-09-11T09:14:17.734+0500</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:45.168+0500</t>
+          <t>2025-09-11T09:15:22.445+0500</t>
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
@@ -12167,7 +12179,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
@@ -12176,7 +12188,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr">
@@ -12186,54 +12198,54 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RLT-86</t>
+          <t>RLT-85</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Planned Leave 15th July 2025</t>
+          <t>Casual leave 10 sept 25</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:06.810+0500</t>
+          <t>2025-09-11T09:16:09.033+0500</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:30.527+0500</t>
+          <t>2025-09-11T09:16:45.168+0500</t>
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
@@ -12247,7 +12259,7 @@
       <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -12268,17 +12280,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RLT-87</t>
+          <t>RLT-86</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Planned 1st Sept 2025</t>
+          <t>Planned Leave 15th July 2025</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12303,12 +12315,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2025-09-26T09:56:28.622+0500</t>
+          <t>2025-09-26T09:55:06.810+0500</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:11.707+0500</t>
+          <t>2025-09-26T09:55:30.527+0500</t>
         </is>
       </c>
       <c r="J146" t="inlineStr"/>
@@ -12343,17 +12355,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RLT-88</t>
+          <t>RLT-87</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2025</t>
+          <t>Planned 1st Sept 2025</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12378,12 +12390,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:27.334+0500</t>
+          <t>2025-09-26T09:56:28.622+0500</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:46.408+0500</t>
+          <t>2025-09-26T10:05:11.707+0500</t>
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
@@ -12418,22 +12430,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RLT-89</t>
+          <t>RLT-88</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
+          <t>Planned Leave 15th Aug 2025</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -12453,12 +12465,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2025-10-08T10:16:40.435+0500</t>
+          <t>2025-09-26T10:05:27.334+0500</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2025-11-06T09:37:59.818+0500</t>
+          <t>2025-09-26T10:05:46.408+0500</t>
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
@@ -12467,7 +12479,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
@@ -12476,12 +12488,12 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -12493,22 +12505,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RLT-90</t>
+          <t>RLT-89</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Planned Leave 5th Nov 2025</t>
+          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -12528,12 +12540,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2025-11-06T09:38:11.154+0500</t>
+          <t>2025-10-08T10:16:40.435+0500</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:11.084+0500</t>
+          <t>2025-11-06T09:37:59.818+0500</t>
         </is>
       </c>
       <c r="J149" t="inlineStr"/>
@@ -12542,21 +12554,21 @@
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -12568,22 +12580,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RLT-95</t>
+          <t>RLT-90</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>31542</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sick Leave 18th Nov 2025</t>
+          <t>Planned Leave 5th Nov 2025</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -12603,12 +12615,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:01.035+0500</t>
+          <t>2025-11-06T09:38:11.154+0500</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:30.413+0500</t>
+          <t>2025-12-08T11:30:11.084+0500</t>
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
@@ -12622,7 +12634,7 @@
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -12643,22 +12655,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RLT-96</t>
+          <t>RLT-95</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
+          <t>Sick Leave 18th Nov 2025</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -12678,12 +12690,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:53.468+0500</t>
+          <t>2025-12-08T11:30:01.035+0500</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:21.845+0500</t>
+          <t>2025-12-08T11:30:30.413+0500</t>
         </is>
       </c>
       <c r="J151" t="inlineStr"/>
@@ -12692,7 +12704,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
@@ -12701,12 +12713,12 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -12718,22 +12730,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RLT-97</t>
+          <t>RLT-96</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>3rd Dec 2025</t>
+          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -12753,12 +12765,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.693+0500</t>
+          <t>2025-12-08T11:30:53.468+0500</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2025-12-08T11:32:24.681+0500</t>
+          <t>2025-12-08T11:31:21.845+0500</t>
         </is>
       </c>
       <c r="J152" t="inlineStr"/>
@@ -12767,21 +12779,21 @@
         <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -12793,47 +12805,47 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>RLT-99</t>
+          <t>RLT-97</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Leave for one day 05-12-25</t>
+          <t>3rd Dec 2025</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2025-12-29T12:28:16.268+0500</t>
+          <t>2025-12-08T11:31:59.693+0500</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2025-12-29T12:29:46.783+0500</t>
+          <t>2025-12-08T11:32:24.681+0500</t>
         </is>
       </c>
       <c r="J153" t="inlineStr"/>
@@ -12847,7 +12859,7 @@
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -12860,6 +12872,81 @@
         </is>
       </c>
       <c r="S153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>RLT-99</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>32431</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Leave for one day 05-12-25</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Resolved!</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>RLT-35</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:28:16.268+0500</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:29:46.783+0500</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>8</v>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -12876,7 +12963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S271"/>
+  <dimension ref="A1:S272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32320,77 +32407,77 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RLT-43</t>
+          <t>RLT-218</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>40546</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Planned Leave 15th May 2024</t>
+          <t>Sick Leave March 16, 2026</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-11</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>2024-05-15T13:17:36.997+0500</t>
+          <t>2026-03-18T09:24:00.476+0500</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:48.485+0500</t>
+          <t>2026-03-18T09:28:18.821+0500</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M229" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="R229" t="inlineStr">
@@ -32407,82 +32494,82 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RLT-44</t>
+          <t>RLT-43</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Leaves Faiza</t>
+          <t>Planned Leave 15th May 2024</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2024-05-27T17:19:47.991+0500</t>
+          <t>2024-05-15T13:17:36.997+0500</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2025-12-30T10:15:12.915+0500</t>
+          <t>2024-08-16T16:28:48.485+0500</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="L230" t="n">
         <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P230" t="n">
-        <v>136</v>
+        <v>8</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S230" t="inlineStr">
@@ -32494,70 +32581,82 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RLT-45</t>
+          <t>RLT-44</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Leave for one day 05-06-24</t>
+          <t>Leaves Faiza</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2024-06-06T09:10:07.974+0500</t>
+          <t>2024-05-27T17:19:47.991+0500</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2024-06-06T09:11:39.142+0500</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
+          <t>2025-12-30T10:15:12.915+0500</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
       <c r="L231" t="n">
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q231" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -32569,47 +32668,47 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RLT-46</t>
+          <t>RLT-45</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Planned Leave 20th June 2024</t>
+          <t>Leave for one day 05-06-24</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2024-06-21T09:20:21.600+0500</t>
+          <t>2024-06-06T09:10:07.974+0500</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:56.168+0500</t>
+          <t>2024-06-06T09:11:39.142+0500</t>
         </is>
       </c>
       <c r="J232" t="inlineStr"/>
@@ -32623,7 +32722,7 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -32644,47 +32743,47 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>RLT-47</t>
+          <t>RLT-46</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Leave for two days 20 and 21-06-24</t>
+          <t>Planned Leave 20th June 2024</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2024-06-24T09:18:18.735+0500</t>
+          <t>2024-06-21T09:20:21.600+0500</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2024-06-24T09:19:43.343+0500</t>
+          <t>2024-08-16T16:28:56.168+0500</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
@@ -32693,21 +32792,21 @@
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P233" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
@@ -32719,75 +32818,67 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RLT-49</t>
+          <t>RLT-47</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Emergency leave</t>
+          <t>Leave for two days 20 and 21-06-24</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2024-07-18T11:05:11.868+0500</t>
+          <t>2024-06-24T09:18:18.735+0500</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2026-01-29T16:48:09.549+0500</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
+          <t>2024-06-24T09:19:43.343+0500</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="n">
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P234" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -32802,56 +32893,60 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>RLT-50</t>
+          <t>RLT-49</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Sick leave for one day 22-07-24</t>
+          <t>Emergency leave</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2024-07-23T09:08:09.289+0500</t>
+          <t>2024-07-18T11:05:11.868+0500</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2024-07-23T09:09:17.479+0500</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr"/>
+          <t>2026-01-29T16:48:09.549+0500</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="n">
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
@@ -32860,12 +32955,16 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q235" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
@@ -32877,17 +32976,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RLT-52</t>
+          <t>RLT-50</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Urgent work leave 05-08-24</t>
+          <t>Sick leave for one day 22-07-24</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -32912,12 +33011,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2024-08-06T09:08:48.315+0500</t>
+          <t>2024-07-23T09:08:09.289+0500</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2024-08-06T09:11:15.823+0500</t>
+          <t>2024-07-23T09:09:17.479+0500</t>
         </is>
       </c>
       <c r="J236" t="inlineStr"/>
@@ -32931,7 +33030,7 @@
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -32952,47 +33051,47 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RLT-53</t>
+          <t>RLT-52</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2024</t>
+          <t>Urgent work leave 05-08-24</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:43.991+0500</t>
+          <t>2024-08-06T09:08:48.315+0500</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2024-08-16T16:29:17.981+0500</t>
+          <t>2024-08-06T09:11:15.823+0500</t>
         </is>
       </c>
       <c r="J237" t="inlineStr"/>
@@ -33006,7 +33105,7 @@
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -33027,47 +33126,47 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>RLT-54</t>
+          <t>RLT-53</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Leave for one day 30-08-24</t>
+          <t>Planned Leave 15th Aug 2024</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:09.454+0500</t>
+          <t>2024-08-16T16:28:43.991+0500</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2024-09-03T09:15:53.284+0500</t>
+          <t>2024-08-16T16:29:17.981+0500</t>
         </is>
       </c>
       <c r="J238" t="inlineStr"/>
@@ -33081,7 +33180,7 @@
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -33102,17 +33201,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>RLT-55</t>
+          <t>RLT-54</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Leave for one day 02-09-24</t>
+          <t>Leave for one day 30-08-24</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -33137,12 +33236,12 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:29.824+0500</t>
+          <t>2024-08-28T16:51:09.454+0500</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2024-09-03T09:16:12.471+0500</t>
+          <t>2024-09-03T09:15:53.284+0500</t>
         </is>
       </c>
       <c r="J239" t="inlineStr"/>
@@ -33177,47 +33276,47 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>RLT-56</t>
+          <t>RLT-55</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Sick leave 28th Aug 2024</t>
+          <t>Leave for one day 02-09-24</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2024-09-03T10:03:57.925+0500</t>
+          <t>2024-08-28T16:51:29.824+0500</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2024-09-03T10:04:14.562+0500</t>
+          <t>2024-09-03T09:16:12.471+0500</t>
         </is>
       </c>
       <c r="J240" t="inlineStr"/>
@@ -33231,7 +33330,7 @@
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -33252,17 +33351,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>RLT-57</t>
+          <t>RLT-56</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Sick Leave 13th Sept 2024</t>
+          <t>Sick leave 28th Aug 2024</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -33287,12 +33386,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2024-09-23T11:07:49.200+0500</t>
+          <t>2024-09-03T10:03:57.925+0500</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2024-09-23T11:08:09.638+0500</t>
+          <t>2024-09-03T10:04:14.562+0500</t>
         </is>
       </c>
       <c r="J241" t="inlineStr"/>
@@ -33327,47 +33426,47 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>RLT-58</t>
+          <t>RLT-57</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Leave for one day 14-11-24</t>
+          <t>Sick Leave 13th Sept 2024</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2024-11-15T09:25:05.670+0500</t>
+          <t>2024-09-23T11:07:49.200+0500</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2024-11-15T09:38:06.205+0500</t>
+          <t>2024-09-23T11:08:09.638+0500</t>
         </is>
       </c>
       <c r="J242" t="inlineStr"/>
@@ -33381,7 +33480,7 @@
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -33402,47 +33501,47 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>RLT-59</t>
+          <t>RLT-58</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Planned Leave 8th Nov 2024</t>
+          <t>Leave for one day 14-11-24</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2024-11-21T12:24:36.990+0500</t>
+          <t>2024-11-15T09:25:05.670+0500</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:57.134+0500</t>
+          <t>2024-11-15T09:38:06.205+0500</t>
         </is>
       </c>
       <c r="J243" t="inlineStr"/>
@@ -33451,16 +33550,16 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q243" t="inlineStr"/>
       <c r="R243" t="inlineStr">
@@ -33470,24 +33569,24 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>RLT-60</t>
+          <t>RLT-59</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Planned Leave 19th Nov 2024</t>
+          <t>Planned Leave 8th Nov 2024</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -33512,12 +33611,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2024-11-21T12:25:03.206+0500</t>
+          <t>2024-11-21T12:24:36.990+0500</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:07.591+0500</t>
+          <t>2024-12-31T11:38:57.134+0500</t>
         </is>
       </c>
       <c r="J244" t="inlineStr"/>
@@ -33526,7 +33625,7 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr">
@@ -33535,7 +33634,7 @@
         </is>
       </c>
       <c r="P244" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q244" t="inlineStr"/>
       <c r="R244" t="inlineStr">
@@ -33545,54 +33644,54 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>RLT-62</t>
+          <t>RLT-60</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Sick leave for one day 30-12-24</t>
+          <t>Planned Leave 19th Nov 2024</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:13.907+0500</t>
+          <t>2024-11-21T12:25:03.206+0500</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:33.151+0500</t>
+          <t>2024-12-31T11:39:07.591+0500</t>
         </is>
       </c>
       <c r="J245" t="inlineStr"/>
@@ -33606,7 +33705,7 @@
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -33627,47 +33726,47 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RLT-63</t>
+          <t>RLT-62</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Planned Leave 29th Nov 2024</t>
+          <t>Sick leave for one day 30-12-24</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:18.228+0500</t>
+          <t>2024-12-31T09:30:13.907+0500</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:11.165+0500</t>
+          <t>2024-12-31T09:30:33.151+0500</t>
         </is>
       </c>
       <c r="J246" t="inlineStr"/>
@@ -33681,7 +33780,7 @@
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -33702,17 +33801,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>RLT-64</t>
+          <t>RLT-63</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Planned Leave 16th Dec 2024</t>
+          <t>Planned Leave 29th Nov 2024</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -33737,12 +33836,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:25.533+0500</t>
+          <t>2024-12-31T11:38:18.228+0500</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:27.662+0500</t>
+          <t>2024-12-31T11:39:11.165+0500</t>
         </is>
       </c>
       <c r="J247" t="inlineStr"/>
@@ -33777,17 +33876,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>RLT-65</t>
+          <t>RLT-64</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
+          <t>Planned Leave 16th Dec 2024</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -33812,12 +33911,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2024-12-31T11:40:34.525+0500</t>
+          <t>2024-12-31T11:39:25.533+0500</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:36.616+0500</t>
+          <t>2025-03-25T09:09:27.662+0500</t>
         </is>
       </c>
       <c r="J248" t="inlineStr"/>
@@ -33826,7 +33925,7 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr">
@@ -33835,12 +33934,12 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S248" t="inlineStr">
@@ -33852,47 +33951,47 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>RLT-67</t>
+          <t>RLT-65</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Casual Leave for half day 02-01-25</t>
+          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2025-01-06T09:19:42.013+0500</t>
+          <t>2024-12-31T11:40:34.525+0500</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:11.598+0500</t>
+          <t>2025-03-25T09:09:36.616+0500</t>
         </is>
       </c>
       <c r="J249" t="inlineStr"/>
@@ -33901,7 +34000,7 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr">
@@ -33910,12 +34009,12 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
@@ -33927,17 +34026,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RLT-68</t>
+          <t>RLT-67</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Leave for one day 03-01-25</t>
+          <t>Casual Leave for half day 02-01-25</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -33962,12 +34061,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2025-01-06T09:20:06.483+0500</t>
+          <t>2025-01-06T09:19:42.013+0500</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:08.280+0500</t>
+          <t>2025-01-06T09:21:11.598+0500</t>
         </is>
       </c>
       <c r="J250" t="inlineStr"/>
@@ -33976,16 +34075,16 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P250" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr">
@@ -34002,17 +34101,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>RLT-71</t>
+          <t>RLT-68</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Leave for one day 27-02-25</t>
+          <t>Leave for one day 03-01-25</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -34037,12 +34136,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:26.122+0500</t>
+          <t>2025-01-06T09:20:06.483+0500</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:46.578+0500</t>
+          <t>2025-01-06T09:21:08.280+0500</t>
         </is>
       </c>
       <c r="J251" t="inlineStr"/>
@@ -34077,17 +34176,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RLT-72</t>
+          <t>RLT-71</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual leave 31 Jan</t>
+          <t>Leave for one day 27-02-25</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -34097,27 +34196,27 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:16.894+0500</t>
+          <t>2025-02-28T09:31:26.122+0500</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:47.087+0500</t>
+          <t>2025-02-28T09:31:46.578+0500</t>
         </is>
       </c>
       <c r="J252" t="inlineStr"/>
@@ -34131,7 +34230,7 @@
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -34152,47 +34251,47 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>RLT-74</t>
+          <t>RLT-72</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Planned Leave 21st Feb 2025</t>
+          <t>Annual leave 31 Jan</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:51.777+0500</t>
+          <t>2025-03-04T11:51:16.894+0500</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:06.523+0500</t>
+          <t>2025-03-04T11:51:47.087+0500</t>
         </is>
       </c>
       <c r="J253" t="inlineStr"/>
@@ -34227,17 +34326,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>RLT-77</t>
+          <t>RLT-74</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Planned Leave 3rd April 2025</t>
+          <t>Planned Leave 21st Feb 2025</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -34262,12 +34361,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2025-04-29T14:35:54.729+0500</t>
+          <t>2025-03-25T09:09:51.777+0500</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:21.782+0500</t>
+          <t>2025-04-29T14:36:06.523+0500</t>
         </is>
       </c>
       <c r="J254" t="inlineStr"/>
@@ -34302,17 +34401,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>RLT-78</t>
+          <t>RLT-77</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Planned Leave 4th April 2025</t>
+          <t>Planned Leave 3rd April 2025</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -34337,12 +34436,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:42.933+0500</t>
+          <t>2025-04-29T14:35:54.729+0500</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2025-04-29T14:37:01.596+0500</t>
+          <t>2025-04-29T14:36:21.782+0500</t>
         </is>
       </c>
       <c r="J255" t="inlineStr"/>
@@ -34377,47 +34476,47 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RLT-79</t>
+          <t>RLT-78</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Sick leave</t>
+          <t>Planned Leave 4th April 2025</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2025-05-15T10:52:44.037+0500</t>
+          <t>2025-04-29T14:36:42.933+0500</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:11.410+0500</t>
+          <t>2025-04-29T14:37:01.596+0500</t>
         </is>
       </c>
       <c r="J256" t="inlineStr"/>
@@ -34431,7 +34530,7 @@
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -34452,59 +34551,51 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>RLT-80</t>
+          <t>RLT-79</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>16 may 2025</t>
+          <t>Sick leave</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>RLT-5</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:34.680+0500</t>
+          <t>2025-05-15T10:52:44.037+0500</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:58.959+0500</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
+          <t>2025-09-11T09:15:11.410+0500</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
       <c r="L257" t="n">
         <v>0</v>
       </c>
@@ -34520,11 +34611,7 @@
       <c r="P257" t="n">
         <v>8</v>
       </c>
-      <c r="Q257" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
+      <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr">
         <is>
           <t>No</t>
@@ -34539,51 +34626,59 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>RLT-81</t>
+          <t>RLT-80</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Annual leave 22 May</t>
+          <t>16 may 2025</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-5</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2025-05-21T17:45:49.062+0500</t>
+          <t>2025-05-20T15:48:34.680+0500</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:14.892+0500</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
+          <t>2025-05-20T15:48:58.959+0500</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
       <c r="L258" t="n">
         <v>0</v>
       </c>
@@ -34593,13 +34688,17 @@
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P258" t="n">
         <v>8</v>
       </c>
-      <c r="Q258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
       <c r="R258" t="inlineStr">
         <is>
           <t>No</t>
@@ -34614,47 +34713,47 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>RLT-82</t>
+          <t>RLT-81</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Planned Leave 5th June 2025</t>
+          <t>Annual leave 22 May</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2025-06-10T11:05:56.983+0500</t>
+          <t>2025-05-21T17:45:49.062+0500</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:20.879+0500</t>
+          <t>2025-09-11T09:15:14.892+0500</t>
         </is>
       </c>
       <c r="J259" t="inlineStr"/>
@@ -34689,47 +34788,47 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>RLT-83</t>
+          <t>RLT-82</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annual leave 07 July</t>
+          <t>Planned Leave 5th June 2025</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2025-07-07T12:00:55.557+0500</t>
+          <t>2025-06-10T11:05:56.983+0500</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:19.601+0500</t>
+          <t>2025-09-26T09:55:20.879+0500</t>
         </is>
       </c>
       <c r="J260" t="inlineStr"/>
@@ -34764,17 +34863,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>RLT-84</t>
+          <t>RLT-83</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Casual leave</t>
+          <t>Annual leave 07 July</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34799,12 +34898,12 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2025-09-11T09:14:17.734+0500</t>
+          <t>2025-07-07T12:00:55.557+0500</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:22.445+0500</t>
+          <t>2025-09-11T09:15:19.601+0500</t>
         </is>
       </c>
       <c r="J261" t="inlineStr"/>
@@ -34813,7 +34912,7 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr">
@@ -34822,7 +34921,7 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q261" t="inlineStr"/>
       <c r="R261" t="inlineStr">
@@ -34832,24 +34931,24 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>RLT-85</t>
+          <t>RLT-84</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Casual leave 10 sept 25</t>
+          <t>Casual leave</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34874,12 +34973,12 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:09.033+0500</t>
+          <t>2025-09-11T09:14:17.734+0500</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:45.168+0500</t>
+          <t>2025-09-11T09:15:22.445+0500</t>
         </is>
       </c>
       <c r="J262" t="inlineStr"/>
@@ -34888,7 +34987,7 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr">
@@ -34897,7 +34996,7 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr">
@@ -34907,54 +35006,54 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>RLT-86</t>
+          <t>RLT-85</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Planned Leave 15th July 2025</t>
+          <t>Casual leave 10 sept 25</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:06.810+0500</t>
+          <t>2025-09-11T09:16:09.033+0500</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:30.527+0500</t>
+          <t>2025-09-11T09:16:45.168+0500</t>
         </is>
       </c>
       <c r="J263" t="inlineStr"/>
@@ -34968,7 +35067,7 @@
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -34989,17 +35088,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>RLT-87</t>
+          <t>RLT-86</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Planned 1st Sept 2025</t>
+          <t>Planned Leave 15th July 2025</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -35024,12 +35123,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2025-09-26T09:56:28.622+0500</t>
+          <t>2025-09-26T09:55:06.810+0500</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:11.707+0500</t>
+          <t>2025-09-26T09:55:30.527+0500</t>
         </is>
       </c>
       <c r="J264" t="inlineStr"/>
@@ -35064,17 +35163,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>RLT-88</t>
+          <t>RLT-87</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2025</t>
+          <t>Planned 1st Sept 2025</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -35099,12 +35198,12 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:27.334+0500</t>
+          <t>2025-09-26T09:56:28.622+0500</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:46.408+0500</t>
+          <t>2025-09-26T10:05:11.707+0500</t>
         </is>
       </c>
       <c r="J265" t="inlineStr"/>
@@ -35139,22 +35238,22 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>RLT-89</t>
+          <t>RLT-88</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
+          <t>Planned Leave 15th Aug 2025</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -35174,12 +35273,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2025-10-08T10:16:40.435+0500</t>
+          <t>2025-09-26T10:05:27.334+0500</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>2025-11-06T09:37:59.818+0500</t>
+          <t>2025-09-26T10:05:46.408+0500</t>
         </is>
       </c>
       <c r="J266" t="inlineStr"/>
@@ -35188,7 +35287,7 @@
         <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr">
@@ -35197,12 +35296,12 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q266" t="inlineStr"/>
       <c r="R266" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S266" t="inlineStr">
@@ -35214,22 +35313,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>RLT-90</t>
+          <t>RLT-89</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Planned Leave 5th Nov 2025</t>
+          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -35249,12 +35348,12 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>2025-11-06T09:38:11.154+0500</t>
+          <t>2025-10-08T10:16:40.435+0500</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:11.084+0500</t>
+          <t>2025-11-06T09:37:59.818+0500</t>
         </is>
       </c>
       <c r="J267" t="inlineStr"/>
@@ -35263,21 +35362,21 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P267" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q267" t="inlineStr"/>
       <c r="R267" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
@@ -35289,22 +35388,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>RLT-95</t>
+          <t>RLT-90</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>31542</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Sick Leave 18th Nov 2025</t>
+          <t>Planned Leave 5th Nov 2025</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -35324,12 +35423,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:01.035+0500</t>
+          <t>2025-11-06T09:38:11.154+0500</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:30.413+0500</t>
+          <t>2025-12-08T11:30:11.084+0500</t>
         </is>
       </c>
       <c r="J268" t="inlineStr"/>
@@ -35343,7 +35442,7 @@
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -35364,22 +35463,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>RLT-96</t>
+          <t>RLT-95</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
+          <t>Sick Leave 18th Nov 2025</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -35399,12 +35498,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:53.468+0500</t>
+          <t>2025-12-08T11:30:01.035+0500</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:21.845+0500</t>
+          <t>2025-12-08T11:30:30.413+0500</t>
         </is>
       </c>
       <c r="J269" t="inlineStr"/>
@@ -35413,7 +35512,7 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr">
@@ -35422,12 +35521,12 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q269" t="inlineStr"/>
       <c r="R269" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
@@ -35439,22 +35538,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>RLT-97</t>
+          <t>RLT-96</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>3rd Dec 2025</t>
+          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -35474,12 +35573,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.693+0500</t>
+          <t>2025-12-08T11:30:53.468+0500</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2025-12-08T11:32:24.681+0500</t>
+          <t>2025-12-08T11:31:21.845+0500</t>
         </is>
       </c>
       <c r="J270" t="inlineStr"/>
@@ -35488,21 +35587,21 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P270" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q270" t="inlineStr"/>
       <c r="R270" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
@@ -35514,47 +35613,47 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>RLT-99</t>
+          <t>RLT-97</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Leave for one day 05-12-25</t>
+          <t>3rd Dec 2025</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>2025-12-29T12:28:16.268+0500</t>
+          <t>2025-12-08T11:31:59.693+0500</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2025-12-29T12:29:46.783+0500</t>
+          <t>2025-12-08T11:32:24.681+0500</t>
         </is>
       </c>
       <c r="J271" t="inlineStr"/>
@@ -35568,7 +35667,7 @@
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -35581,6 +35680,81 @@
         </is>
       </c>
       <c r="S271" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>RLT-99</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>32431</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Leave for one day 05-12-25</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Resolved!</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>RLT-35</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:28:16.268+0500</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:29:46.783+0500</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" t="n">
+        <v>8</v>
+      </c>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -35597,7 +35771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39155,37 +39329,37 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-218</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-16T15:30:00.000+0500</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RLT-217</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-03-17T15:30:00.000+0500</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -39195,36 +39369,36 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-217</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-17T15:30:00.000+0500</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="146">
@@ -39240,7 +39414,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -39265,7 +39439,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -39290,7 +39464,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -39315,7 +39489,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -39340,7 +39514,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -39365,7 +39539,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -39390,7 +39564,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -39415,7 +39589,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -39440,7 +39614,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -39455,17 +39629,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -39490,7 +39664,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -39515,7 +39689,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -39540,7 +39714,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -39565,7 +39739,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -39590,7 +39764,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -39615,7 +39789,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -39640,7 +39814,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -39665,7 +39839,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -39690,7 +39864,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -39715,7 +39889,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -39740,7 +39914,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -39765,7 +39939,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -39790,7 +39964,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -39815,7 +39989,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -39840,7 +40014,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -39865,7 +40039,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -39890,7 +40064,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -39915,7 +40089,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -39940,7 +40114,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -39965,7 +40139,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -39990,15 +40164,40 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>Maria Sharafat</t>
         </is>
       </c>
-      <c r="E176" t="n">
+      <c r="E177" t="n">
         <v>8</v>
       </c>
     </row>
@@ -40013,7 +40212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40097,14 +40296,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>awais akhter</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -40113,13 +40312,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -40128,14 +40327,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>awais akhter</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -40144,13 +40343,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -40159,7 +40358,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hamza Ali</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -40190,14 +40389,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Hamza Ali</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>30.5</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -40206,13 +40405,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.81</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -40221,29 +40420,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>30.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -40252,11 +40451,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -40271,7 +40470,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -40283,29 +40482,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>512</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -40314,29 +40513,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.62</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -40345,14 +40544,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muhammad Ahmad Saleem</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -40367,7 +40566,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -40376,17 +40575,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Muhammad Ahmad Saleem</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -40395,29 +40594,29 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -40426,19 +40625,19 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Muhammad Zeeshan Aslam</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -40469,14 +40668,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sarmad Sabir</t>
+          <t>Muhammad Zeeshan Aslam</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -40485,13 +40684,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.62</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -40500,11 +40699,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Sarmad Sabir</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>13</v>
@@ -40516,10 +40715,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>1.62</v>
@@ -40531,14 +40730,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Waqar Rasheed</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -40550,10 +40749,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -40562,31 +40761,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Waqar Rasheed</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>48</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Zeeshan Sarwar</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>12</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -40601,7 +40831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42689,7 +42919,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -42698,32 +42928,32 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-218</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-218</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -42732,66 +42962,66 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>RLT-216</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-216</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-216</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-216</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -42800,59 +43030,59 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>RLT-217</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-217</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-217</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-217</t>
         </is>
       </c>
     </row>
@@ -42864,7 +43094,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -42898,7 +43128,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -42932,7 +43162,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -42966,7 +43196,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -43000,7 +43230,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -43034,7 +43264,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -43068,7 +43298,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -43102,7 +43332,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -43136,7 +43366,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -43170,7 +43400,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -43187,19 +43417,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -43208,59 +43438,59 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D77" t="n">
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
         <v>8</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>RLT-176</t>
+          <t>RLT-173</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-176</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F78" t="n">
         <v>8</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-176</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-176</t>
         </is>
       </c>
     </row>
@@ -43272,7 +43502,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -43306,7 +43536,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -43340,7 +43570,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -43374,7 +43604,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -43408,7 +43638,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -43442,7 +43672,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -43476,7 +43706,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -43510,7 +43740,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -43544,7 +43774,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -43578,7 +43808,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -43612,7 +43842,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -43646,7 +43876,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -43680,7 +43910,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -43714,7 +43944,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -43748,7 +43978,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -43782,7 +44012,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -43816,7 +44046,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -43850,7 +44080,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -43884,7 +44114,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -43918,27 +44148,61 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>8</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C98" t="n">
-        <v>8</v>
-      </c>
-      <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="n">
-        <v>8</v>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="C99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>8</v>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>RLT-173</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
         </is>
@@ -43955,7 +44219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44641,7 +44905,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -44650,22 +44914,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -44674,22 +44938,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D30" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>6.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -44713,25 +44977,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-W13</t>
+          <t>2026-W12</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>40</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="33">
@@ -44742,7 +45006,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W13</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -44761,7 +45025,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -44770,40 +45034,40 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -44814,7 +45078,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -44838,7 +45102,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -44862,19 +45126,43 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>40</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>2026-W18</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C39" t="n">
         <v>32</v>
       </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
         <v>32</v>
       </c>
     </row>
@@ -44889,7 +45177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45215,7 +45503,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -45224,22 +45512,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>22.5</v>
+        <v>6.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>54.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -45248,22 +45536,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>176</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -45272,22 +45560,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -45299,19 +45587,19 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -45320,10 +45608,10 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
         <v>6.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -45335,7 +45623,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -45344,22 +45632,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sarmad Sabir</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -45371,19 +45659,19 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Sarmad Sabir</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -45395,60 +45683,84 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>176</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>176</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Muhammad Imran Aslam</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="n">
         <v>8</v>
       </c>
     </row>

--- a/rlt_leave_report.xlsx
+++ b/rlt_leave_report.xlsx
@@ -9402,7 +9402,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-16T10:29:39.119+0500</t>
+          <t>2026-03-24T14:47:00.468+0500</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -9411,7 +9411,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
@@ -9420,12 +9420,12 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -32210,7 +32210,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2026-03-16T10:29:39.119+0500</t>
+          <t>2026-03-24T14:47:00.468+0500</t>
         </is>
       </c>
       <c r="J226" t="inlineStr"/>
@@ -32219,7 +32219,7 @@
         <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
@@ -32228,12 +32228,12 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S226" t="inlineStr">
@@ -35771,7 +35771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E177"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38804,37 +38804,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-215</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-03T09:00:00.000+0500</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Faiq Butt</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RLT-202</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-03-04T04:41:00.000+0500</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -38844,7 +38844,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Syed Yousaf Qadri</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -38854,12 +38854,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RLT-208</t>
+          <t>RLT-202</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-03-04T14:27:00.000+0500</t>
+          <t>2026-03-04T04:41:00.000+0500</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -38869,7 +38869,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Syed Yousaf Qadri</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -38879,22 +38879,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-208</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-04T14:27:00.000+0500</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Ameer Hamza Khan</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -38904,12 +38904,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RLT-209</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-03-05T14:27:00.000+0500</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -38919,7 +38919,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -38929,22 +38929,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-209</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-05T14:27:00.000+0500</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Ameer Hamza Khan</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -38954,12 +38954,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RLT-203</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-03-06T09:00:00.000+0500</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -38969,7 +38969,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -38979,7 +38979,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RLT-204</t>
+          <t>RLT-203</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -38994,22 +38994,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RLT-210</t>
+          <t>RLT-204</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-03-06T14:27:00.000+0500</t>
+          <t>2026-03-06T09:00:00.000+0500</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -39019,22 +39019,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RLT-213</t>
+          <t>RLT-210</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-03-06T09:00:00.000+0500</t>
+          <t>2026-03-06T14:27:00.000+0500</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Faiq Butt</t>
+          <t>Ameer Hamza Khan</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -39054,22 +39054,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-213</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-06T09:00:00.000+0500</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Faiq Butt</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -39079,12 +39079,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RLT-205</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-09T07:08:00.000+0500</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -39094,22 +39094,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sarmad Sabir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RLT-214</t>
+          <t>RLT-205</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-03-09T09:00:00.000+0500</t>
+          <t>2026-03-09T07:08:00.000+0500</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -39119,47 +39119,47 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Faiq Butt</t>
+          <t>Sarmad Sabir</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>32</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-214</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-09T09:00:00.000+0500</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Faiq Butt</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RLT-211</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-03-10T14:28:00.000+0500</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -39169,7 +39169,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -39179,22 +39179,22 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-211</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-10T14:28:00.000+0500</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Ameer Hamza Khan</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -39214,7 +39214,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -39239,7 +39239,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -39254,12 +39254,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RLT-212</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-03-13T09:00:00.000+0500</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -39269,47 +39269,47 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-212</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-13T09:00:00.000+0500</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RLT-216</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-03-16T09:00:00.000+0500</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -39319,22 +39319,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RLT-218</t>
+          <t>RLT-216</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-03-16T15:30:00.000+0500</t>
+          <t>2026-03-16T09:00:00.000+0500</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -39344,7 +39344,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Arsalan Zafar Khan</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -39354,37 +39354,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-218</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-16T15:30:00.000+0500</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RLT-217</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-03-17T15:30:00.000+0500</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -39394,36 +39394,36 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-217</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-17T15:30:00.000+0500</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="147">
@@ -39439,7 +39439,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -39464,7 +39464,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -39489,7 +39489,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -39514,7 +39514,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -39539,7 +39539,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -39564,7 +39564,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -39589,7 +39589,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -39614,7 +39614,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -39639,7 +39639,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -39654,17 +39654,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -39689,7 +39689,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -39714,7 +39714,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -39739,7 +39739,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -39764,7 +39764,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -39789,7 +39789,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -39814,7 +39814,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -39839,7 +39839,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -39864,7 +39864,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -39889,7 +39889,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -39939,7 +39939,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -39964,7 +39964,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -39989,7 +39989,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -40014,7 +40014,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -40064,7 +40064,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -40089,7 +40089,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -40114,7 +40114,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -40139,7 +40139,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -40164,7 +40164,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -40189,15 +40189,40 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>Maria Sharafat</t>
         </is>
       </c>
-      <c r="E177" t="n">
+      <c r="E178" t="n">
         <v>8</v>
       </c>
     </row>
@@ -40424,7 +40449,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
         <v>30.5</v>
@@ -40439,7 +40464,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
         <v>3.81</v>
@@ -40831,7 +40856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42273,7 +42298,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -42282,7 +42307,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -42291,23 +42316,23 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-215</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-215</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -42316,10 +42341,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -42329,24 +42354,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>RLT-189</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-189</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Muhammad Usman Javed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -42363,19 +42388,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>RLT-208</t>
+          <t>RLT-189</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-208</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-189</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Ameer Hamza Khan</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -42397,19 +42422,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>RLT-202</t>
+          <t>RLT-208</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-202</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-208</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -42418,10 +42443,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -42431,31 +42456,31 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-202</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-202</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -42465,19 +42490,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>RLT-209</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-209</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Ameer Hamza Khan</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -42486,10 +42511,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -42499,31 +42524,31 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-209</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-209</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -42533,19 +42558,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>RLT-210</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-210</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Ameer Hamza Khan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -42557,29 +42582,29 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>RLT-204, RLT-213</t>
+          <t>RLT-210</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-204, https://octopusdtlsupport.atlassian.net/browse/RLT-213</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-210</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -42588,32 +42613,32 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-204, RLT-213</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-204, https://octopusdtlsupport.atlassian.net/browse/RLT-213</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -42622,10 +42647,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -42635,53 +42660,53 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>RLT-203</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-203</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>RLT-214</t>
+          <t>RLT-203</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-214</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-203</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -42690,7 +42715,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -42699,23 +42724,23 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-214</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-214</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sarmad Sabir</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -42724,66 +42749,66 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>RLT-205</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-205</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ameer Hamza Khan</t>
+          <t>Sarmad Sabir</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>RLT-211</t>
+          <t>RLT-205</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-211</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-205</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Ameer Hamza Khan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -42792,10 +42817,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -42805,12 +42830,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-211</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-211</t>
         </is>
       </c>
     </row>
@@ -42822,7 +42847,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -42856,7 +42881,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -42890,7 +42915,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -42919,41 +42944,41 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Arsalan Zafar Khan</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>RLT-218</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-218</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Arsalan Zafar Khan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -42962,32 +42987,32 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-218</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-218</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Taimur Zahid</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -42996,66 +43021,66 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>RLT-216</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-216</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-216</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-216</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Muhammad Abdullah</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -43064,59 +43089,59 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D66" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>RLT-217</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-217</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Abdullah</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-217</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-217</t>
         </is>
       </c>
     </row>
@@ -43128,7 +43153,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -43162,7 +43187,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -43196,7 +43221,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -43230,7 +43255,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -43264,7 +43289,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -43298,7 +43323,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -43332,7 +43357,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -43366,7 +43391,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -43400,7 +43425,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -43434,7 +43459,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -43451,19 +43476,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -43472,59 +43497,59 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>8</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>RLT-176</t>
+          <t>RLT-173</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-176</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
         <v>8</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-176</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-176</t>
         </is>
       </c>
     </row>
@@ -43536,7 +43561,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -43570,7 +43595,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -43604,7 +43629,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -43638,7 +43663,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -43672,7 +43697,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -43706,7 +43731,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -43740,7 +43765,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -43774,7 +43799,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -43808,7 +43833,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -43842,7 +43867,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -43876,7 +43901,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -43910,7 +43935,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -43944,7 +43969,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -43978,7 +44003,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -44012,7 +44037,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -44046,7 +44071,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -44080,7 +44105,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -44114,7 +44139,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -44148,7 +44173,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -44182,27 +44207,61 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>8</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C99" t="n">
-        <v>8</v>
-      </c>
-      <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="n">
-        <v>8</v>
-      </c>
-      <c r="G99" t="inlineStr">
+      <c r="C100" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>8</v>
+      </c>
+      <c r="G100" t="inlineStr">
         <is>
           <t>RLT-173</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
         </is>
@@ -44674,7 +44733,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
         <v>22.5</v>
@@ -44683,7 +44742,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>22.5</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="20">
@@ -45536,7 +45595,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>22.5</v>
@@ -45545,7 +45604,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>54.5</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="16">
@@ -46877,7 +46936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47102,17 +47161,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RLT-116</t>
+          <t>RLT-215</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Annual Leaves</t>
+          <t>Compassionate Leaves</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -47122,11 +47181,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -47145,7 +47204,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RLT-65</t>
+          <t>RLT-116</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -47155,7 +47214,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
+          <t>Annual Leaves</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -47169,7 +47228,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -47188,7 +47247,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RLT-89</t>
+          <t>RLT-65</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -47198,21 +47257,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
+          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -47231,7 +47290,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RLT-96</t>
+          <t>RLT-89</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -47241,7 +47300,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
+          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -47255,7 +47314,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -47274,50 +47333,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-96</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Maternity Leaves 1 Jan - 31 March 2026</t>
+          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>528</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>528</v>
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>No Entry</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>No Entry</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -47327,7 +47386,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Annual Leaves 1 April - 30 April 2026</t>
+          <t>Maternity Leaves 1 Jan - 31 March 2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -47341,36 +47400,36 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>176</v>
+        <v>528</v>
       </c>
       <c r="G11" t="n">
-        <v>176</v>
+        <v>528</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RLT-188</t>
+          <t>RLT-173</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Muhammad Usman Javed</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annual Leaves</t>
+          <t>Annual Leaves 1 April - 30 April 2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -47384,60 +47443,103 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No Entry</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No Entry</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>RLT-188</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Muhammad Usman Javed</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Annual Leaves</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Considered in Roadmap &amp; Queued</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>56</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>No Entry</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No Entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>RLT-47</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Zeeshan Sarwar</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Leave for two days 20 and 21-06-24</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Resolved!</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F14" t="n">
         <v>16</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>No Entry</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>No Entry</t>
         </is>

--- a/rlt_leave_report.xlsx
+++ b/rlt_leave_report.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S154"/>
+  <dimension ref="A1:S156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-02-23T13:49:22.887+0500</t>
+          <t>2026-03-26T12:43:19.338+0500</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9686,61 +9686,61 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RLT-43</t>
+          <t>RLT-219</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>41154</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Planned Leave 15th May 2024</t>
+          <t>Leave - March 24, 2026</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-118</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2024-05-15T13:17:36.997+0500</t>
+          <t>2026-03-25T15:18:55.401+0500</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:48.485+0500</t>
+          <t>2026-03-25T15:19:42.879+0500</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M112" t="n">
         <v>8</v>
@@ -9748,7 +9748,7 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -9773,82 +9773,82 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>RLT-44</t>
+          <t>RLT-220</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>41316</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Leaves Faiza</t>
+          <t>Planned Leave 15th April 2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-26</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2024-05-27T17:19:47.991+0500</t>
+          <t>2026-03-26T12:12:31.418+0500</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2025-12-30T10:15:12.915+0500</t>
+          <t>2026-03-26T12:14:04.911+0500</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M113" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -9860,51 +9860,59 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RLT-45</t>
+          <t>RLT-43</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Leave for one day 05-06-24</t>
+          <t>Planned Leave 15th May 2024</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2024-06-06T09:10:07.974+0500</t>
+          <t>2024-05-15T13:17:36.997+0500</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2024-06-06T09:11:39.142+0500</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+          <t>2024-08-16T16:28:48.485+0500</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
@@ -9914,13 +9922,17 @@
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P114" t="n">
         <v>8</v>
       </c>
-      <c r="Q114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
       <c r="R114" t="inlineStr">
         <is>
           <t>No</t>
@@ -9935,70 +9947,82 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RLT-46</t>
+          <t>RLT-44</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Planned Leave 20th June 2024</t>
+          <t>Leaves Faiza</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2024-06-21T09:20:21.600+0500</t>
+          <t>2024-05-27T17:19:47.991+0500</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:56.168+0500</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+          <t>2025-12-30T10:15:12.915+0500</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q115" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -10010,17 +10034,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RLT-47</t>
+          <t>RLT-45</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Leave for two days 20 and 21-06-24</t>
+          <t>Leave for one day 05-06-24</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10045,12 +10069,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2024-06-24T09:18:18.735+0500</t>
+          <t>2024-06-06T09:10:07.974+0500</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2024-06-24T09:19:43.343+0500</t>
+          <t>2024-06-06T09:11:39.142+0500</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -10059,7 +10083,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
@@ -10068,12 +10092,12 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -10085,78 +10109,70 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RLT-49</t>
+          <t>RLT-46</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Emergency leave</t>
+          <t>Planned Leave 20th June 2024</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2024-07-18T11:05:11.868+0500</t>
+          <t>2024-06-21T09:20:21.600+0500</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-01-29T16:48:09.549+0500</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
+          <t>2024-08-16T16:28:56.168+0500</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -10168,17 +10184,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RLT-50</t>
+          <t>RLT-47</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sick leave for one day 22-07-24</t>
+          <t>Leave for two days 20 and 21-06-24</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10203,12 +10219,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2024-07-23T09:08:09.289+0500</t>
+          <t>2024-06-24T09:18:18.735+0500</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2024-07-23T09:09:17.479+0500</t>
+          <t>2024-06-24T09:19:43.343+0500</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -10217,21 +10233,21 @@
         <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -10243,70 +10259,78 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RLT-52</t>
+          <t>RLT-49</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Urgent work leave 05-08-24</t>
+          <t>Emergency leave</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2024-08-06T09:08:48.315+0500</t>
+          <t>2024-07-18T11:05:11.868+0500</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2024-08-06T09:11:15.823+0500</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr"/>
+          <t>2026-01-29T16:48:09.549+0500</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q119" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -10318,47 +10342,47 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RLT-53</t>
+          <t>RLT-50</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2024</t>
+          <t>Sick leave for one day 22-07-24</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:43.991+0500</t>
+          <t>2024-07-23T09:08:09.289+0500</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2024-08-16T16:29:17.981+0500</t>
+          <t>2024-07-23T09:09:17.479+0500</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -10372,7 +10396,7 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -10393,17 +10417,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RLT-54</t>
+          <t>RLT-52</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Leave for one day 30-08-24</t>
+          <t>Urgent work leave 05-08-24</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10428,12 +10452,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:09.454+0500</t>
+          <t>2024-08-06T09:08:48.315+0500</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2024-09-03T09:15:53.284+0500</t>
+          <t>2024-08-06T09:11:15.823+0500</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -10468,47 +10492,47 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RLT-55</t>
+          <t>RLT-53</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Leave for one day 02-09-24</t>
+          <t>Planned Leave 15th Aug 2024</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:29.824+0500</t>
+          <t>2024-08-16T16:28:43.991+0500</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2024-09-03T09:16:12.471+0500</t>
+          <t>2024-08-16T16:29:17.981+0500</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -10522,7 +10546,7 @@
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -10543,47 +10567,47 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RLT-56</t>
+          <t>RLT-54</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sick leave 28th Aug 2024</t>
+          <t>Leave for one day 30-08-24</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2024-09-03T10:03:57.925+0500</t>
+          <t>2024-08-28T16:51:09.454+0500</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2024-09-03T10:04:14.562+0500</t>
+          <t>2024-09-03T09:15:53.284+0500</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -10597,7 +10621,7 @@
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -10618,47 +10642,47 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>RLT-57</t>
+          <t>RLT-55</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sick Leave 13th Sept 2024</t>
+          <t>Leave for one day 02-09-24</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2024-09-23T11:07:49.200+0500</t>
+          <t>2024-08-28T16:51:29.824+0500</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2024-09-23T11:08:09.638+0500</t>
+          <t>2024-09-03T09:16:12.471+0500</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -10672,7 +10696,7 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -10693,47 +10717,47 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RLT-58</t>
+          <t>RLT-56</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Leave for one day 14-11-24</t>
+          <t>Sick leave 28th Aug 2024</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2024-11-15T09:25:05.670+0500</t>
+          <t>2024-09-03T10:03:57.925+0500</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2024-11-15T09:38:06.205+0500</t>
+          <t>2024-09-03T10:04:14.562+0500</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -10747,7 +10771,7 @@
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -10768,22 +10792,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RLT-59</t>
+          <t>RLT-57</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Planned Leave 8th Nov 2024</t>
+          <t>Sick Leave 13th Sept 2024</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -10803,12 +10827,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2024-11-21T12:24:36.990+0500</t>
+          <t>2024-09-23T11:07:49.200+0500</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:57.134+0500</t>
+          <t>2024-09-23T11:08:09.638+0500</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -10817,16 +10841,16 @@
         <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
@@ -10836,54 +10860,54 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RLT-60</t>
+          <t>RLT-58</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Planned Leave 19th Nov 2024</t>
+          <t>Leave for one day 14-11-24</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2024-11-21T12:25:03.206+0500</t>
+          <t>2024-11-15T09:25:05.670+0500</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:07.591+0500</t>
+          <t>2024-11-15T09:38:06.205+0500</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -10897,7 +10921,7 @@
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -10918,47 +10942,47 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RLT-62</t>
+          <t>RLT-59</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sick leave for one day 30-12-24</t>
+          <t>Planned Leave 8th Nov 2024</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:13.907+0500</t>
+          <t>2024-11-21T12:24:36.990+0500</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:33.151+0500</t>
+          <t>2024-12-31T11:38:57.134+0500</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -10967,16 +10991,16 @@
         <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
@@ -10986,24 +11010,24 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RLT-63</t>
+          <t>RLT-60</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Planned Leave 29th Nov 2024</t>
+          <t>Planned Leave 19th Nov 2024</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11028,12 +11052,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:18.228+0500</t>
+          <t>2024-11-21T12:25:03.206+0500</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:11.165+0500</t>
+          <t>2024-12-31T11:39:07.591+0500</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -11068,47 +11092,47 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RLT-64</t>
+          <t>RLT-62</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Planned Leave 16th Dec 2024</t>
+          <t>Sick leave for one day 30-12-24</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:25.533+0500</t>
+          <t>2024-12-31T09:30:13.907+0500</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:27.662+0500</t>
+          <t>2024-12-31T09:30:33.151+0500</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -11122,7 +11146,7 @@
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -11143,17 +11167,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RLT-65</t>
+          <t>RLT-63</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
+          <t>Planned Leave 29th Nov 2024</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11178,12 +11202,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2024-12-31T11:40:34.525+0500</t>
+          <t>2024-12-31T11:38:18.228+0500</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:36.616+0500</t>
+          <t>2024-12-31T11:39:11.165+0500</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -11192,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
@@ -11201,12 +11225,12 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -11218,47 +11242,47 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RLT-67</t>
+          <t>RLT-64</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Casual Leave for half day 02-01-25</t>
+          <t>Planned Leave 16th Dec 2024</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2025-01-06T09:19:42.013+0500</t>
+          <t>2024-12-31T11:39:25.533+0500</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:11.598+0500</t>
+          <t>2025-03-25T09:09:27.662+0500</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -11267,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
@@ -11276,7 +11300,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
@@ -11293,47 +11317,47 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RLT-68</t>
+          <t>RLT-65</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Leave for one day 03-01-25</t>
+          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2025-01-06T09:20:06.483+0500</t>
+          <t>2024-12-31T11:40:34.525+0500</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:08.280+0500</t>
+          <t>2025-03-25T09:09:36.616+0500</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -11342,21 +11366,21 @@
         <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P133" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -11368,17 +11392,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RLT-71</t>
+          <t>RLT-67</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Leave for one day 27-02-25</t>
+          <t>Casual Leave for half day 02-01-25</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11403,12 +11427,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:26.122+0500</t>
+          <t>2025-01-06T09:19:42.013+0500</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:46.578+0500</t>
+          <t>2025-01-06T09:21:11.598+0500</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -11417,16 +11441,16 @@
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr">
@@ -11443,17 +11467,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RLT-72</t>
+          <t>RLT-68</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Annual leave 31 Jan</t>
+          <t>Leave for one day 03-01-25</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11463,27 +11487,27 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:16.894+0500</t>
+          <t>2025-01-06T09:20:06.483+0500</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:47.087+0500</t>
+          <t>2025-01-06T09:21:08.280+0500</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -11497,7 +11521,7 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -11518,47 +11542,47 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RLT-74</t>
+          <t>RLT-71</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Planned Leave 21st Feb 2025</t>
+          <t>Leave for one day 27-02-25</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:51.777+0500</t>
+          <t>2025-02-28T09:31:26.122+0500</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:06.523+0500</t>
+          <t>2025-02-28T09:31:46.578+0500</t>
         </is>
       </c>
       <c r="J136" t="inlineStr"/>
@@ -11572,7 +11596,7 @@
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -11593,47 +11617,47 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RLT-77</t>
+          <t>RLT-72</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Planned Leave 3rd April 2025</t>
+          <t>Annual leave 31 Jan</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2025-04-29T14:35:54.729+0500</t>
+          <t>2025-03-04T11:51:16.894+0500</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:21.782+0500</t>
+          <t>2025-03-04T11:51:47.087+0500</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -11668,17 +11692,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RLT-78</t>
+          <t>RLT-74</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Planned Leave 4th April 2025</t>
+          <t>Planned Leave 21st Feb 2025</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -11703,12 +11727,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:42.933+0500</t>
+          <t>2025-03-25T09:09:51.777+0500</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2025-04-29T14:37:01.596+0500</t>
+          <t>2025-04-29T14:36:06.523+0500</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -11743,47 +11767,47 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RLT-79</t>
+          <t>RLT-77</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sick leave</t>
+          <t>Planned Leave 3rd April 2025</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2025-05-15T10:52:44.037+0500</t>
+          <t>2025-04-29T14:35:54.729+0500</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:11.410+0500</t>
+          <t>2025-04-29T14:36:21.782+0500</t>
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
@@ -11797,7 +11821,7 @@
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -11818,59 +11842,51 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RLT-80</t>
+          <t>RLT-78</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>16 may 2025</t>
+          <t>Planned Leave 4th April 2025</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>RLT-5</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:34.680+0500</t>
+          <t>2025-04-29T14:36:42.933+0500</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:58.959+0500</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
+          <t>2025-04-29T14:37:01.596+0500</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="n">
         <v>0</v>
       </c>
@@ -11880,17 +11896,13 @@
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P140" t="n">
         <v>8</v>
       </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
+      <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr">
         <is>
           <t>No</t>
@@ -11905,17 +11917,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RLT-81</t>
+          <t>RLT-79</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Annual leave 22 May</t>
+          <t>Sick leave</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -11940,12 +11952,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2025-05-21T17:45:49.062+0500</t>
+          <t>2025-05-15T10:52:44.037+0500</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:14.892+0500</t>
+          <t>2025-09-11T09:15:11.410+0500</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
@@ -11959,7 +11971,7 @@
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -11980,51 +11992,59 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RLT-82</t>
+          <t>RLT-80</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Planned Leave 5th June 2025</t>
+          <t>16 may 2025</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2025-06-10T11:05:56.983+0500</t>
+          <t>2025-05-20T15:48:34.680+0500</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:20.879+0500</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+          <t>2025-05-20T15:48:58.959+0500</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
       <c r="L142" t="n">
         <v>0</v>
       </c>
@@ -12034,13 +12054,17 @@
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P142" t="n">
         <v>8</v>
       </c>
-      <c r="Q142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
       <c r="R142" t="inlineStr">
         <is>
           <t>No</t>
@@ -12055,17 +12079,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RLT-83</t>
+          <t>RLT-81</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Annual leave 07 July</t>
+          <t>Annual leave 22 May</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12090,12 +12114,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2025-07-07T12:00:55.557+0500</t>
+          <t>2025-05-21T17:45:49.062+0500</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:19.601+0500</t>
+          <t>2025-09-11T09:15:14.892+0500</t>
         </is>
       </c>
       <c r="J143" t="inlineStr"/>
@@ -12130,47 +12154,47 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RLT-84</t>
+          <t>RLT-82</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Casual leave</t>
+          <t>Planned Leave 5th June 2025</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2025-09-11T09:14:17.734+0500</t>
+          <t>2025-06-10T11:05:56.983+0500</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:22.445+0500</t>
+          <t>2025-09-26T09:55:20.879+0500</t>
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
@@ -12179,7 +12203,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
@@ -12188,7 +12212,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr">
@@ -12198,24 +12222,24 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RLT-85</t>
+          <t>RLT-83</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Casual leave 10 sept 25</t>
+          <t>Annual leave 07 July</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12240,12 +12264,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:09.033+0500</t>
+          <t>2025-07-07T12:00:55.557+0500</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:45.168+0500</t>
+          <t>2025-09-11T09:15:19.601+0500</t>
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
@@ -12280,47 +12304,47 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RLT-86</t>
+          <t>RLT-84</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Planned Leave 15th July 2025</t>
+          <t>Casual leave</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:06.810+0500</t>
+          <t>2025-09-11T09:14:17.734+0500</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:30.527+0500</t>
+          <t>2025-09-11T09:15:22.445+0500</t>
         </is>
       </c>
       <c r="J146" t="inlineStr"/>
@@ -12329,16 +12353,16 @@
         <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr">
@@ -12348,54 +12372,54 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RLT-87</t>
+          <t>RLT-85</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Planned 1st Sept 2025</t>
+          <t>Casual leave 10 sept 25</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2025-09-26T09:56:28.622+0500</t>
+          <t>2025-09-11T09:16:09.033+0500</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:11.707+0500</t>
+          <t>2025-09-11T09:16:45.168+0500</t>
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
@@ -12409,7 +12433,7 @@
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -12430,17 +12454,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RLT-88</t>
+          <t>RLT-86</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2025</t>
+          <t>Planned Leave 15th July 2025</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -12465,12 +12489,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:27.334+0500</t>
+          <t>2025-09-26T09:55:06.810+0500</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:46.408+0500</t>
+          <t>2025-09-26T09:55:30.527+0500</t>
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
@@ -12505,22 +12529,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RLT-89</t>
+          <t>RLT-87</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
+          <t>Planned 1st Sept 2025</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -12540,12 +12564,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2025-10-08T10:16:40.435+0500</t>
+          <t>2025-09-26T09:56:28.622+0500</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2025-11-06T09:37:59.818+0500</t>
+          <t>2025-09-26T10:05:11.707+0500</t>
         </is>
       </c>
       <c r="J149" t="inlineStr"/>
@@ -12554,7 +12578,7 @@
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
@@ -12563,12 +12587,12 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -12580,22 +12604,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RLT-90</t>
+          <t>RLT-88</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Planned Leave 5th Nov 2025</t>
+          <t>Planned Leave 15th Aug 2025</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -12615,12 +12639,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2025-11-06T09:38:11.154+0500</t>
+          <t>2025-09-26T10:05:27.334+0500</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:11.084+0500</t>
+          <t>2025-09-26T10:05:46.408+0500</t>
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
@@ -12634,7 +12658,7 @@
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -12655,22 +12679,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RLT-95</t>
+          <t>RLT-89</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>31542</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Sick Leave 18th Nov 2025</t>
+          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -12690,12 +12714,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:01.035+0500</t>
+          <t>2025-10-08T10:16:40.435+0500</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:30.413+0500</t>
+          <t>2025-11-06T09:37:59.818+0500</t>
         </is>
       </c>
       <c r="J151" t="inlineStr"/>
@@ -12704,7 +12728,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
@@ -12713,12 +12737,12 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -12730,22 +12754,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RLT-96</t>
+          <t>RLT-90</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
+          <t>Planned Leave 5th Nov 2025</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -12765,12 +12789,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:53.468+0500</t>
+          <t>2025-11-06T09:38:11.154+0500</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:21.845+0500</t>
+          <t>2025-12-08T11:30:11.084+0500</t>
         </is>
       </c>
       <c r="J152" t="inlineStr"/>
@@ -12779,21 +12803,21 @@
         <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -12805,22 +12829,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>RLT-97</t>
+          <t>RLT-95</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>3rd Dec 2025</t>
+          <t>Sick Leave 18th Nov 2025</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -12840,12 +12864,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.693+0500</t>
+          <t>2025-12-08T11:30:01.035+0500</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2025-12-08T11:32:24.681+0500</t>
+          <t>2025-12-08T11:30:30.413+0500</t>
         </is>
       </c>
       <c r="J153" t="inlineStr"/>
@@ -12859,7 +12883,7 @@
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -12880,47 +12904,47 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RLT-99</t>
+          <t>RLT-96</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Leave for one day 05-12-25</t>
+          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2025-12-29T12:28:16.268+0500</t>
+          <t>2025-12-08T11:30:53.468+0500</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2025-12-29T12:29:46.783+0500</t>
+          <t>2025-12-08T11:31:21.845+0500</t>
         </is>
       </c>
       <c r="J154" t="inlineStr"/>
@@ -12929,24 +12953,174 @@
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P154" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>RLT-97</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>31546</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>3rd Dec 2025</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Planned Leave</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Hassan Saeed Wattoo</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>RLT-39</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Hassan Saeed Wattoo</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2025-12-08T11:31:59.693+0500</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2025-12-08T11:32:24.681+0500</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>8</v>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>RLT-99</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>32431</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Leave for one day 05-12-25</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Resolved!</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>RLT-35</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:28:16.268+0500</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:29:46.783+0500</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>8</v>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -12963,7 +13137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S272"/>
+  <dimension ref="A1:S274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29146,7 +29320,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -29171,7 +29345,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>2026-02-23T13:49:22.887+0500</t>
+          <t>2026-03-26T12:43:19.338+0500</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -32494,61 +32668,61 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>RLT-43</t>
+          <t>RLT-219</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>41154</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Planned Leave 15th May 2024</t>
+          <t>Leave - March 24, 2026</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-118</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>2024-05-15T13:17:36.997+0500</t>
+          <t>2026-03-25T15:18:55.401+0500</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:48.485+0500</t>
+          <t>2026-03-25T15:19:42.879+0500</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M230" t="n">
         <v>8</v>
@@ -32556,7 +32730,7 @@
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -32564,7 +32738,7 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="R230" t="inlineStr">
@@ -32581,82 +32755,82 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RLT-44</t>
+          <t>RLT-220</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>41316</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Leaves Faiza</t>
+          <t>Planned Leave 15th April 2026</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-26</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>2024-05-27T17:19:47.991+0500</t>
+          <t>2026-03-26T12:12:31.418+0500</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>2025-12-30T10:15:12.915+0500</t>
+          <t>2026-03-26T12:14:04.911+0500</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M231" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S231" t="inlineStr">
@@ -32668,51 +32842,59 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>RLT-45</t>
+          <t>RLT-43</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Leave for one day 05-06-24</t>
+          <t>Planned Leave 15th May 2024</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>2024-06-06T09:10:07.974+0500</t>
+          <t>2024-05-15T13:17:36.997+0500</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>2024-06-06T09:11:39.142+0500</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
+          <t>2024-08-16T16:28:48.485+0500</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
       <c r="L232" t="n">
         <v>0</v>
       </c>
@@ -32722,13 +32904,17 @@
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P232" t="n">
         <v>8</v>
       </c>
-      <c r="Q232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
       <c r="R232" t="inlineStr">
         <is>
           <t>No</t>
@@ -32743,70 +32929,82 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>RLT-46</t>
+          <t>RLT-44</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Planned Leave 20th June 2024</t>
+          <t>Leaves Faiza</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2024-06-21T09:20:21.600+0500</t>
+          <t>2024-05-27T17:19:47.991+0500</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:56.168+0500</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
+          <t>2025-12-30T10:15:12.915+0500</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
       <c r="L233" t="n">
         <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P233" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q233" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
@@ -32818,17 +33016,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>RLT-47</t>
+          <t>RLT-45</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Leave for two days 20 and 21-06-24</t>
+          <t>Leave for one day 05-06-24</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -32853,12 +33051,12 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2024-06-24T09:18:18.735+0500</t>
+          <t>2024-06-06T09:10:07.974+0500</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>2024-06-24T09:19:43.343+0500</t>
+          <t>2024-06-06T09:11:39.142+0500</t>
         </is>
       </c>
       <c r="J234" t="inlineStr"/>
@@ -32867,7 +33065,7 @@
         <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr">
@@ -32876,12 +33074,12 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S234" t="inlineStr">
@@ -32893,78 +33091,70 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>RLT-49</t>
+          <t>RLT-46</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Emergency leave</t>
+          <t>Planned Leave 20th June 2024</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Considered in Roadmap &amp; Queued</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>RLT-13</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Faiza Nasir</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>2024-07-18T11:05:11.868+0500</t>
+          <t>2024-06-21T09:20:21.600+0500</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2026-01-29T16:48:09.549+0500</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
+          <t>2024-08-16T16:28:56.168+0500</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="n">
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P235" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S235" t="inlineStr">
@@ -32976,17 +33166,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RLT-50</t>
+          <t>RLT-47</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Sick leave for one day 22-07-24</t>
+          <t>Leave for two days 20 and 21-06-24</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -33011,12 +33201,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>2024-07-23T09:08:09.289+0500</t>
+          <t>2024-06-24T09:18:18.735+0500</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2024-07-23T09:09:17.479+0500</t>
+          <t>2024-06-24T09:19:43.343+0500</t>
         </is>
       </c>
       <c r="J236" t="inlineStr"/>
@@ -33025,21 +33215,21 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P236" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S236" t="inlineStr">
@@ -33051,70 +33241,78 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>RLT-52</t>
+          <t>RLT-49</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Urgent work leave 05-08-24</t>
+          <t>Emergency leave</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Considered in Roadmap &amp; Queued</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-13</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Faiza Nasir</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2024-08-06T09:08:48.315+0500</t>
+          <t>2024-07-18T11:05:11.868+0500</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>2024-08-06T09:11:15.823+0500</t>
-        </is>
-      </c>
-      <c r="J237" t="inlineStr"/>
+          <t>2026-01-29T16:48:09.549+0500</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="n">
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q237" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S237" t="inlineStr">
@@ -33126,47 +33324,47 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>RLT-53</t>
+          <t>RLT-50</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2024</t>
+          <t>Sick leave for one day 22-07-24</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>2024-08-16T16:28:43.991+0500</t>
+          <t>2024-07-23T09:08:09.289+0500</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2024-08-16T16:29:17.981+0500</t>
+          <t>2024-07-23T09:09:17.479+0500</t>
         </is>
       </c>
       <c r="J238" t="inlineStr"/>
@@ -33180,7 +33378,7 @@
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -33201,17 +33399,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>RLT-54</t>
+          <t>RLT-52</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>18829</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Leave for one day 30-08-24</t>
+          <t>Urgent work leave 05-08-24</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -33236,12 +33434,12 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:09.454+0500</t>
+          <t>2024-08-06T09:08:48.315+0500</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2024-09-03T09:15:53.284+0500</t>
+          <t>2024-08-06T09:11:15.823+0500</t>
         </is>
       </c>
       <c r="J239" t="inlineStr"/>
@@ -33276,47 +33474,47 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>RLT-55</t>
+          <t>RLT-53</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Leave for one day 02-09-24</t>
+          <t>Planned Leave 15th Aug 2024</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>2024-08-28T16:51:29.824+0500</t>
+          <t>2024-08-16T16:28:43.991+0500</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>2024-09-03T09:16:12.471+0500</t>
+          <t>2024-08-16T16:29:17.981+0500</t>
         </is>
       </c>
       <c r="J240" t="inlineStr"/>
@@ -33330,7 +33528,7 @@
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -33351,47 +33549,47 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>RLT-56</t>
+          <t>RLT-54</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Sick leave 28th Aug 2024</t>
+          <t>Leave for one day 30-08-24</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>2024-09-03T10:03:57.925+0500</t>
+          <t>2024-08-28T16:51:09.454+0500</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2024-09-03T10:04:14.562+0500</t>
+          <t>2024-09-03T09:15:53.284+0500</t>
         </is>
       </c>
       <c r="J241" t="inlineStr"/>
@@ -33405,7 +33603,7 @@
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -33426,47 +33624,47 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>RLT-57</t>
+          <t>RLT-55</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Sick Leave 13th Sept 2024</t>
+          <t>Leave for one day 02-09-24</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>2024-09-23T11:07:49.200+0500</t>
+          <t>2024-08-28T16:51:29.824+0500</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2024-09-23T11:08:09.638+0500</t>
+          <t>2024-09-03T09:16:12.471+0500</t>
         </is>
       </c>
       <c r="J242" t="inlineStr"/>
@@ -33480,7 +33678,7 @@
       <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -33501,47 +33699,47 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>RLT-58</t>
+          <t>RLT-56</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Leave for one day 14-11-24</t>
+          <t>Sick leave 28th Aug 2024</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>2024-11-15T09:25:05.670+0500</t>
+          <t>2024-09-03T10:03:57.925+0500</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2024-11-15T09:38:06.205+0500</t>
+          <t>2024-09-03T10:04:14.562+0500</t>
         </is>
       </c>
       <c r="J243" t="inlineStr"/>
@@ -33555,7 +33753,7 @@
       <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -33576,22 +33774,22 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>RLT-59</t>
+          <t>RLT-57</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Planned Leave 8th Nov 2024</t>
+          <t>Sick Leave 13th Sept 2024</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -33611,12 +33809,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>2024-11-21T12:24:36.990+0500</t>
+          <t>2024-09-23T11:07:49.200+0500</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:57.134+0500</t>
+          <t>2024-09-23T11:08:09.638+0500</t>
         </is>
       </c>
       <c r="J244" t="inlineStr"/>
@@ -33625,16 +33823,16 @@
         <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P244" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q244" t="inlineStr"/>
       <c r="R244" t="inlineStr">
@@ -33644,54 +33842,54 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>RLT-60</t>
+          <t>RLT-58</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Planned Leave 19th Nov 2024</t>
+          <t>Leave for one day 14-11-24</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>2024-11-21T12:25:03.206+0500</t>
+          <t>2024-11-15T09:25:05.670+0500</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:07.591+0500</t>
+          <t>2024-11-15T09:38:06.205+0500</t>
         </is>
       </c>
       <c r="J245" t="inlineStr"/>
@@ -33705,7 +33903,7 @@
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -33726,47 +33924,47 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>RLT-62</t>
+          <t>RLT-59</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Sick leave for one day 30-12-24</t>
+          <t>Planned Leave 8th Nov 2024</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:13.907+0500</t>
+          <t>2024-11-21T12:24:36.990+0500</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>2024-12-31T09:30:33.151+0500</t>
+          <t>2024-12-31T11:38:57.134+0500</t>
         </is>
       </c>
       <c r="J246" t="inlineStr"/>
@@ -33775,16 +33973,16 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P246" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q246" t="inlineStr"/>
       <c r="R246" t="inlineStr">
@@ -33794,24 +33992,24 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>RLT-63</t>
+          <t>RLT-60</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20294</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Planned Leave 29th Nov 2024</t>
+          <t>Planned Leave 19th Nov 2024</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -33836,12 +34034,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>2024-12-31T11:38:18.228+0500</t>
+          <t>2024-11-21T12:25:03.206+0500</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:11.165+0500</t>
+          <t>2024-12-31T11:39:07.591+0500</t>
         </is>
       </c>
       <c r="J247" t="inlineStr"/>
@@ -33876,47 +34074,47 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>RLT-64</t>
+          <t>RLT-62</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20648</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Planned Leave 16th Dec 2024</t>
+          <t>Sick leave for one day 30-12-24</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>2024-12-31T11:39:25.533+0500</t>
+          <t>2024-12-31T09:30:13.907+0500</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:27.662+0500</t>
+          <t>2024-12-31T09:30:33.151+0500</t>
         </is>
       </c>
       <c r="J248" t="inlineStr"/>
@@ -33930,7 +34128,7 @@
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -33951,17 +34149,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>RLT-65</t>
+          <t>RLT-63</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
+          <t>Planned Leave 29th Nov 2024</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -33986,12 +34184,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2024-12-31T11:40:34.525+0500</t>
+          <t>2024-12-31T11:38:18.228+0500</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:36.616+0500</t>
+          <t>2024-12-31T11:39:11.165+0500</t>
         </is>
       </c>
       <c r="J249" t="inlineStr"/>
@@ -34000,7 +34198,7 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr">
@@ -34009,12 +34207,12 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S249" t="inlineStr">
@@ -34026,47 +34224,47 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>RLT-67</t>
+          <t>RLT-64</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>20765</t>
+          <t>20676</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Casual Leave for half day 02-01-25</t>
+          <t>Planned Leave 16th Dec 2024</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>2025-01-06T09:19:42.013+0500</t>
+          <t>2024-12-31T11:39:25.533+0500</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:11.598+0500</t>
+          <t>2025-03-25T09:09:27.662+0500</t>
         </is>
       </c>
       <c r="J250" t="inlineStr"/>
@@ -34075,7 +34273,7 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr">
@@ -34084,7 +34282,7 @@
         </is>
       </c>
       <c r="P250" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr">
@@ -34101,47 +34299,47 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>RLT-68</t>
+          <t>RLT-65</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>20766</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Leave for one day 03-01-25</t>
+          <t>Annual Leave 23rd Dec, 24th Dec, 26th Dec, 27th Dec</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>2025-01-06T09:20:06.483+0500</t>
+          <t>2024-12-31T11:40:34.525+0500</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>2025-01-06T09:21:08.280+0500</t>
+          <t>2025-03-25T09:09:36.616+0500</t>
         </is>
       </c>
       <c r="J251" t="inlineStr"/>
@@ -34150,21 +34348,21 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P251" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S251" t="inlineStr">
@@ -34176,17 +34374,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>RLT-71</t>
+          <t>RLT-67</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Leave for one day 27-02-25</t>
+          <t>Casual Leave for half day 02-01-25</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -34211,12 +34409,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:26.122+0500</t>
+          <t>2025-01-06T09:19:42.013+0500</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>2025-02-28T09:31:46.578+0500</t>
+          <t>2025-01-06T09:21:11.598+0500</t>
         </is>
       </c>
       <c r="J252" t="inlineStr"/>
@@ -34225,16 +34423,16 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P252" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr">
@@ -34251,17 +34449,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>RLT-72</t>
+          <t>RLT-68</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>20766</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Annual leave 31 Jan</t>
+          <t>Leave for one day 03-01-25</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -34271,27 +34469,27 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:16.894+0500</t>
+          <t>2025-01-06T09:20:06.483+0500</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>2025-03-04T11:51:47.087+0500</t>
+          <t>2025-01-06T09:21:08.280+0500</t>
         </is>
       </c>
       <c r="J253" t="inlineStr"/>
@@ -34305,7 +34503,7 @@
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -34326,47 +34524,47 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>RLT-74</t>
+          <t>RLT-71</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>21801</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Planned Leave 21st Feb 2025</t>
+          <t>Leave for one day 27-02-25</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-35</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>2025-03-25T09:09:51.777+0500</t>
+          <t>2025-02-28T09:31:26.122+0500</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:06.523+0500</t>
+          <t>2025-02-28T09:31:46.578+0500</t>
         </is>
       </c>
       <c r="J254" t="inlineStr"/>
@@ -34380,7 +34578,7 @@
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -34401,47 +34599,47 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>RLT-77</t>
+          <t>RLT-72</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Planned Leave 3rd April 2025</t>
+          <t>Annual leave 31 Jan</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>2025-04-29T14:35:54.729+0500</t>
+          <t>2025-03-04T11:51:16.894+0500</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:21.782+0500</t>
+          <t>2025-03-04T11:51:47.087+0500</t>
         </is>
       </c>
       <c r="J255" t="inlineStr"/>
@@ -34476,17 +34674,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RLT-78</t>
+          <t>RLT-74</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Planned Leave 4th April 2025</t>
+          <t>Planned Leave 21st Feb 2025</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -34511,12 +34709,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>2025-04-29T14:36:42.933+0500</t>
+          <t>2025-03-25T09:09:51.777+0500</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>2025-04-29T14:37:01.596+0500</t>
+          <t>2025-04-29T14:36:06.523+0500</t>
         </is>
       </c>
       <c r="J256" t="inlineStr"/>
@@ -34551,47 +34749,47 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>RLT-79</t>
+          <t>RLT-77</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Sick leave</t>
+          <t>Planned Leave 3rd April 2025</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>2025-05-15T10:52:44.037+0500</t>
+          <t>2025-04-29T14:35:54.729+0500</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:11.410+0500</t>
+          <t>2025-04-29T14:36:21.782+0500</t>
         </is>
       </c>
       <c r="J257" t="inlineStr"/>
@@ -34605,7 +34803,7 @@
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -34626,59 +34824,51 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>RLT-80</t>
+          <t>RLT-78</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>22345</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>16 may 2025</t>
+          <t>Planned Leave 4th April 2025</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Hassan Malik</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>RLT-5</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:34.680+0500</t>
+          <t>2025-04-29T14:36:42.933+0500</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>2025-05-20T15:48:58.959+0500</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
+          <t>2025-04-29T14:37:01.596+0500</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="n">
         <v>0</v>
       </c>
@@ -34688,17 +34878,13 @@
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P258" t="n">
         <v>8</v>
       </c>
-      <c r="Q258" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
+      <c r="Q258" t="inlineStr"/>
       <c r="R258" t="inlineStr">
         <is>
           <t>No</t>
@@ -34713,17 +34899,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>RLT-81</t>
+          <t>RLT-79</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Annual leave 22 May</t>
+          <t>Sick leave</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -34748,12 +34934,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>2025-05-21T17:45:49.062+0500</t>
+          <t>2025-05-15T10:52:44.037+0500</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:14.892+0500</t>
+          <t>2025-09-11T09:15:11.410+0500</t>
         </is>
       </c>
       <c r="J259" t="inlineStr"/>
@@ -34767,7 +34953,7 @@
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -34788,51 +34974,59 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>RLT-82</t>
+          <t>RLT-80</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>22592</t>
+          <t>22345</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Planned Leave 5th June 2025</t>
+          <t>16 may 2025</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Hassan Malik</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-5</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Zeeshan Sarwar</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>2025-06-10T11:05:56.983+0500</t>
+          <t>2025-05-20T15:48:34.680+0500</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:20.879+0500</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
+          <t>2025-05-20T15:48:58.959+0500</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
       <c r="L260" t="n">
         <v>0</v>
       </c>
@@ -34842,13 +35036,17 @@
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P260" t="n">
         <v>8</v>
       </c>
-      <c r="Q260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
       <c r="R260" t="inlineStr">
         <is>
           <t>No</t>
@@ -34863,17 +35061,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>RLT-83</t>
+          <t>RLT-81</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>23236</t>
+          <t>22353</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annual leave 07 July</t>
+          <t>Annual leave 22 May</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34898,12 +35096,12 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>2025-07-07T12:00:55.557+0500</t>
+          <t>2025-05-21T17:45:49.062+0500</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:19.601+0500</t>
+          <t>2025-09-11T09:15:14.892+0500</t>
         </is>
       </c>
       <c r="J261" t="inlineStr"/>
@@ -34938,47 +35136,47 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>RLT-84</t>
+          <t>RLT-82</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Casual leave</t>
+          <t>Planned Leave 5th June 2025</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>RLT-17</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Muhammad Abbas</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>2025-09-11T09:14:17.734+0500</t>
+          <t>2025-06-10T11:05:56.983+0500</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>2025-09-11T09:15:22.445+0500</t>
+          <t>2025-09-26T09:55:20.879+0500</t>
         </is>
       </c>
       <c r="J262" t="inlineStr"/>
@@ -34987,7 +35185,7 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr">
@@ -34996,7 +35194,7 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr">
@@ -35006,24 +35204,24 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>RLT-85</t>
+          <t>RLT-83</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Casual leave 10 sept 25</t>
+          <t>Annual leave 07 July</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -35048,12 +35246,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:09.033+0500</t>
+          <t>2025-07-07T12:00:55.557+0500</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>2025-09-11T09:16:45.168+0500</t>
+          <t>2025-09-11T09:15:19.601+0500</t>
         </is>
       </c>
       <c r="J263" t="inlineStr"/>
@@ -35088,47 +35286,47 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>RLT-86</t>
+          <t>RLT-84</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Planned Leave 15th July 2025</t>
+          <t>Casual leave</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:06.810+0500</t>
+          <t>2025-09-11T09:14:17.734+0500</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>2025-09-26T09:55:30.527+0500</t>
+          <t>2025-09-11T09:15:22.445+0500</t>
         </is>
       </c>
       <c r="J264" t="inlineStr"/>
@@ -35137,16 +35335,16 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P264" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q264" t="inlineStr"/>
       <c r="R264" t="inlineStr">
@@ -35156,54 +35354,54 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>RLT-87</t>
+          <t>RLT-85</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Planned 1st Sept 2025</t>
+          <t>Casual leave 10 sept 25</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Resolved!</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>RLT-39</t>
+          <t>RLT-17</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hassan Saeed Wattoo</t>
+          <t>Muhammad Abbas</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>2025-09-26T09:56:28.622+0500</t>
+          <t>2025-09-11T09:16:09.033+0500</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:11.707+0500</t>
+          <t>2025-09-11T09:16:45.168+0500</t>
         </is>
       </c>
       <c r="J265" t="inlineStr"/>
@@ -35217,7 +35415,7 @@
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -35238,17 +35436,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>RLT-88</t>
+          <t>RLT-86</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Planned Leave 15th Aug 2025</t>
+          <t>Planned Leave 15th July 2025</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -35273,12 +35471,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:27.334+0500</t>
+          <t>2025-09-26T09:55:06.810+0500</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>2025-09-26T10:05:46.408+0500</t>
+          <t>2025-09-26T09:55:30.527+0500</t>
         </is>
       </c>
       <c r="J266" t="inlineStr"/>
@@ -35313,22 +35511,22 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>RLT-89</t>
+          <t>RLT-87</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>24388</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
+          <t>Planned 1st Sept 2025</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -35348,12 +35546,12 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>2025-10-08T10:16:40.435+0500</t>
+          <t>2025-09-26T09:56:28.622+0500</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>2025-11-06T09:37:59.818+0500</t>
+          <t>2025-09-26T10:05:11.707+0500</t>
         </is>
       </c>
       <c r="J267" t="inlineStr"/>
@@ -35362,7 +35560,7 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr">
@@ -35371,12 +35569,12 @@
         </is>
       </c>
       <c r="P267" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q267" t="inlineStr"/>
       <c r="R267" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S267" t="inlineStr">
@@ -35388,22 +35586,22 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>RLT-90</t>
+          <t>RLT-88</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Planned Leave 5th Nov 2025</t>
+          <t>Planned Leave 15th Aug 2025</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -35423,12 +35621,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>2025-11-06T09:38:11.154+0500</t>
+          <t>2025-09-26T10:05:27.334+0500</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:11.084+0500</t>
+          <t>2025-09-26T10:05:46.408+0500</t>
         </is>
       </c>
       <c r="J268" t="inlineStr"/>
@@ -35442,7 +35640,7 @@
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -35463,22 +35661,22 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>RLT-95</t>
+          <t>RLT-89</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>31542</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Sick Leave 18th Nov 2025</t>
+          <t>Compassionate Leave 29th Sept, 30th Sept, 1st Oct</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Sick Leave</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -35498,12 +35696,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:01.035+0500</t>
+          <t>2025-10-08T10:16:40.435+0500</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:30.413+0500</t>
+          <t>2025-11-06T09:37:59.818+0500</t>
         </is>
       </c>
       <c r="J269" t="inlineStr"/>
@@ -35512,7 +35710,7 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr">
@@ -35521,12 +35719,12 @@
         </is>
       </c>
       <c r="P269" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q269" t="inlineStr"/>
       <c r="R269" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S269" t="inlineStr">
@@ -35538,22 +35736,22 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>RLT-96</t>
+          <t>RLT-90</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
+          <t>Planned Leave 5th Nov 2025</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Emergency Leave</t>
+          <t>Planned Leave</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -35573,12 +35771,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>2025-12-08T11:30:53.468+0500</t>
+          <t>2025-11-06T09:38:11.154+0500</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:21.845+0500</t>
+          <t>2025-12-08T11:30:11.084+0500</t>
         </is>
       </c>
       <c r="J270" t="inlineStr"/>
@@ -35587,21 +35785,21 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr">
         <is>
-          <t>Unplanned</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="P270" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="Q270" t="inlineStr"/>
       <c r="R270" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S270" t="inlineStr">
@@ -35613,22 +35811,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>RLT-97</t>
+          <t>RLT-95</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>31546</t>
+          <t>31542</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>3rd Dec 2025</t>
+          <t>Sick Leave 18th Nov 2025</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Planned Leave</t>
+          <t>Sick Leave</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -35648,12 +35846,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.693+0500</t>
+          <t>2025-12-08T11:30:01.035+0500</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>2025-12-08T11:32:24.681+0500</t>
+          <t>2025-12-08T11:30:30.413+0500</t>
         </is>
       </c>
       <c r="J271" t="inlineStr"/>
@@ -35667,7 +35865,7 @@
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -35688,47 +35886,47 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>RLT-99</t>
+          <t>RLT-96</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>31544</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Leave for one day 05-12-25</t>
+          <t>Compassionate Leaves 24th Nov, 25th Nov 2025</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Resolved!</t>
+          <t>Emergency Leave</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>RLT-35</t>
+          <t>RLT-39</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Zeeshan Sarwar</t>
+          <t>Hassan Saeed Wattoo</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>2025-12-29T12:28:16.268+0500</t>
+          <t>2025-12-08T11:30:53.468+0500</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>2025-12-29T12:29:46.783+0500</t>
+          <t>2025-12-08T11:31:21.845+0500</t>
         </is>
       </c>
       <c r="J272" t="inlineStr"/>
@@ -35737,24 +35935,174 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Unplanned</t>
         </is>
       </c>
       <c r="P272" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q272" t="inlineStr"/>
       <c r="R272" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S272" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>RLT-97</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>31546</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>3rd Dec 2025</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Planned Leave</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Hassan Saeed Wattoo</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>RLT-39</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Hassan Saeed Wattoo</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>2025-12-08T11:31:59.693+0500</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>2025-12-08T11:32:24.681+0500</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" t="n">
+        <v>8</v>
+      </c>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>RLT-99</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>32431</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Leave for one day 05-12-25</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Resolved!</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>RLT-35</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Zeeshan Sarwar</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:28:16.268+0500</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>2025-12-29T12:29:46.783+0500</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="n">
+        <v>0</v>
+      </c>
+      <c r="M274" t="n">
+        <v>8</v>
+      </c>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -35771,7 +36119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39554,22 +39902,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-219</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
+          <t>2026-03-24T09:00:00.000+0500</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -39589,7 +39937,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -39614,7 +39962,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -39639,7 +39987,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -39664,7 +40012,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -39679,17 +40027,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+          <t>redistributed:2026-01-01-&gt;2026-03-31</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -39714,7 +40062,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -39739,7 +40087,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -39764,7 +40112,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -39789,7 +40137,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -39814,7 +40162,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -39839,7 +40187,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -39864,7 +40212,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -39889,7 +40237,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -39914,7 +40262,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -39939,7 +40287,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -39964,7 +40312,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -39989,7 +40337,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -40014,7 +40362,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -40039,7 +40387,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -40064,7 +40412,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -40089,7 +40437,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -40114,7 +40462,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -40139,7 +40487,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -40164,7 +40512,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -40189,7 +40537,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -40214,15 +40562,40 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>redistributed:2026-04-01-&gt;2026-04-30</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>Maria Sharafat</t>
         </is>
       </c>
-      <c r="E178" t="n">
+      <c r="E179" t="n">
         <v>8</v>
       </c>
     </row>
@@ -40641,7 +41014,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -40656,7 +41029,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -40762,7 +41135,7 @@
         <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -40777,7 +41150,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -40856,7 +41229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43318,19 +43691,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -43340,12 +43713,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>RLT-172</t>
+          <t>RLT-219</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-219</t>
         </is>
       </c>
     </row>
@@ -43357,7 +43730,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -43391,7 +43764,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -43425,7 +43798,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -43459,7 +43832,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -43493,7 +43866,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -43510,19 +43883,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-172</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-172</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -43531,59 +43904,59 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
         <v>8</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>RLT-176</t>
+          <t>RLT-173</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-176</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F80" t="n">
         <v>8</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-176</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-176</t>
         </is>
       </c>
     </row>
@@ -43595,7 +43968,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -43629,7 +44002,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -43663,7 +44036,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -43697,7 +44070,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -43731,7 +44104,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -43765,7 +44138,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -43799,7 +44172,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -43833,7 +44206,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -43867,7 +44240,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -43901,7 +44274,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -43930,34 +44303,34 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F91" t="n">
         <v>8</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>RLT-173</t>
+          <t>RLT-220</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-220</t>
         </is>
       </c>
     </row>
@@ -43969,7 +44342,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -44003,7 +44376,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -44037,7 +44410,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -44071,7 +44444,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -44105,7 +44478,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -44139,7 +44512,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -44173,7 +44546,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -44207,7 +44580,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -44241,27 +44614,95 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>8</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>8</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>RLT-173</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>8</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>8</v>
-      </c>
-      <c r="G100" t="inlineStr">
+      <c r="C102" t="n">
+        <v>8</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>8</v>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>RLT-173</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>https://octopusdtlsupport.atlassian.net/browse/RLT-173</t>
         </is>
@@ -44278,7 +44719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45084,31 +45525,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Taimur Zahid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W13</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Muhammad Imran Aslam</t>
+          <t>Maria Sharafat</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -45117,40 +45558,40 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maria Sharafat</t>
+          <t>Muhammad Imran Aslam</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-W15</t>
+          <t>2026-W14</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
@@ -45161,7 +45602,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-W16</t>
+          <t>2026-W15</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -45185,7 +45626,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-W17</t>
+          <t>2026-W16</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -45204,24 +45645,72 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Muhammad Imran Aslam</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Maria Sharafat</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>40</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Maria Sharafat</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>2026-W18</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C41" t="n">
         <v>32</v>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
         <v>32</v>
       </c>
     </row>
@@ -45766,13 +46255,13 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -45817,10 +46306,10 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
